--- a/public/plantilla-memoria.xlsx
+++ b/public/plantilla-memoria.xlsx
@@ -10089,464 +10089,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-memoria.xlsx
+++ b/public/plantilla-memoria.xlsx
@@ -14,16 +14,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+  <numFmts count="8">
+    <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
+    <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="167">
+  <fonts count="168">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1222,6 +1223,11 @@
       <color theme="1"/>
       <sz val="8"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF8A8F99"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="76">
@@ -1673,7 +1679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="406">
+  <borders count="411">
     <border>
       <left/>
       <right/>
@@ -2871,6 +2877,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
@@ -2878,9 +2895,7 @@
       <top style="thin">
         <color rgb="FFB7C3D0"/>
       </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2890,6 +2905,89 @@
       <right/>
       <top/>
       <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color theme="3" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -2900,206 +2998,77 @@
         <color theme="0" tint="-0.3499862666707358"/>
       </right>
       <top style="thin">
+        <color rgb="FFEAF0F6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right style="thin">
         <color rgb="FFB7C3D0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFEAF0F6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right style="thin">
+      </right>
+      <top style="thin">
         <color rgb="FFB7C3D0"/>
-      </right>
-      <top style="thin">
+      </top>
+      <bottom style="thin">
         <color rgb="FFB7C3D0"/>
-      </top>
-      <bottom style="thin">
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color rgb="FFB7C3D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFB7C3D0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB7C3D0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB7C3D0"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -3227,17 +3196,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF17365D"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB7C3D0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4179,32 +4137,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB7C3D0"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB7C3D0"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB7C3D0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB8C2CC"/>
       </left>
@@ -6174,6 +6106,84 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF17365D"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF17365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E1F2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E1F2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF17365D"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7C3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF002060"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thick">
         <color rgb="FF17365D"/>
@@ -6265,6 +6275,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF002060"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF002060"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="hair">
         <color theme="0" tint="-0.3499862666707358"/>
       </left>
@@ -6322,6 +6367,30 @@
         <color rgb="FF17365D"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7C3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7C3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -6504,7 +6573,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1383">
+  <cellXfs count="1307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -6657,25 +6726,25 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="5" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6697,15 +6766,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="40" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="40" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="40" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -6844,15 +6913,6 @@
     <xf numFmtId="0" fontId="81" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="44" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="44" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="45" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -6865,11 +6925,11 @@
     <xf numFmtId="0" fontId="9" fillId="43" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="43" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="9" fillId="43" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="48" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -6892,10 +6952,10 @@
     <xf numFmtId="0" fontId="21" fillId="47" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6904,25 +6964,46 @@
     <xf numFmtId="0" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6934,28 +7015,7 @@
     <xf numFmtId="0" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -6969,47 +7029,41 @@
     <xf numFmtId="0" fontId="112" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="28" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7024,7 +7078,7 @@
     <xf numFmtId="0" fontId="66" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="111" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7033,16 +7087,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="57" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="58" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="84" fillId="58" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="58" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7083,20 +7137,20 @@
     <xf numFmtId="0" fontId="123" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="53" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="119" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="119" fillId="53" borderId="174" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="2" fontId="127" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="127" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="127" fillId="55" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
@@ -7109,71 +7163,69 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="69" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="69" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="18" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="138" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="242" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="137" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="145" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="242" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="148" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="60" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="60" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7192,26 +7244,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="150" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="149" fillId="70" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="143" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7221,34 +7261,34 @@
     <xf numFmtId="4" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="274" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7259,64 +7299,61 @@
     <xf numFmtId="0" fontId="154" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="25" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="73" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="17" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="136" fillId="25" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="73" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="140" fillId="16" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="140" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="28" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="28" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="74" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="17" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="16" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="80" fillId="74" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="74" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="17" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="16" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="74" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="17" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="16" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="144" fillId="25" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="287" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="144" fillId="25" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -7331,22 +7368,22 @@
     <xf numFmtId="0" fontId="55" fillId="25" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="42" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7354,34 +7391,33 @@
     <xf numFmtId="0" fontId="38" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="42" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="147" fillId="42" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7391,34 +7427,32 @@
     <xf numFmtId="0" fontId="38" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="17" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="25" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="25" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7457,7 +7491,7 @@
     <xf numFmtId="0" fontId="123" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="284" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="123" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -7475,19 +7509,19 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="39" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7496,52 +7530,124 @@
     <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="16" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="5" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="64" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="28" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="25" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="163" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="137" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -7552,226 +7658,166 @@
     <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="46" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="41" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="126" fillId="41" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="274" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="46" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="357" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="64" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="25" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="28" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="28" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="117" fillId="28" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="164" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="28" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="157" fillId="3" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="155" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="87" fillId="49" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="38" fillId="17" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="124" fillId="17" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="167" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="124" fillId="17" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="168" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="165" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="28" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="157" fillId="3" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="155" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="87" fillId="49" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="137" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="137" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="137" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="138" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="138" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="138" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="138" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="168" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7797,12 +7843,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="62" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="55" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="88" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="55" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7811,7 +7857,7 @@
     <xf numFmtId="168" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="55" fillId="20" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7841,37 +7887,37 @@
     <xf numFmtId="168" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="168" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="127" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="167" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="127" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="167" fontId="127" fillId="55" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="168" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="124" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="170" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="170" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="168" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7880,20 +7926,20 @@
     <xf numFmtId="167" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="44" fillId="18" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="44" fillId="18" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="44" fillId="18" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="44" fillId="18" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="59" fillId="19" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="59" fillId="19" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="34" fillId="18" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="34" fillId="18" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7902,11 +7948,12 @@
     <xf numFmtId="167" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="159" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="166" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="97" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7917,30 +7964,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="28" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="162" fillId="25" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="162" fillId="25" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="116" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="28" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="161" fillId="28" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="97" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7963,42 +8010,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="49" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="87" fillId="49" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="28" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="28" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="159" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="41" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="53" fillId="41" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8007,27 +8054,27 @@
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="163" fillId="28" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="163" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8037,7 +8084,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8074,85 +8121,68 @@
     <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="234" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="42" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="133" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="61" borderId="239" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="134" fillId="71" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="259" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="43" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="263" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="61" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="134" fillId="71" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="43" borderId="240" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="60" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="60" borderId="258" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="61" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="61" borderId="239" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="133" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8176,24 +8206,14 @@
     <xf numFmtId="0" fontId="42" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="259" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="257" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="136" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8201,9 +8221,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -8221,20 +8238,17 @@
     <xf numFmtId="0" fontId="66" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="25" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="92" fillId="25" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="75" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="70" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8253,35 +8267,35 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="129" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="128" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="110" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="194" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="198" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="3" borderId="198" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -8290,135 +8304,126 @@
     <xf numFmtId="0" fontId="101" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="49" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="62" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="62" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="100" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="95" fillId="34" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="109" fillId="20" borderId="199" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="200" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="49" fillId="3" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="95" fillId="34" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="109" fillId="20" borderId="195" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="196" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="42" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="3" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="28" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="38" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="34" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="28" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="3" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="36" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="38" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="34" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="28" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8433,57 +8438,50 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="211" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="105" fillId="44" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="120" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
@@ -8494,12 +8492,12 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="210" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -8511,35 +8509,27 @@
     <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="202" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8547,27 +8537,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="108" fillId="44" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
@@ -8578,13 +8565,10 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="198" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="40" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -8597,181 +8581,181 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="26" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="171" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="176" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="41" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="26" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="56" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="121" fillId="28" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="165" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="41" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="28" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="28" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="56" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="121" fillId="28" borderId="361" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="369" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="28" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="28" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="214" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="171" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="211" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="117" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="194" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="194" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="53" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8796,22 +8780,19 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="69" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8826,8 +8807,8 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="236" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="58" fillId="34" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8837,15 +8818,15 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="227" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8858,29 +8839,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="226" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="20" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="232" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="165" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8895,11 +8876,11 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="107" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="3" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="21" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8912,14 +8893,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="223" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="225" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -8941,13 +8922,13 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="234" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="228" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8964,20 +8945,20 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="199" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="228" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="222" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8997,7 +8978,7 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -9019,7 +9000,7 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="224" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -9055,87 +9036,84 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="232" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="226" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="227" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="30" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="169" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="47" fillId="16" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="24" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="29" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="29" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9148,20 +9126,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="49" fillId="3" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -9171,10 +9149,10 @@
     <xf numFmtId="0" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9186,16 +9164,16 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="89" fillId="14" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9205,14 +9183,11 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="169" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -9220,165 +9195,174 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="370" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="57" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="38" fillId="16" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="341" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="47" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="38" fillId="16" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="51" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="51" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="51" fillId="16" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="51" fillId="16" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="253" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="336" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="89" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="255" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="88" fillId="24" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="48" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="47" fillId="16" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="53" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9387,578 +9371,433 @@
     </xf>
     <xf numFmtId="0" fontId="91" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="36" fillId="0" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="14" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="15" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="39" fillId="3" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="102" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="332" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="40" fillId="3" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="25" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="25" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="50" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="372" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="198" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="153" fillId="3" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="49" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="70" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="70" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="132" fillId="60" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="66" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="25" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="28" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="157" fillId="3" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="155" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="87" fillId="49" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="38" fillId="17" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="274" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="41" fillId="66" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="50" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="23" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="15" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="53" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="59" fillId="49" borderId="384" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="39" fillId="3" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="28" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="157" fillId="3" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="155" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="87" fillId="49" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="38" fillId="17" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="137" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="137" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="137" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="138" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="138" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="138" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="138" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="62" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="55" fillId="20" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="55" fillId="20" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="127" fillId="55" borderId="192" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="127" fillId="55" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="124" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="124" fillId="54" borderId="183" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="254" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="44" fillId="18" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="44" fillId="18" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="59" fillId="19" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="51" fillId="16" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="51" fillId="16" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="38" fillId="16" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="18" borderId="256" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="39" fillId="3" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10091,24 +9930,482 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Costo directo por capítulo (COP)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </title>
+    <plotArea>
+      <layout/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Resumen!$C$11</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Valor (COP)</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+            <txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </txPr>
+            <dLblPos val="outEnd"/>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="1"/>
+            <showLeaderLines val="0"/>
+          </dLbls>
+          <cat>
+            <strRef>
+              <f>Resumen!$A$12:$A$25</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>1</v>
+                </pt>
+                <pt idx="1">
+                  <v>2</v>
+                </pt>
+                <pt idx="2">
+                  <v>3</v>
+                </pt>
+                <pt idx="3">
+                  <v>4</v>
+                </pt>
+                <pt idx="4">
+                  <v>5</v>
+                </pt>
+                <pt idx="5">
+                  <v>6</v>
+                </pt>
+                <pt idx="6">
+                  <v>7</v>
+                </pt>
+                <pt idx="7">
+                  <v>8</v>
+                </pt>
+                <pt idx="8">
+                  <v>9</v>
+                </pt>
+                <pt idx="9">
+                  <v>10</v>
+                </pt>
+                <pt idx="10">
+                  <v>11</v>
+                </pt>
+                <pt idx="11">
+                  <v>12</v>
+                </pt>
+                <pt idx="12">
+                  <v>13</v>
+                </pt>
+                <pt idx="13">
+                  <v>14</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Resumen!$C$12:$C$25</f>
+              <numCache>
+                <formatCode>"$ "#,##0</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+                <pt idx="11">
+                  <v>0</v>
+                </pt>
+                <pt idx="12">
+                  <v>0</v>
+                </pt>
+                <pt idx="13">
+                  <v>0</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="50050775"/>
+        <axId val="41416401"/>
+      </barChart>
+      <catAx>
+        <axId val="50050775"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Capítulo</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </txPr>
+        <crossAx val="41416401"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
+      </catAx>
+      <valAx>
+        <axId val="41416401"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>COP</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </title>
+        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </txPr>
+        <crossAx val="50050775"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>OpenAI</author>
+  </authors>
+  <commentList>
+    <comment ref="I26" authorId="0" shapeId="0">
+      <text>
+        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
+      </text>
+    </comment>
+    <comment ref="J26" authorId="0" shapeId="0">
+      <text>
+        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
+      </text>
+    </comment>
+    <comment ref="K26" authorId="0" shapeId="0">
+      <text>
+        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>650240</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>12701</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>6529</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>155382</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Image 1" descr="Picture"/>
+        <xdr:cNvPr id="4" name="Imagen 2"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -10119,8 +10416,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="313765"/>
-          <a:ext cx="2768152" cy="1099671"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2808000" cy="1332000"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -10323,260 +10620,263 @@
   <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4" customWidth="1" style="760" min="1" max="1"/>
-    <col width="27" customWidth="1" style="760" min="2" max="2"/>
-    <col width="10" customWidth="1" style="760" min="3" max="4"/>
-    <col width="11.5546875" customWidth="1" style="760" min="5" max="5"/>
-    <col width="12" customWidth="1" style="760" min="6" max="6"/>
-    <col width="10" customWidth="1" style="760" min="7" max="7"/>
-    <col width="15" customWidth="1" style="760" min="8" max="8"/>
-    <col width="10" customWidth="1" style="760" min="9" max="9"/>
-    <col width="22" customWidth="1" style="760" min="10" max="10"/>
-    <col width="11" customWidth="1" style="760" min="11" max="13"/>
-    <col width="8.88671875" customWidth="1" style="760" min="14" max="16"/>
-    <col width="8.88671875" customWidth="1" style="760" min="17" max="16384"/>
+    <col width="4" customWidth="1" style="740" min="1" max="1"/>
+    <col width="27" customWidth="1" style="740" min="2" max="2"/>
+    <col width="10" customWidth="1" style="740" min="3" max="4"/>
+    <col width="11.5546875" customWidth="1" style="740" min="5" max="5"/>
+    <col width="12" customWidth="1" style="740" min="6" max="6"/>
+    <col width="10" customWidth="1" style="740" min="7" max="7"/>
+    <col width="15" customWidth="1" style="740" min="8" max="8"/>
+    <col width="10" customWidth="1" style="740" min="9" max="9"/>
+    <col width="22" customWidth="1" style="740" min="10" max="10"/>
+    <col width="11" customWidth="1" style="740" min="11" max="13"/>
+    <col width="8.88671875" customWidth="1" style="740" min="14" max="17"/>
+    <col width="8.88671875" customWidth="1" style="740" min="18" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="539">
-      <c r="A1" s="772" t="n"/>
-      <c r="B1" s="757" t="n"/>
-      <c r="C1" s="773" t="n"/>
-      <c r="D1" s="831" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="1223">
+      <c r="A1" s="1236" t="n"/>
+      <c r="B1" s="1258" t="n"/>
+      <c r="C1" s="1258" t="n"/>
+      <c r="D1" s="1232" t="inlineStr">
         <is>
           <t xml:space="preserve">MEMORIAS DE CÁLCULO
 </t>
         </is>
       </c>
-      <c r="E1" s="556" t="n"/>
-      <c r="F1" s="556" t="n"/>
-      <c r="G1" s="556" t="n"/>
-      <c r="H1" s="556" t="n"/>
-      <c r="I1" s="556" t="n"/>
-      <c r="J1" s="556" t="n"/>
-      <c r="K1" s="556" t="n"/>
-      <c r="L1" s="556" t="n"/>
-      <c r="M1" s="557" t="n"/>
+      <c r="E1" s="550" t="n"/>
+      <c r="F1" s="550" t="n"/>
+      <c r="G1" s="550" t="n"/>
+      <c r="H1" s="550" t="n"/>
+      <c r="I1" s="550" t="n"/>
+      <c r="J1" s="550" t="n"/>
+      <c r="K1" s="550" t="n"/>
+      <c r="L1" s="550" t="n"/>
+      <c r="M1" s="551" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="539">
-      <c r="A2" s="759" t="n"/>
-      <c r="C2" s="552" t="n"/>
-      <c r="D2" s="767" t="n"/>
-      <c r="M2" s="552" t="n"/>
+    <row r="2" ht="18" customHeight="1" s="1223">
+      <c r="A2" s="1258" t="n"/>
+      <c r="B2" s="1236" t="n"/>
+      <c r="C2" s="1258" t="n"/>
+      <c r="M2" s="546" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="539">
-      <c r="A3" s="759" t="n"/>
-      <c r="C3" s="552" t="n"/>
-      <c r="D3" s="767" t="n"/>
-      <c r="M3" s="552" t="n"/>
+    <row r="3" ht="18" customHeight="1" s="1223">
+      <c r="A3" s="1258" t="n"/>
+      <c r="B3" s="1236" t="n"/>
+      <c r="C3" s="1258" t="n"/>
+      <c r="M3" s="546" t="n"/>
     </row>
-    <row r="4" ht="4.95" customHeight="1" s="539">
-      <c r="A4" s="759" t="n"/>
-      <c r="C4" s="552" t="n"/>
-      <c r="D4" s="129" t="n"/>
-      <c r="E4" s="130" t="n"/>
-      <c r="F4" s="130" t="n"/>
-      <c r="G4" s="130" t="n"/>
-      <c r="H4" s="130" t="n"/>
-      <c r="I4" s="130" t="n"/>
-      <c r="J4" s="130" t="n"/>
-      <c r="K4" s="130" t="n"/>
-      <c r="L4" s="130" t="n"/>
-      <c r="M4" s="131" t="n"/>
+    <row r="4" ht="4.95" customHeight="1" s="1223">
+      <c r="A4" s="1258" t="n"/>
+      <c r="B4" s="1236" t="n"/>
+      <c r="C4" s="1258" t="n"/>
+      <c r="D4" s="1233" t="n"/>
+      <c r="E4" s="1233" t="n"/>
+      <c r="F4" s="1233" t="n"/>
+      <c r="G4" s="1233" t="n"/>
+      <c r="H4" s="1233" t="n"/>
+      <c r="I4" s="1233" t="n"/>
+      <c r="J4" s="1233" t="n"/>
+      <c r="K4" s="1233" t="n"/>
+      <c r="L4" s="1233" t="n"/>
+      <c r="M4" s="128" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="539">
-      <c r="A5" s="759" t="n"/>
-      <c r="C5" s="552" t="n"/>
-      <c r="D5" s="775" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="1223">
+      <c r="A5" s="1258" t="n"/>
+      <c r="B5" s="1236" t="n"/>
+      <c r="C5" s="1258" t="n"/>
+      <c r="D5" s="1234" t="inlineStr">
         <is>
           <t xml:space="preserve">REFORMAS Y REMODELACIONES                                        </t>
         </is>
       </c>
-      <c r="K5" s="765" t="inlineStr">
+      <c r="K5" s="745" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="L5" s="770" t="inlineStr">
+      <c r="L5" s="750" t="inlineStr">
         <is>
           <t>RYR-MC-001</t>
         </is>
       </c>
-      <c r="M5" s="764" t="n"/>
+      <c r="M5" s="744" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="539">
-      <c r="A6" s="759" t="n"/>
-      <c r="C6" s="552" t="n"/>
-      <c r="D6" s="767" t="n"/>
-      <c r="K6" s="765" t="inlineStr">
+    <row r="6" ht="18" customHeight="1" s="1223">
+      <c r="A6" s="1258" t="n"/>
+      <c r="B6" s="1236" t="n"/>
+      <c r="C6" s="1258" t="n"/>
+      <c r="K6" s="745" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="L6" s="770" t="n">
+      <c r="L6" s="750" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="764" t="n"/>
+      <c r="M6" s="744" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="539">
-      <c r="A7" s="759" t="n"/>
-      <c r="C7" s="552" t="n"/>
-      <c r="D7" s="818" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="1223">
+      <c r="A7" s="1258" t="n"/>
+      <c r="B7" s="1236" t="n"/>
+      <c r="C7" s="1258" t="n"/>
+      <c r="D7" s="1235" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
         </is>
       </c>
-      <c r="K7" s="765" t="inlineStr">
+      <c r="K7" s="745" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="L7" s="770" t="inlineStr">
+      <c r="L7" s="750" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="M7" s="764" t="n"/>
+      <c r="M7" s="744" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="539">
-      <c r="A8" s="774" t="n"/>
-      <c r="B8" s="602" t="n"/>
-      <c r="C8" s="750" t="n"/>
-      <c r="D8" s="127" t="n"/>
-      <c r="E8" s="128" t="n"/>
-      <c r="F8" s="128" t="n"/>
-      <c r="G8" s="128" t="n"/>
-      <c r="H8" s="128" t="n"/>
-      <c r="I8" s="128" t="n"/>
-      <c r="J8" s="128" t="n"/>
-      <c r="K8" s="95" t="inlineStr">
+    <row r="8" ht="18" customHeight="1" s="1223">
+      <c r="A8" s="1237" t="n"/>
+      <c r="B8" s="1237" t="n"/>
+      <c r="C8" s="1237" t="n"/>
+      <c r="D8" s="1238" t="n"/>
+      <c r="E8" s="1238" t="n"/>
+      <c r="F8" s="1238" t="n"/>
+      <c r="G8" s="1238" t="n"/>
+      <c r="H8" s="1238" t="n"/>
+      <c r="I8" s="1238" t="n"/>
+      <c r="J8" s="1238" t="n"/>
+      <c r="K8" s="1239" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="L8" s="813" t="inlineStr">
+      <c r="L8" s="1240" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
-      <c r="M8" s="814" t="n"/>
+      <c r="M8" s="741" t="n"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1" s="539">
-      <c r="A9" s="810" t="inlineStr">
+    <row r="9" ht="19.5" customHeight="1" s="1223">
+      <c r="A9" s="1241" t="inlineStr">
         <is>
           <t>01  |  IDENTIFICACIÓN DEL PROYECTO Y DE LA ACTIVIDAD</t>
         </is>
       </c>
-      <c r="B9" s="556" t="n"/>
-      <c r="C9" s="556" t="n"/>
-      <c r="D9" s="556" t="n"/>
-      <c r="E9" s="556" t="n"/>
-      <c r="F9" s="556" t="n"/>
-      <c r="G9" s="556" t="n"/>
-      <c r="H9" s="556" t="n"/>
-      <c r="I9" s="556" t="n"/>
-      <c r="J9" s="556" t="n"/>
-      <c r="K9" s="556" t="n"/>
-      <c r="L9" s="556" t="n"/>
-      <c r="M9" s="811" t="n"/>
+      <c r="B9" s="1242" t="n"/>
+      <c r="C9" s="1242" t="n"/>
+      <c r="D9" s="1242" t="n"/>
+      <c r="E9" s="1242" t="n"/>
+      <c r="F9" s="1242" t="n"/>
+      <c r="G9" s="1242" t="n"/>
+      <c r="H9" s="1242" t="n"/>
+      <c r="I9" s="1242" t="n"/>
+      <c r="J9" s="1242" t="n"/>
+      <c r="K9" s="1242" t="n"/>
+      <c r="L9" s="1242" t="n"/>
+      <c r="M9" s="1299" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="539">
-      <c r="A10" s="780" t="inlineStr">
+    <row r="10" ht="18" customHeight="1" s="1223">
+      <c r="A10" s="757" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B10" s="763" t="n"/>
-      <c r="C10" s="808" t="n"/>
-      <c r="H10" s="765" t="inlineStr">
+      <c r="B10" s="743" t="n"/>
+      <c r="C10" s="786" t="n"/>
+      <c r="H10" s="745" t="inlineStr">
         <is>
           <t>Área / Frente</t>
         </is>
       </c>
-      <c r="I10" s="763" t="n"/>
+      <c r="I10" s="743" t="n"/>
       <c r="J10" s="31" t="n"/>
-      <c r="K10" s="765" t="inlineStr">
+      <c r="K10" s="745" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="L10" s="763" t="n"/>
+      <c r="L10" s="743" t="n"/>
       <c r="M10" s="69" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="539">
-      <c r="A11" s="780" t="inlineStr">
+    <row r="11" ht="18" customHeight="1" s="1223">
+      <c r="A11" s="757" t="inlineStr">
         <is>
           <t>Contratante</t>
         </is>
       </c>
-      <c r="B11" s="763" t="n"/>
-      <c r="C11" s="816" t="n"/>
-      <c r="D11" s="817" t="n"/>
-      <c r="E11" s="817" t="n"/>
-      <c r="F11" s="817" t="n"/>
-      <c r="G11" s="817" t="n"/>
-      <c r="H11" s="787" t="inlineStr">
+      <c r="B11" s="743" t="n"/>
+      <c r="C11" s="789" t="n"/>
+      <c r="D11" s="790" t="n"/>
+      <c r="E11" s="790" t="n"/>
+      <c r="F11" s="790" t="n"/>
+      <c r="G11" s="790" t="n"/>
+      <c r="H11" s="764" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="I11" s="784" t="n"/>
+      <c r="I11" s="761" t="n"/>
       <c r="J11" s="32" t="n"/>
-      <c r="K11" s="765" t="inlineStr">
+      <c r="K11" s="745" t="inlineStr">
         <is>
           <t>Memoria No.</t>
         </is>
       </c>
-      <c r="L11" s="763" t="n"/>
+      <c r="L11" s="743" t="n"/>
       <c r="M11" s="69" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="539">
-      <c r="A12" s="780" t="inlineStr">
+    <row r="12" ht="30" customHeight="1" s="1223">
+      <c r="A12" s="757" t="inlineStr">
         <is>
           <t>Actividad / Ítem</t>
         </is>
       </c>
-      <c r="B12" s="763" t="n"/>
-      <c r="C12" s="815" t="inlineStr">
+      <c r="B12" s="743" t="n"/>
+      <c r="C12" s="788" t="inlineStr">
         <is>
           <t>1.3.1</t>
         </is>
       </c>
-      <c r="D12" s="763" t="n"/>
-      <c r="E12" s="765" t="inlineStr">
+      <c r="D12" s="743" t="n"/>
+      <c r="E12" s="745" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="F12" s="828" t="inlineStr">
+      <c r="F12" s="800" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="G12" s="829" t="n"/>
-      <c r="H12" s="791" t="inlineStr">
+      <c r="G12" s="801" t="n"/>
+      <c r="H12" s="768" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="I12" s="784" t="n"/>
-      <c r="J12" s="797" t="n"/>
-      <c r="K12" s="784" t="n"/>
-      <c r="L12" s="784" t="n"/>
-      <c r="M12" s="785" t="n"/>
+      <c r="I12" s="761" t="n"/>
+      <c r="J12" s="774" t="n"/>
+      <c r="K12" s="761" t="n"/>
+      <c r="L12" s="761" t="n"/>
+      <c r="M12" s="762" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="539">
+    <row r="13" ht="18" customHeight="1" s="1223">
       <c r="A13" s="70" t="n"/>
       <c r="M13" s="71" t="n"/>
     </row>
-    <row r="14" ht="19.5" customHeight="1" s="539" thickBot="1">
-      <c r="A14" s="812" t="inlineStr">
+    <row r="14" ht="19.5" customHeight="1" s="1223" thickBot="1">
+      <c r="A14" s="787" t="inlineStr">
         <is>
           <t>02  |  MEDICIÓN DE CAMPO / DATOS DE ENTRADA</t>
         </is>
       </c>
-      <c r="M14" s="761" t="n"/>
+      <c r="M14" s="741" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="539" thickBot="1">
+    <row r="15" ht="18" customHeight="1" s="1223" thickBot="1">
       <c r="A15" s="76" t="inlineStr">
         <is>
           <t>N°</t>
@@ -10622,26 +10922,26 @@
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="J15" s="834" t="inlineStr">
+      <c r="J15" s="805" t="inlineStr">
         <is>
           <t>OBSERVACIÓN</t>
         </is>
       </c>
-      <c r="K15" s="777" t="n"/>
-      <c r="L15" s="777" t="n"/>
-      <c r="M15" s="835" t="n"/>
+      <c r="K15" s="754" t="n"/>
+      <c r="L15" s="754" t="n"/>
+      <c r="M15" s="806" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1" s="539">
+    <row r="16" ht="18" customHeight="1" s="1223">
       <c r="A16" s="72" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="10" t="n"/>
-      <c r="C16" s="1327" t="n"/>
-      <c r="D16" s="1327" t="n"/>
-      <c r="E16" s="1327" t="n"/>
-      <c r="F16" s="1327" t="n"/>
-      <c r="G16" s="1327" t="n"/>
-      <c r="H16" s="1328">
+      <c r="C16" s="1300" t="n"/>
+      <c r="D16" s="1300" t="n"/>
+      <c r="E16" s="1300" t="n"/>
+      <c r="F16" s="1300" t="n"/>
+      <c r="G16" s="1300" t="n"/>
+      <c r="H16" s="1301">
         <f>IF(COUNTA(C16:G16)=0,"",ROUND(PRODUCT(C16:G16),3))</f>
         <v/>
       </c>
@@ -10650,22 +10950,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J16" s="821" t="n"/>
-      <c r="K16" s="822" t="n"/>
-      <c r="L16" s="822" t="n"/>
-      <c r="M16" s="823" t="n"/>
+      <c r="J16" s="793" t="n"/>
+      <c r="K16" s="794" t="n"/>
+      <c r="L16" s="794" t="n"/>
+      <c r="M16" s="795" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="539">
+    <row r="17" ht="18" customHeight="1" s="1223">
       <c r="A17" s="72" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="10" t="n"/>
-      <c r="C17" s="1327" t="n"/>
-      <c r="D17" s="1327" t="n"/>
-      <c r="E17" s="1327" t="n"/>
-      <c r="F17" s="1327" t="n"/>
-      <c r="G17" s="1327" t="n"/>
-      <c r="H17" s="1328">
+      <c r="C17" s="1300" t="n"/>
+      <c r="D17" s="1300" t="n"/>
+      <c r="E17" s="1300" t="n"/>
+      <c r="F17" s="1300" t="n"/>
+      <c r="G17" s="1300" t="n"/>
+      <c r="H17" s="1301">
         <f>IF(COUNTA(C17:G17)=0,"",ROUND(PRODUCT(C17:G17),3))</f>
         <v/>
       </c>
@@ -10674,22 +10974,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J17" s="768" t="n"/>
-      <c r="K17" s="536" t="n"/>
-      <c r="L17" s="536" t="n"/>
-      <c r="M17" s="769" t="n"/>
+      <c r="J17" s="748" t="n"/>
+      <c r="K17" s="530" t="n"/>
+      <c r="L17" s="530" t="n"/>
+      <c r="M17" s="749" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="539">
+    <row r="18" ht="18" customHeight="1" s="1223">
       <c r="A18" s="72" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="10" t="n"/>
-      <c r="C18" s="1327" t="n"/>
-      <c r="D18" s="1327" t="n"/>
-      <c r="E18" s="1327" t="n"/>
-      <c r="F18" s="1327" t="n"/>
-      <c r="G18" s="1327" t="n"/>
-      <c r="H18" s="1328">
+      <c r="C18" s="1300" t="n"/>
+      <c r="D18" s="1300" t="n"/>
+      <c r="E18" s="1300" t="n"/>
+      <c r="F18" s="1300" t="n"/>
+      <c r="G18" s="1300" t="n"/>
+      <c r="H18" s="1301">
         <f>IF(COUNTA(C18:G18)=0,"",ROUND(PRODUCT(C18:G18),3))</f>
         <v/>
       </c>
@@ -10698,22 +10998,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J18" s="768" t="n"/>
-      <c r="K18" s="536" t="n"/>
-      <c r="L18" s="536" t="n"/>
-      <c r="M18" s="769" t="n"/>
+      <c r="J18" s="748" t="n"/>
+      <c r="K18" s="530" t="n"/>
+      <c r="L18" s="530" t="n"/>
+      <c r="M18" s="749" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="539">
+    <row r="19" ht="18" customHeight="1" s="1223">
       <c r="A19" s="72" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="10" t="n"/>
-      <c r="C19" s="1327" t="n"/>
-      <c r="D19" s="1327" t="n"/>
-      <c r="E19" s="1327" t="n"/>
-      <c r="F19" s="1327" t="n"/>
-      <c r="G19" s="1327" t="n"/>
-      <c r="H19" s="1328">
+      <c r="C19" s="1300" t="n"/>
+      <c r="D19" s="1300" t="n"/>
+      <c r="E19" s="1300" t="n"/>
+      <c r="F19" s="1300" t="n"/>
+      <c r="G19" s="1300" t="n"/>
+      <c r="H19" s="1301">
         <f>IF(COUNTA(C19:G19)=0,"",ROUND(PRODUCT(C19:G19),3))</f>
         <v/>
       </c>
@@ -10722,22 +11022,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J19" s="768" t="n"/>
-      <c r="K19" s="536" t="n"/>
-      <c r="L19" s="536" t="n"/>
-      <c r="M19" s="769" t="n"/>
+      <c r="J19" s="748" t="n"/>
+      <c r="K19" s="530" t="n"/>
+      <c r="L19" s="530" t="n"/>
+      <c r="M19" s="749" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="539">
+    <row r="20" ht="18" customHeight="1" s="1223">
       <c r="A20" s="72" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="10" t="n"/>
-      <c r="C20" s="1327" t="n"/>
-      <c r="D20" s="1327" t="n"/>
-      <c r="E20" s="1327" t="n"/>
-      <c r="F20" s="1327" t="n"/>
-      <c r="G20" s="1327" t="n"/>
-      <c r="H20" s="1328">
+      <c r="C20" s="1300" t="n"/>
+      <c r="D20" s="1300" t="n"/>
+      <c r="E20" s="1300" t="n"/>
+      <c r="F20" s="1300" t="n"/>
+      <c r="G20" s="1300" t="n"/>
+      <c r="H20" s="1301">
         <f>IF(COUNTA(C20:G20)=0,"",ROUND(PRODUCT(C20:G20),3))</f>
         <v/>
       </c>
@@ -10746,22 +11046,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J20" s="768" t="n"/>
-      <c r="K20" s="536" t="n"/>
-      <c r="L20" s="536" t="n"/>
-      <c r="M20" s="769" t="n"/>
+      <c r="J20" s="748" t="n"/>
+      <c r="K20" s="530" t="n"/>
+      <c r="L20" s="530" t="n"/>
+      <c r="M20" s="749" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="539">
+    <row r="21" ht="18" customHeight="1" s="1223">
       <c r="A21" s="72" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="10" t="n"/>
-      <c r="C21" s="1327" t="n"/>
-      <c r="D21" s="1327" t="n"/>
-      <c r="E21" s="1327" t="n"/>
-      <c r="F21" s="1327" t="n"/>
-      <c r="G21" s="1327" t="n"/>
-      <c r="H21" s="1328">
+      <c r="C21" s="1300" t="n"/>
+      <c r="D21" s="1300" t="n"/>
+      <c r="E21" s="1300" t="n"/>
+      <c r="F21" s="1300" t="n"/>
+      <c r="G21" s="1300" t="n"/>
+      <c r="H21" s="1301">
         <f>IF(COUNTA(C21:G21)=0,"",ROUND(PRODUCT(C21:G21),3))</f>
         <v/>
       </c>
@@ -10770,22 +11070,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J21" s="768" t="n"/>
-      <c r="K21" s="536" t="n"/>
-      <c r="L21" s="536" t="n"/>
-      <c r="M21" s="769" t="n"/>
+      <c r="J21" s="748" t="n"/>
+      <c r="K21" s="530" t="n"/>
+      <c r="L21" s="530" t="n"/>
+      <c r="M21" s="749" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="539">
+    <row r="22" ht="18" customHeight="1" s="1223">
       <c r="A22" s="72" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="10" t="n"/>
-      <c r="C22" s="1327" t="n"/>
-      <c r="D22" s="1327" t="n"/>
-      <c r="E22" s="1327" t="n"/>
-      <c r="F22" s="1327" t="n"/>
-      <c r="G22" s="1327" t="n"/>
-      <c r="H22" s="1328">
+      <c r="C22" s="1300" t="n"/>
+      <c r="D22" s="1300" t="n"/>
+      <c r="E22" s="1300" t="n"/>
+      <c r="F22" s="1300" t="n"/>
+      <c r="G22" s="1300" t="n"/>
+      <c r="H22" s="1301">
         <f>IF(COUNTA(C22:G22)=0,"",ROUND(PRODUCT(C22:G22),3))</f>
         <v/>
       </c>
@@ -10794,22 +11094,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J22" s="768" t="n"/>
-      <c r="K22" s="536" t="n"/>
-      <c r="L22" s="536" t="n"/>
-      <c r="M22" s="769" t="n"/>
+      <c r="J22" s="748" t="n"/>
+      <c r="K22" s="530" t="n"/>
+      <c r="L22" s="530" t="n"/>
+      <c r="M22" s="749" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="539">
+    <row r="23" ht="18" customHeight="1" s="1223">
       <c r="A23" s="72" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="10" t="n"/>
-      <c r="C23" s="1327" t="n"/>
-      <c r="D23" s="1327" t="n"/>
-      <c r="E23" s="1327" t="n"/>
-      <c r="F23" s="1327" t="n"/>
-      <c r="G23" s="1327" t="n"/>
-      <c r="H23" s="1328">
+      <c r="C23" s="1300" t="n"/>
+      <c r="D23" s="1300" t="n"/>
+      <c r="E23" s="1300" t="n"/>
+      <c r="F23" s="1300" t="n"/>
+      <c r="G23" s="1300" t="n"/>
+      <c r="H23" s="1301">
         <f>IF(COUNTA(C23:G23)=0,"",ROUND(PRODUCT(C23:G23),3))</f>
         <v/>
       </c>
@@ -10818,22 +11118,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J23" s="768" t="n"/>
-      <c r="K23" s="536" t="n"/>
-      <c r="L23" s="536" t="n"/>
-      <c r="M23" s="769" t="n"/>
+      <c r="J23" s="748" t="n"/>
+      <c r="K23" s="530" t="n"/>
+      <c r="L23" s="530" t="n"/>
+      <c r="M23" s="749" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="539">
+    <row r="24" ht="18" customHeight="1" s="1223">
       <c r="A24" s="72" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="10" t="n"/>
-      <c r="C24" s="1327" t="n"/>
-      <c r="D24" s="1327" t="n"/>
-      <c r="E24" s="1327" t="n"/>
-      <c r="F24" s="1327" t="n"/>
-      <c r="G24" s="1327" t="n"/>
-      <c r="H24" s="1328">
+      <c r="C24" s="1300" t="n"/>
+      <c r="D24" s="1300" t="n"/>
+      <c r="E24" s="1300" t="n"/>
+      <c r="F24" s="1300" t="n"/>
+      <c r="G24" s="1300" t="n"/>
+      <c r="H24" s="1301">
         <f>IF(COUNTA(C24:G24)=0,"",ROUND(PRODUCT(C24:G24),3))</f>
         <v/>
       </c>
@@ -10842,22 +11142,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J24" s="768" t="n"/>
-      <c r="K24" s="536" t="n"/>
-      <c r="L24" s="536" t="n"/>
-      <c r="M24" s="769" t="n"/>
+      <c r="J24" s="748" t="n"/>
+      <c r="K24" s="530" t="n"/>
+      <c r="L24" s="530" t="n"/>
+      <c r="M24" s="749" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="539" thickBot="1">
+    <row r="25" ht="18" customHeight="1" s="1223" thickBot="1">
       <c r="A25" s="72" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="10" t="n"/>
-      <c r="C25" s="1327" t="n"/>
-      <c r="D25" s="1327" t="n"/>
-      <c r="E25" s="1327" t="n"/>
-      <c r="F25" s="1327" t="n"/>
-      <c r="G25" s="1327" t="n"/>
-      <c r="H25" s="1328">
+      <c r="C25" s="1300" t="n"/>
+      <c r="D25" s="1300" t="n"/>
+      <c r="E25" s="1300" t="n"/>
+      <c r="F25" s="1300" t="n"/>
+      <c r="G25" s="1300" t="n"/>
+      <c r="H25" s="1301">
         <f>IF(COUNTA(C25:G25)=0,"",ROUND(PRODUCT(C25:G25),3))</f>
         <v/>
       </c>
@@ -10866,23 +11166,23 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J25" s="768" t="n"/>
-      <c r="K25" s="536" t="n"/>
-      <c r="L25" s="536" t="n"/>
-      <c r="M25" s="769" t="n"/>
+      <c r="J25" s="748" t="n"/>
+      <c r="K25" s="530" t="n"/>
+      <c r="L25" s="530" t="n"/>
+      <c r="M25" s="749" t="n"/>
     </row>
     <row r="26" ht="18" customFormat="1" customHeight="1" s="12" thickBot="1">
-      <c r="A26" s="776" t="inlineStr">
+      <c r="A26" s="753" t="inlineStr">
         <is>
           <t>TOTAL CANTIDAD CALCULADA</t>
         </is>
       </c>
-      <c r="B26" s="777" t="n"/>
-      <c r="C26" s="777" t="n"/>
-      <c r="D26" s="777" t="n"/>
-      <c r="E26" s="777" t="n"/>
-      <c r="F26" s="777" t="n"/>
-      <c r="G26" s="777" t="n"/>
+      <c r="B26" s="754" t="n"/>
+      <c r="C26" s="754" t="n"/>
+      <c r="D26" s="754" t="n"/>
+      <c r="E26" s="754" t="n"/>
+      <c r="F26" s="754" t="n"/>
+      <c r="G26" s="754" t="n"/>
       <c r="H26" s="11">
         <f>IF(COUNT(H16:H25)=0,"",ROUND(SUM(H16:H25),3))</f>
         <v/>
@@ -10892,144 +11192,144 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J26" s="768" t="n"/>
-      <c r="K26" s="536" t="n"/>
-      <c r="L26" s="536" t="n"/>
-      <c r="M26" s="769" t="n"/>
+      <c r="J26" s="748" t="n"/>
+      <c r="K26" s="530" t="n"/>
+      <c r="L26" s="530" t="n"/>
+      <c r="M26" s="749" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="539">
+    <row r="27" ht="18" customHeight="1" s="1223">
       <c r="A27" s="70" t="n"/>
-      <c r="J27" s="789" t="n"/>
-      <c r="K27" s="763" t="n"/>
-      <c r="L27" s="763" t="n"/>
-      <c r="M27" s="790" t="n"/>
+      <c r="J27" s="766" t="n"/>
+      <c r="K27" s="743" t="n"/>
+      <c r="L27" s="743" t="n"/>
+      <c r="M27" s="767" t="n"/>
     </row>
-    <row r="28" ht="19.5" customHeight="1" s="539">
-      <c r="A28" s="783" t="inlineStr">
+    <row r="28" ht="19.5" customHeight="1" s="1223">
+      <c r="A28" s="760" t="inlineStr">
         <is>
           <t>03  |  RESUMEN Y CONTROL DE CANTIDADES</t>
         </is>
       </c>
-      <c r="B28" s="784" t="n"/>
-      <c r="C28" s="784" t="n"/>
-      <c r="D28" s="784" t="n"/>
-      <c r="E28" s="784" t="n"/>
-      <c r="F28" s="784" t="n"/>
-      <c r="G28" s="784" t="n"/>
-      <c r="H28" s="784" t="n"/>
-      <c r="I28" s="784" t="n"/>
-      <c r="J28" s="784" t="n"/>
-      <c r="K28" s="784" t="n"/>
-      <c r="L28" s="784" t="n"/>
-      <c r="M28" s="785" t="n"/>
+      <c r="B28" s="761" t="n"/>
+      <c r="C28" s="761" t="n"/>
+      <c r="D28" s="761" t="n"/>
+      <c r="E28" s="761" t="n"/>
+      <c r="F28" s="761" t="n"/>
+      <c r="G28" s="761" t="n"/>
+      <c r="H28" s="761" t="n"/>
+      <c r="I28" s="761" t="n"/>
+      <c r="J28" s="761" t="n"/>
+      <c r="K28" s="761" t="n"/>
+      <c r="L28" s="761" t="n"/>
+      <c r="M28" s="762" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="539">
-      <c r="A29" s="780" t="inlineStr">
+    <row r="29" ht="18" customHeight="1" s="1223">
+      <c r="A29" s="757" t="inlineStr">
         <is>
           <t>Cantidad calculada</t>
         </is>
       </c>
-      <c r="B29" s="763" t="n"/>
-      <c r="C29" s="763" t="n"/>
-      <c r="D29" s="771">
+      <c r="B29" s="743" t="n"/>
+      <c r="C29" s="743" t="n"/>
+      <c r="D29" s="751">
         <f>H26</f>
         <v/>
       </c>
-      <c r="E29" s="763" t="n"/>
-      <c r="F29" s="763" t="n"/>
-      <c r="G29" s="763" t="n"/>
-      <c r="H29" s="805" t="inlineStr">
+      <c r="E29" s="743" t="n"/>
+      <c r="F29" s="743" t="n"/>
+      <c r="G29" s="743" t="n"/>
+      <c r="H29" s="782" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="I29" s="763" t="n"/>
+      <c r="I29" s="743" t="n"/>
       <c r="M29" s="71" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="539">
-      <c r="A30" s="780" t="inlineStr">
+    <row r="30" ht="18" customHeight="1" s="1223">
+      <c r="A30" s="757" t="inlineStr">
         <is>
           <t>Cantidad contractual</t>
         </is>
       </c>
-      <c r="B30" s="763" t="n"/>
-      <c r="C30" s="763" t="n"/>
-      <c r="D30" s="827" t="n"/>
-      <c r="E30" s="763" t="n"/>
-      <c r="F30" s="763" t="n"/>
-      <c r="G30" s="763" t="n"/>
-      <c r="H30" s="805" t="inlineStr">
+      <c r="B30" s="743" t="n"/>
+      <c r="C30" s="743" t="n"/>
+      <c r="D30" s="799" t="n"/>
+      <c r="E30" s="743" t="n"/>
+      <c r="F30" s="743" t="n"/>
+      <c r="G30" s="743" t="n"/>
+      <c r="H30" s="782" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="I30" s="763" t="n"/>
+      <c r="I30" s="743" t="n"/>
       <c r="M30" s="71" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="539">
-      <c r="A31" s="780" t="inlineStr">
+    <row r="31" ht="18" customHeight="1" s="1223">
+      <c r="A31" s="757" t="inlineStr">
         <is>
           <t>Saldo contractual</t>
         </is>
       </c>
-      <c r="B31" s="763" t="n"/>
-      <c r="C31" s="763" t="n"/>
-      <c r="D31" s="771">
+      <c r="B31" s="743" t="n"/>
+      <c r="C31" s="743" t="n"/>
+      <c r="D31" s="751">
         <f>IF(OR(D29="",D30=""),"",D30-D29)</f>
         <v/>
       </c>
-      <c r="E31" s="763" t="n"/>
-      <c r="F31" s="763" t="n"/>
-      <c r="G31" s="763" t="n"/>
-      <c r="H31" s="805" t="inlineStr">
+      <c r="E31" s="743" t="n"/>
+      <c r="F31" s="743" t="n"/>
+      <c r="G31" s="743" t="n"/>
+      <c r="H31" s="782" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="I31" s="763" t="n"/>
+      <c r="I31" s="743" t="n"/>
       <c r="M31" s="71" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="539">
-      <c r="A32" s="780" t="inlineStr">
+    <row r="32" ht="18" customHeight="1" s="1223">
+      <c r="A32" s="757" t="inlineStr">
         <is>
           <t>% ejecutado</t>
         </is>
       </c>
-      <c r="B32" s="763" t="n"/>
-      <c r="C32" s="763" t="n"/>
-      <c r="D32" s="836">
+      <c r="B32" s="743" t="n"/>
+      <c r="C32" s="743" t="n"/>
+      <c r="D32" s="807">
         <f>IFERROR(D29/D30,0)</f>
         <v/>
       </c>
-      <c r="E32" s="763" t="n"/>
-      <c r="F32" s="763" t="n"/>
-      <c r="G32" s="763" t="n"/>
-      <c r="H32" s="805" t="inlineStr">
+      <c r="E32" s="743" t="n"/>
+      <c r="F32" s="743" t="n"/>
+      <c r="G32" s="743" t="n"/>
+      <c r="H32" s="782" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="I32" s="763" t="n"/>
+      <c r="I32" s="743" t="n"/>
       <c r="M32" s="71" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="539">
-      <c r="A33" s="830" t="inlineStr">
+    <row r="33" ht="18" customHeight="1" s="1223">
+      <c r="A33" s="802" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D33" s="782">
+      <c r="D33" s="759">
         <f>IF(D30="","PENDIENTE DE DATO",IF(D29&lt;=D30,"DENTRO DE CANTIDAD","REVISAR SOBREEJECUCIÓN"))</f>
         <v/>
       </c>
-      <c r="H33" s="837" t="inlineStr">
+      <c r="H33" s="808" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
       <c r="M33" s="71" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="539">
+    <row r="34" ht="18" customHeight="1" s="1223">
       <c r="A34" s="73" t="n"/>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -11044,435 +11344,435 @@
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="74" t="n"/>
     </row>
-    <row r="35" ht="19.5" customHeight="1" s="539">
-      <c r="A35" s="781" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1" s="1223">
+      <c r="A35" s="758" t="inlineStr">
         <is>
           <t>04  |  DESARROLLO MATEMÁTICO Y CRITERIO DE MEDICIÓN</t>
         </is>
       </c>
-      <c r="B35" s="763" t="n"/>
-      <c r="C35" s="763" t="n"/>
-      <c r="D35" s="763" t="n"/>
-      <c r="E35" s="763" t="n"/>
-      <c r="F35" s="763" t="n"/>
-      <c r="G35" s="763" t="n"/>
-      <c r="H35" s="763" t="n"/>
-      <c r="I35" s="763" t="n"/>
-      <c r="J35" s="763" t="n"/>
-      <c r="K35" s="763" t="n"/>
-      <c r="L35" s="763" t="n"/>
-      <c r="M35" s="764" t="n"/>
+      <c r="B35" s="743" t="n"/>
+      <c r="C35" s="743" t="n"/>
+      <c r="D35" s="743" t="n"/>
+      <c r="E35" s="743" t="n"/>
+      <c r="F35" s="743" t="n"/>
+      <c r="G35" s="743" t="n"/>
+      <c r="H35" s="743" t="n"/>
+      <c r="I35" s="743" t="n"/>
+      <c r="J35" s="743" t="n"/>
+      <c r="K35" s="743" t="n"/>
+      <c r="L35" s="743" t="n"/>
+      <c r="M35" s="744" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="539">
-      <c r="A36" s="766" t="inlineStr">
+    <row r="36" ht="18" customHeight="1" s="1223">
+      <c r="A36" s="746" t="inlineStr">
         <is>
           <t>CRITERIO
 Producto de las dimensiones, cantidades y factores registrados. Ajustar el factor cuando aplique.</t>
         </is>
       </c>
-      <c r="B36" s="757" t="n"/>
-      <c r="C36" s="757" t="n"/>
-      <c r="D36" s="758" t="n"/>
-      <c r="E36" s="786" t="inlineStr">
+      <c r="B36" s="737" t="n"/>
+      <c r="C36" s="737" t="n"/>
+      <c r="D36" s="738" t="n"/>
+      <c r="E36" s="763" t="inlineStr">
         <is>
           <t>OPERACIÓN AUTOMÁTICA
 Resultado por registro = PRODUCTO(CANT., LARGO, ANCHO, ALTO/PESO, FACTOR)</t>
         </is>
       </c>
-      <c r="F36" s="757" t="n"/>
-      <c r="G36" s="757" t="n"/>
-      <c r="H36" s="757" t="n"/>
-      <c r="I36" s="758" t="n"/>
-      <c r="J36" s="833" t="inlineStr">
+      <c r="F36" s="737" t="n"/>
+      <c r="G36" s="737" t="n"/>
+      <c r="H36" s="737" t="n"/>
+      <c r="I36" s="738" t="n"/>
+      <c r="J36" s="804" t="inlineStr">
         <is>
           <t>RESULTADO
 =H23</t>
         </is>
       </c>
-      <c r="K36" s="757" t="n"/>
-      <c r="L36" s="757" t="n"/>
-      <c r="M36" s="773" t="n"/>
+      <c r="K36" s="737" t="n"/>
+      <c r="L36" s="737" t="n"/>
+      <c r="M36" s="752" t="n"/>
     </row>
-    <row r="37" ht="60" customHeight="1" s="539">
-      <c r="A37" s="767" t="n"/>
-      <c r="D37" s="761" t="n"/>
-      <c r="E37" s="759" t="n"/>
-      <c r="I37" s="761" t="n"/>
-      <c r="M37" s="552" t="n"/>
+    <row r="37" ht="60" customHeight="1" s="1223">
+      <c r="A37" s="747" t="n"/>
+      <c r="D37" s="741" t="n"/>
+      <c r="E37" s="739" t="n"/>
+      <c r="I37" s="741" t="n"/>
+      <c r="M37" s="546" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="539">
+    <row r="38" ht="18" customHeight="1" s="1223">
       <c r="A38" s="70" t="n"/>
       <c r="M38" s="71" t="n"/>
     </row>
-    <row r="39" ht="19.5" customHeight="1" s="539">
-      <c r="A39" s="812" t="inlineStr">
+    <row r="39" ht="19.5" customHeight="1" s="1223">
+      <c r="A39" s="787" t="inlineStr">
         <is>
           <t>05  |  SOPORTE GRÁFICO</t>
         </is>
       </c>
-      <c r="M39" s="761" t="n"/>
+      <c r="M39" s="741" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="12">
-      <c r="A40" s="806" t="inlineStr">
+      <c r="A40" s="783" t="inlineStr">
         <is>
           <t>FOTOGRAFÍA 01</t>
         </is>
       </c>
-      <c r="B40" s="784" t="n"/>
-      <c r="C40" s="784" t="n"/>
-      <c r="D40" s="784" t="n"/>
-      <c r="E40" s="784" t="n"/>
-      <c r="F40" s="784" t="n"/>
-      <c r="G40" s="785" t="n"/>
-      <c r="H40" s="819" t="inlineStr">
+      <c r="B40" s="761" t="n"/>
+      <c r="C40" s="761" t="n"/>
+      <c r="D40" s="761" t="n"/>
+      <c r="E40" s="761" t="n"/>
+      <c r="F40" s="761" t="n"/>
+      <c r="G40" s="762" t="n"/>
+      <c r="H40" s="791" t="inlineStr">
         <is>
           <t>FOTOGRAFÍA 02</t>
         </is>
       </c>
-      <c r="I40" s="784" t="n"/>
-      <c r="J40" s="784" t="n"/>
-      <c r="K40" s="784" t="n"/>
-      <c r="L40" s="784" t="n"/>
-      <c r="M40" s="785" t="n"/>
+      <c r="I40" s="761" t="n"/>
+      <c r="J40" s="761" t="n"/>
+      <c r="K40" s="761" t="n"/>
+      <c r="L40" s="761" t="n"/>
+      <c r="M40" s="762" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="539">
-      <c r="A41" s="820" t="inlineStr">
+    <row r="41" ht="18" customHeight="1" s="1223">
+      <c r="A41" s="792" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="B41" s="757" t="n"/>
-      <c r="C41" s="757" t="n"/>
-      <c r="D41" s="757" t="n"/>
-      <c r="E41" s="757" t="n"/>
-      <c r="F41" s="757" t="n"/>
-      <c r="G41" s="758" t="n"/>
-      <c r="H41" s="756" t="inlineStr">
+      <c r="B41" s="737" t="n"/>
+      <c r="C41" s="737" t="n"/>
+      <c r="D41" s="737" t="n"/>
+      <c r="E41" s="737" t="n"/>
+      <c r="F41" s="737" t="n"/>
+      <c r="G41" s="738" t="n"/>
+      <c r="H41" s="736" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="I41" s="757" t="n"/>
-      <c r="J41" s="757" t="n"/>
-      <c r="K41" s="757" t="n"/>
-      <c r="L41" s="757" t="n"/>
-      <c r="M41" s="758" t="n"/>
+      <c r="I41" s="737" t="n"/>
+      <c r="J41" s="737" t="n"/>
+      <c r="K41" s="737" t="n"/>
+      <c r="L41" s="737" t="n"/>
+      <c r="M41" s="738" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="539">
-      <c r="A42" s="767" t="n"/>
-      <c r="G42" s="761" t="n"/>
-      <c r="H42" s="759" t="n"/>
-      <c r="M42" s="761" t="n"/>
+    <row r="42" ht="18" customHeight="1" s="1223">
+      <c r="A42" s="747" t="n"/>
+      <c r="G42" s="741" t="n"/>
+      <c r="H42" s="739" t="n"/>
+      <c r="M42" s="741" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="539">
-      <c r="A43" s="767" t="n"/>
-      <c r="G43" s="761" t="n"/>
-      <c r="H43" s="759" t="n"/>
-      <c r="M43" s="761" t="n"/>
+    <row r="43" ht="18" customHeight="1" s="1223">
+      <c r="A43" s="747" t="n"/>
+      <c r="G43" s="741" t="n"/>
+      <c r="H43" s="739" t="n"/>
+      <c r="M43" s="741" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="539">
-      <c r="A44" s="767" t="n"/>
-      <c r="G44" s="761" t="n"/>
-      <c r="H44" s="759" t="n"/>
-      <c r="M44" s="761" t="n"/>
+    <row r="44" ht="18" customHeight="1" s="1223">
+      <c r="A44" s="747" t="n"/>
+      <c r="G44" s="741" t="n"/>
+      <c r="H44" s="739" t="n"/>
+      <c r="M44" s="741" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="539">
-      <c r="A45" s="767" t="n"/>
-      <c r="G45" s="761" t="n"/>
-      <c r="H45" s="759" t="n"/>
-      <c r="M45" s="761" t="n"/>
+    <row r="45" ht="18" customHeight="1" s="1223">
+      <c r="A45" s="747" t="n"/>
+      <c r="G45" s="741" t="n"/>
+      <c r="H45" s="739" t="n"/>
+      <c r="M45" s="741" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1" s="539">
-      <c r="A46" s="767" t="n"/>
-      <c r="G46" s="761" t="n"/>
-      <c r="H46" s="759" t="n"/>
-      <c r="M46" s="761" t="n"/>
+    <row r="46" ht="18" customHeight="1" s="1223">
+      <c r="A46" s="747" t="n"/>
+      <c r="G46" s="741" t="n"/>
+      <c r="H46" s="739" t="n"/>
+      <c r="M46" s="741" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1" s="539">
-      <c r="A47" s="767" t="n"/>
-      <c r="G47" s="761" t="n"/>
-      <c r="H47" s="759" t="n"/>
-      <c r="M47" s="761" t="n"/>
+    <row r="47" ht="18" customHeight="1" s="1223">
+      <c r="A47" s="747" t="n"/>
+      <c r="G47" s="741" t="n"/>
+      <c r="H47" s="739" t="n"/>
+      <c r="M47" s="741" t="n"/>
     </row>
-    <row r="48" ht="18" customHeight="1" s="539">
-      <c r="A48" s="767" t="n"/>
-      <c r="G48" s="761" t="n"/>
-      <c r="H48" s="759" t="n"/>
-      <c r="M48" s="761" t="n"/>
+    <row r="48" ht="18" customHeight="1" s="1223">
+      <c r="A48" s="747" t="n"/>
+      <c r="G48" s="741" t="n"/>
+      <c r="H48" s="739" t="n"/>
+      <c r="M48" s="741" t="n"/>
     </row>
-    <row r="49" ht="18" customHeight="1" s="539">
-      <c r="A49" s="767" t="n"/>
-      <c r="G49" s="761" t="n"/>
-      <c r="H49" s="759" t="n"/>
-      <c r="M49" s="761" t="n"/>
+    <row r="49" ht="18" customHeight="1" s="1223">
+      <c r="A49" s="747" t="n"/>
+      <c r="G49" s="741" t="n"/>
+      <c r="H49" s="739" t="n"/>
+      <c r="M49" s="741" t="n"/>
     </row>
-    <row r="50" ht="18" customHeight="1" s="539">
-      <c r="A50" s="767" t="n"/>
-      <c r="G50" s="761" t="n"/>
-      <c r="H50" s="759" t="n"/>
-      <c r="M50" s="761" t="n"/>
+    <row r="50" ht="18" customHeight="1" s="1223">
+      <c r="A50" s="747" t="n"/>
+      <c r="G50" s="741" t="n"/>
+      <c r="H50" s="739" t="n"/>
+      <c r="M50" s="741" t="n"/>
     </row>
-    <row r="51" ht="18" customHeight="1" s="539">
-      <c r="A51" s="767" t="n"/>
-      <c r="G51" s="761" t="n"/>
-      <c r="H51" s="759" t="n"/>
-      <c r="M51" s="761" t="n"/>
+    <row r="51" ht="18" customHeight="1" s="1223">
+      <c r="A51" s="747" t="n"/>
+      <c r="G51" s="741" t="n"/>
+      <c r="H51" s="739" t="n"/>
+      <c r="M51" s="741" t="n"/>
     </row>
-    <row r="52" ht="18" customHeight="1" s="539">
-      <c r="A52" s="767" t="n"/>
-      <c r="G52" s="761" t="n"/>
-      <c r="H52" s="759" t="n"/>
-      <c r="M52" s="761" t="n"/>
+    <row r="52" ht="18" customHeight="1" s="1223">
+      <c r="A52" s="747" t="n"/>
+      <c r="G52" s="741" t="n"/>
+      <c r="H52" s="739" t="n"/>
+      <c r="M52" s="741" t="n"/>
     </row>
-    <row r="53" ht="18" customHeight="1" s="539">
-      <c r="A53" s="767" t="n"/>
-      <c r="G53" s="761" t="n"/>
-      <c r="H53" s="759" t="n"/>
-      <c r="M53" s="761" t="n"/>
+    <row r="53" ht="18" customHeight="1" s="1223">
+      <c r="A53" s="747" t="n"/>
+      <c r="G53" s="741" t="n"/>
+      <c r="H53" s="739" t="n"/>
+      <c r="M53" s="741" t="n"/>
     </row>
-    <row r="54" ht="18" customHeight="1" s="539">
-      <c r="A54" s="767" t="n"/>
-      <c r="G54" s="761" t="n"/>
-      <c r="H54" s="759" t="n"/>
-      <c r="M54" s="761" t="n"/>
+    <row r="54" ht="18" customHeight="1" s="1223">
+      <c r="A54" s="747" t="n"/>
+      <c r="G54" s="741" t="n"/>
+      <c r="H54" s="739" t="n"/>
+      <c r="M54" s="741" t="n"/>
     </row>
-    <row r="55" ht="18" customHeight="1" s="539">
-      <c r="A55" s="767" t="n"/>
-      <c r="G55" s="761" t="n"/>
-      <c r="H55" s="759" t="n"/>
-      <c r="M55" s="761" t="n"/>
+    <row r="55" ht="18" customHeight="1" s="1223">
+      <c r="A55" s="747" t="n"/>
+      <c r="G55" s="741" t="n"/>
+      <c r="H55" s="739" t="n"/>
+      <c r="M55" s="741" t="n"/>
     </row>
-    <row r="56" ht="18" customHeight="1" s="539">
-      <c r="A56" s="779" t="n"/>
-      <c r="B56" s="763" t="n"/>
-      <c r="C56" s="763" t="n"/>
-      <c r="D56" s="763" t="n"/>
-      <c r="E56" s="763" t="n"/>
-      <c r="F56" s="763" t="n"/>
-      <c r="G56" s="764" t="n"/>
-      <c r="H56" s="762" t="n"/>
-      <c r="I56" s="763" t="n"/>
-      <c r="J56" s="763" t="n"/>
-      <c r="K56" s="763" t="n"/>
-      <c r="L56" s="763" t="n"/>
-      <c r="M56" s="764" t="n"/>
+    <row r="56" ht="18" customHeight="1" s="1223">
+      <c r="A56" s="756" t="n"/>
+      <c r="B56" s="743" t="n"/>
+      <c r="C56" s="743" t="n"/>
+      <c r="D56" s="743" t="n"/>
+      <c r="E56" s="743" t="n"/>
+      <c r="F56" s="743" t="n"/>
+      <c r="G56" s="744" t="n"/>
+      <c r="H56" s="742" t="n"/>
+      <c r="I56" s="743" t="n"/>
+      <c r="J56" s="743" t="n"/>
+      <c r="K56" s="743" t="n"/>
+      <c r="L56" s="743" t="n"/>
+      <c r="M56" s="744" t="n"/>
     </row>
-    <row r="57" ht="18" customHeight="1" s="539">
-      <c r="A57" s="788" t="inlineStr">
+    <row r="57" ht="18" customHeight="1" s="1223">
+      <c r="A57" s="765" t="inlineStr">
         <is>
           <t>Pie de foto / fecha / ubicación: ____________________</t>
         </is>
       </c>
-      <c r="B57" s="784" t="n"/>
-      <c r="C57" s="784" t="n"/>
-      <c r="D57" s="784" t="n"/>
-      <c r="E57" s="784" t="n"/>
-      <c r="F57" s="784" t="n"/>
-      <c r="G57" s="785" t="n"/>
-      <c r="H57" s="809" t="inlineStr">
+      <c r="B57" s="761" t="n"/>
+      <c r="C57" s="761" t="n"/>
+      <c r="D57" s="761" t="n"/>
+      <c r="E57" s="761" t="n"/>
+      <c r="F57" s="761" t="n"/>
+      <c r="G57" s="762" t="n"/>
+      <c r="H57" s="785" t="inlineStr">
         <is>
           <t>Pie de foto / fecha / ubicación: ____________________</t>
         </is>
       </c>
-      <c r="I57" s="784" t="n"/>
-      <c r="J57" s="784" t="n"/>
-      <c r="K57" s="784" t="n"/>
-      <c r="L57" s="784" t="n"/>
-      <c r="M57" s="785" t="n"/>
+      <c r="I57" s="761" t="n"/>
+      <c r="J57" s="761" t="n"/>
+      <c r="K57" s="761" t="n"/>
+      <c r="L57" s="761" t="n"/>
+      <c r="M57" s="762" t="n"/>
     </row>
     <row r="58" ht="18" customFormat="1" customHeight="1" s="12">
-      <c r="A58" s="806" t="inlineStr">
+      <c r="A58" s="783" t="inlineStr">
         <is>
           <t>FOTOGRAFÍA 03</t>
         </is>
       </c>
-      <c r="B58" s="784" t="n"/>
-      <c r="C58" s="784" t="n"/>
-      <c r="D58" s="784" t="n"/>
-      <c r="E58" s="784" t="n"/>
-      <c r="F58" s="784" t="n"/>
-      <c r="G58" s="785" t="n"/>
-      <c r="H58" s="819" t="inlineStr">
+      <c r="B58" s="761" t="n"/>
+      <c r="C58" s="761" t="n"/>
+      <c r="D58" s="761" t="n"/>
+      <c r="E58" s="761" t="n"/>
+      <c r="F58" s="761" t="n"/>
+      <c r="G58" s="762" t="n"/>
+      <c r="H58" s="791" t="inlineStr">
         <is>
           <t>FOTOGRAFÍA 04</t>
         </is>
       </c>
-      <c r="I58" s="784" t="n"/>
-      <c r="J58" s="784" t="n"/>
-      <c r="K58" s="784" t="n"/>
-      <c r="L58" s="784" t="n"/>
-      <c r="M58" s="785" t="n"/>
+      <c r="I58" s="761" t="n"/>
+      <c r="J58" s="761" t="n"/>
+      <c r="K58" s="761" t="n"/>
+      <c r="L58" s="761" t="n"/>
+      <c r="M58" s="762" t="n"/>
     </row>
-    <row r="59" ht="18" customHeight="1" s="539">
-      <c r="A59" s="820" t="inlineStr">
+    <row r="59" ht="18" customHeight="1" s="1223">
+      <c r="A59" s="792" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="B59" s="757" t="n"/>
-      <c r="C59" s="757" t="n"/>
-      <c r="D59" s="757" t="n"/>
-      <c r="E59" s="757" t="n"/>
-      <c r="F59" s="757" t="n"/>
-      <c r="G59" s="758" t="n"/>
-      <c r="H59" s="756" t="inlineStr">
+      <c r="B59" s="737" t="n"/>
+      <c r="C59" s="737" t="n"/>
+      <c r="D59" s="737" t="n"/>
+      <c r="E59" s="737" t="n"/>
+      <c r="F59" s="737" t="n"/>
+      <c r="G59" s="738" t="n"/>
+      <c r="H59" s="736" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="I59" s="757" t="n"/>
-      <c r="J59" s="757" t="n"/>
-      <c r="K59" s="757" t="n"/>
-      <c r="L59" s="757" t="n"/>
-      <c r="M59" s="758" t="n"/>
+      <c r="I59" s="737" t="n"/>
+      <c r="J59" s="737" t="n"/>
+      <c r="K59" s="737" t="n"/>
+      <c r="L59" s="737" t="n"/>
+      <c r="M59" s="738" t="n"/>
     </row>
-    <row r="60" ht="18" customHeight="1" s="539">
-      <c r="A60" s="767" t="n"/>
-      <c r="G60" s="761" t="n"/>
-      <c r="H60" s="759" t="n"/>
-      <c r="M60" s="761" t="n"/>
+    <row r="60" ht="18" customHeight="1" s="1223">
+      <c r="A60" s="747" t="n"/>
+      <c r="G60" s="741" t="n"/>
+      <c r="H60" s="739" t="n"/>
+      <c r="M60" s="741" t="n"/>
     </row>
-    <row r="61" ht="18" customHeight="1" s="539">
-      <c r="A61" s="767" t="n"/>
-      <c r="G61" s="761" t="n"/>
-      <c r="H61" s="759" t="n"/>
-      <c r="M61" s="761" t="n"/>
+    <row r="61" ht="18" customHeight="1" s="1223">
+      <c r="A61" s="747" t="n"/>
+      <c r="G61" s="741" t="n"/>
+      <c r="H61" s="739" t="n"/>
+      <c r="M61" s="741" t="n"/>
     </row>
-    <row r="62" ht="18" customHeight="1" s="539">
-      <c r="A62" s="767" t="n"/>
-      <c r="G62" s="761" t="n"/>
-      <c r="H62" s="759" t="n"/>
-      <c r="M62" s="761" t="n"/>
+    <row r="62" ht="18" customHeight="1" s="1223">
+      <c r="A62" s="747" t="n"/>
+      <c r="G62" s="741" t="n"/>
+      <c r="H62" s="739" t="n"/>
+      <c r="M62" s="741" t="n"/>
     </row>
-    <row r="63" ht="18" customHeight="1" s="539">
-      <c r="A63" s="767" t="n"/>
-      <c r="G63" s="761" t="n"/>
-      <c r="H63" s="759" t="n"/>
-      <c r="M63" s="761" t="n"/>
+    <row r="63" ht="18" customHeight="1" s="1223">
+      <c r="A63" s="747" t="n"/>
+      <c r="G63" s="741" t="n"/>
+      <c r="H63" s="739" t="n"/>
+      <c r="M63" s="741" t="n"/>
     </row>
-    <row r="64" ht="18" customHeight="1" s="539">
-      <c r="A64" s="767" t="n"/>
-      <c r="G64" s="761" t="n"/>
-      <c r="H64" s="759" t="n"/>
-      <c r="M64" s="761" t="n"/>
+    <row r="64" ht="18" customHeight="1" s="1223">
+      <c r="A64" s="747" t="n"/>
+      <c r="G64" s="741" t="n"/>
+      <c r="H64" s="739" t="n"/>
+      <c r="M64" s="741" t="n"/>
     </row>
-    <row r="65" ht="18" customHeight="1" s="539">
-      <c r="A65" s="767" t="n"/>
-      <c r="G65" s="761" t="n"/>
-      <c r="H65" s="759" t="n"/>
-      <c r="M65" s="761" t="n"/>
+    <row r="65" ht="18" customHeight="1" s="1223">
+      <c r="A65" s="747" t="n"/>
+      <c r="G65" s="741" t="n"/>
+      <c r="H65" s="739" t="n"/>
+      <c r="M65" s="741" t="n"/>
     </row>
-    <row r="66" ht="18" customHeight="1" s="539">
-      <c r="A66" s="767" t="n"/>
-      <c r="G66" s="761" t="n"/>
-      <c r="H66" s="759" t="n"/>
-      <c r="M66" s="761" t="n"/>
+    <row r="66" ht="18" customHeight="1" s="1223">
+      <c r="A66" s="747" t="n"/>
+      <c r="G66" s="741" t="n"/>
+      <c r="H66" s="739" t="n"/>
+      <c r="M66" s="741" t="n"/>
     </row>
-    <row r="67" ht="18" customHeight="1" s="539">
-      <c r="A67" s="767" t="n"/>
-      <c r="G67" s="761" t="n"/>
-      <c r="H67" s="759" t="n"/>
-      <c r="M67" s="761" t="n"/>
+    <row r="67" ht="18" customHeight="1" s="1223">
+      <c r="A67" s="747" t="n"/>
+      <c r="G67" s="741" t="n"/>
+      <c r="H67" s="739" t="n"/>
+      <c r="M67" s="741" t="n"/>
     </row>
-    <row r="68" ht="18" customHeight="1" s="539">
-      <c r="A68" s="767" t="n"/>
-      <c r="G68" s="761" t="n"/>
-      <c r="H68" s="759" t="n"/>
-      <c r="M68" s="761" t="n"/>
+    <row r="68" ht="18" customHeight="1" s="1223">
+      <c r="A68" s="747" t="n"/>
+      <c r="G68" s="741" t="n"/>
+      <c r="H68" s="739" t="n"/>
+      <c r="M68" s="741" t="n"/>
     </row>
-    <row r="69" ht="18" customHeight="1" s="539">
-      <c r="A69" s="767" t="n"/>
-      <c r="G69" s="761" t="n"/>
-      <c r="H69" s="759" t="n"/>
-      <c r="M69" s="761" t="n"/>
+    <row r="69" ht="18" customHeight="1" s="1223">
+      <c r="A69" s="747" t="n"/>
+      <c r="G69" s="741" t="n"/>
+      <c r="H69" s="739" t="n"/>
+      <c r="M69" s="741" t="n"/>
     </row>
-    <row r="70" ht="18" customHeight="1" s="539">
-      <c r="A70" s="767" t="n"/>
-      <c r="G70" s="761" t="n"/>
-      <c r="H70" s="759" t="n"/>
-      <c r="M70" s="761" t="n"/>
+    <row r="70" ht="18" customHeight="1" s="1223">
+      <c r="A70" s="747" t="n"/>
+      <c r="G70" s="741" t="n"/>
+      <c r="H70" s="739" t="n"/>
+      <c r="M70" s="741" t="n"/>
     </row>
-    <row r="71" ht="18" customHeight="1" s="539">
-      <c r="A71" s="767" t="n"/>
-      <c r="G71" s="761" t="n"/>
-      <c r="H71" s="759" t="n"/>
-      <c r="M71" s="761" t="n"/>
+    <row r="71" ht="18" customHeight="1" s="1223">
+      <c r="A71" s="747" t="n"/>
+      <c r="G71" s="741" t="n"/>
+      <c r="H71" s="739" t="n"/>
+      <c r="M71" s="741" t="n"/>
     </row>
-    <row r="72" ht="18" customHeight="1" s="539">
-      <c r="A72" s="767" t="n"/>
-      <c r="G72" s="761" t="n"/>
-      <c r="H72" s="759" t="n"/>
-      <c r="M72" s="761" t="n"/>
+    <row r="72" ht="18" customHeight="1" s="1223">
+      <c r="A72" s="747" t="n"/>
+      <c r="G72" s="741" t="n"/>
+      <c r="H72" s="739" t="n"/>
+      <c r="M72" s="741" t="n"/>
     </row>
-    <row r="73" ht="18" customHeight="1" s="539">
-      <c r="A73" s="767" t="n"/>
-      <c r="G73" s="761" t="n"/>
-      <c r="H73" s="759" t="n"/>
-      <c r="M73" s="761" t="n"/>
+    <row r="73" ht="18" customHeight="1" s="1223">
+      <c r="A73" s="747" t="n"/>
+      <c r="G73" s="741" t="n"/>
+      <c r="H73" s="739" t="n"/>
+      <c r="M73" s="741" t="n"/>
     </row>
-    <row r="74" ht="18" customHeight="1" s="539">
-      <c r="A74" s="779" t="n"/>
-      <c r="B74" s="763" t="n"/>
-      <c r="C74" s="763" t="n"/>
-      <c r="D74" s="763" t="n"/>
-      <c r="E74" s="763" t="n"/>
-      <c r="F74" s="763" t="n"/>
-      <c r="G74" s="764" t="n"/>
-      <c r="H74" s="762" t="n"/>
-      <c r="I74" s="763" t="n"/>
-      <c r="J74" s="763" t="n"/>
-      <c r="K74" s="763" t="n"/>
-      <c r="L74" s="763" t="n"/>
-      <c r="M74" s="764" t="n"/>
+    <row r="74" ht="18" customHeight="1" s="1223">
+      <c r="A74" s="756" t="n"/>
+      <c r="B74" s="743" t="n"/>
+      <c r="C74" s="743" t="n"/>
+      <c r="D74" s="743" t="n"/>
+      <c r="E74" s="743" t="n"/>
+      <c r="F74" s="743" t="n"/>
+      <c r="G74" s="744" t="n"/>
+      <c r="H74" s="742" t="n"/>
+      <c r="I74" s="743" t="n"/>
+      <c r="J74" s="743" t="n"/>
+      <c r="K74" s="743" t="n"/>
+      <c r="L74" s="743" t="n"/>
+      <c r="M74" s="744" t="n"/>
     </row>
-    <row r="75" ht="18" customHeight="1" s="539">
-      <c r="A75" s="788" t="inlineStr">
+    <row r="75" ht="18" customHeight="1" s="1223">
+      <c r="A75" s="765" t="inlineStr">
         <is>
           <t>Pie de foto / fecha / ubicación: ____________________</t>
         </is>
       </c>
-      <c r="B75" s="784" t="n"/>
-      <c r="C75" s="784" t="n"/>
-      <c r="D75" s="784" t="n"/>
-      <c r="E75" s="784" t="n"/>
-      <c r="F75" s="784" t="n"/>
-      <c r="G75" s="785" t="n"/>
-      <c r="H75" s="809" t="inlineStr">
+      <c r="B75" s="761" t="n"/>
+      <c r="C75" s="761" t="n"/>
+      <c r="D75" s="761" t="n"/>
+      <c r="E75" s="761" t="n"/>
+      <c r="F75" s="761" t="n"/>
+      <c r="G75" s="762" t="n"/>
+      <c r="H75" s="785" t="inlineStr">
         <is>
           <t>Pie de foto / fecha / ubicación: ____________________</t>
         </is>
       </c>
-      <c r="I75" s="784" t="n"/>
-      <c r="J75" s="784" t="n"/>
-      <c r="K75" s="784" t="n"/>
-      <c r="L75" s="784" t="n"/>
-      <c r="M75" s="785" t="n"/>
+      <c r="I75" s="761" t="n"/>
+      <c r="J75" s="761" t="n"/>
+      <c r="K75" s="761" t="n"/>
+      <c r="L75" s="761" t="n"/>
+      <c r="M75" s="762" t="n"/>
     </row>
-    <row r="76" ht="19.5" customHeight="1" s="539">
-      <c r="A76" s="795" t="inlineStr">
+    <row r="76" ht="19.5" customHeight="1" s="1223">
+      <c r="A76" s="772" t="inlineStr">
         <is>
           <t>06  |  ESQUEMA DE LA ESTRUCTURA / ELEMENTO INTERVENIDO</t>
         </is>
       </c>
-      <c r="M76" s="552" t="n"/>
+      <c r="M76" s="546" t="n"/>
     </row>
-    <row r="77" ht="19.5" customHeight="1" s="539">
-      <c r="A77" s="796" t="inlineStr">
+    <row r="77" ht="19.5" customHeight="1" s="1223">
+      <c r="A77" s="773" t="inlineStr">
         <is>
           <t>INSERTAR AQUÍ ESQUEMA, CROQUIS, DETALLE CONSTRUCTIVO O PLANO
 Indicar ejes, cotas, niveles, espesores, diámetros, longitudes y referencias necesarias para verificar la medición.</t>
         </is>
       </c>
-      <c r="B77" s="757" t="n"/>
-      <c r="C77" s="757" t="n"/>
-      <c r="D77" s="757" t="n"/>
-      <c r="E77" s="757" t="n"/>
-      <c r="F77" s="757" t="n"/>
-      <c r="G77" s="757" t="n"/>
-      <c r="H77" s="757" t="n"/>
-      <c r="I77" s="757" t="n"/>
-      <c r="J77" s="758" t="n"/>
-      <c r="K77" s="839" t="inlineStr">
+      <c r="B77" s="737" t="n"/>
+      <c r="C77" s="737" t="n"/>
+      <c r="D77" s="737" t="n"/>
+      <c r="E77" s="737" t="n"/>
+      <c r="F77" s="737" t="n"/>
+      <c r="G77" s="737" t="n"/>
+      <c r="H77" s="737" t="n"/>
+      <c r="I77" s="737" t="n"/>
+      <c r="J77" s="738" t="n"/>
+      <c r="K77" s="810" t="inlineStr">
         <is>
           <t>REFERENCIAS
 Plano: __________________
@@ -11482,234 +11782,234 @@
 Observación: _____________</t>
         </is>
       </c>
-      <c r="L77" s="757" t="n"/>
-      <c r="M77" s="758" t="n"/>
+      <c r="L77" s="737" t="n"/>
+      <c r="M77" s="738" t="n"/>
     </row>
-    <row r="78" ht="19.5" customHeight="1" s="539">
-      <c r="A78" s="767" t="n"/>
-      <c r="J78" s="761" t="n"/>
-      <c r="K78" s="759" t="n"/>
-      <c r="M78" s="761" t="n"/>
+    <row r="78" ht="19.5" customHeight="1" s="1223">
+      <c r="A78" s="747" t="n"/>
+      <c r="J78" s="741" t="n"/>
+      <c r="K78" s="739" t="n"/>
+      <c r="M78" s="741" t="n"/>
     </row>
-    <row r="79" ht="19.5" customHeight="1" s="539">
-      <c r="A79" s="767" t="n"/>
-      <c r="J79" s="761" t="n"/>
-      <c r="K79" s="759" t="n"/>
-      <c r="M79" s="761" t="n"/>
+    <row r="79" ht="19.5" customHeight="1" s="1223">
+      <c r="A79" s="747" t="n"/>
+      <c r="J79" s="741" t="n"/>
+      <c r="K79" s="739" t="n"/>
+      <c r="M79" s="741" t="n"/>
     </row>
-    <row r="80" ht="19.5" customHeight="1" s="539">
-      <c r="A80" s="767" t="n"/>
-      <c r="J80" s="761" t="n"/>
-      <c r="K80" s="759" t="n"/>
-      <c r="M80" s="761" t="n"/>
+    <row r="80" ht="19.5" customHeight="1" s="1223">
+      <c r="A80" s="747" t="n"/>
+      <c r="J80" s="741" t="n"/>
+      <c r="K80" s="739" t="n"/>
+      <c r="M80" s="741" t="n"/>
     </row>
-    <row r="81" ht="19.5" customHeight="1" s="539">
-      <c r="A81" s="767" t="n"/>
-      <c r="J81" s="761" t="n"/>
-      <c r="K81" s="759" t="n"/>
-      <c r="M81" s="761" t="n"/>
+    <row r="81" ht="19.5" customHeight="1" s="1223">
+      <c r="A81" s="747" t="n"/>
+      <c r="J81" s="741" t="n"/>
+      <c r="K81" s="739" t="n"/>
+      <c r="M81" s="741" t="n"/>
     </row>
-    <row r="82" ht="19.5" customHeight="1" s="539">
-      <c r="A82" s="767" t="n"/>
-      <c r="J82" s="761" t="n"/>
-      <c r="K82" s="759" t="n"/>
-      <c r="M82" s="761" t="n"/>
+    <row r="82" ht="19.5" customHeight="1" s="1223">
+      <c r="A82" s="747" t="n"/>
+      <c r="J82" s="741" t="n"/>
+      <c r="K82" s="739" t="n"/>
+      <c r="M82" s="741" t="n"/>
     </row>
-    <row r="83" ht="18" customHeight="1" s="539">
-      <c r="A83" s="767" t="n"/>
-      <c r="J83" s="761" t="n"/>
-      <c r="K83" s="759" t="n"/>
-      <c r="M83" s="761" t="n"/>
+    <row r="83" ht="18" customHeight="1" s="1223">
+      <c r="A83" s="747" t="n"/>
+      <c r="J83" s="741" t="n"/>
+      <c r="K83" s="739" t="n"/>
+      <c r="M83" s="741" t="n"/>
     </row>
-    <row r="84" ht="18" customHeight="1" s="539">
-      <c r="A84" s="767" t="n"/>
-      <c r="J84" s="761" t="n"/>
-      <c r="K84" s="759" t="n"/>
-      <c r="M84" s="761" t="n"/>
+    <row r="84" ht="18" customHeight="1" s="1223">
+      <c r="A84" s="747" t="n"/>
+      <c r="J84" s="741" t="n"/>
+      <c r="K84" s="739" t="n"/>
+      <c r="M84" s="741" t="n"/>
     </row>
-    <row r="85" ht="18" customHeight="1" s="539">
-      <c r="A85" s="767" t="n"/>
-      <c r="J85" s="761" t="n"/>
-      <c r="K85" s="759" t="n"/>
-      <c r="M85" s="761" t="n"/>
+    <row r="85" ht="18" customHeight="1" s="1223">
+      <c r="A85" s="747" t="n"/>
+      <c r="J85" s="741" t="n"/>
+      <c r="K85" s="739" t="n"/>
+      <c r="M85" s="741" t="n"/>
     </row>
-    <row r="86" ht="18" customHeight="1" s="539">
-      <c r="A86" s="767" t="n"/>
-      <c r="J86" s="761" t="n"/>
-      <c r="K86" s="759" t="n"/>
-      <c r="M86" s="761" t="n"/>
+    <row r="86" ht="18" customHeight="1" s="1223">
+      <c r="A86" s="747" t="n"/>
+      <c r="J86" s="741" t="n"/>
+      <c r="K86" s="739" t="n"/>
+      <c r="M86" s="741" t="n"/>
     </row>
-    <row r="87" ht="18" customHeight="1" s="539">
-      <c r="A87" s="767" t="n"/>
-      <c r="J87" s="761" t="n"/>
-      <c r="K87" s="759" t="n"/>
-      <c r="M87" s="761" t="n"/>
+    <row r="87" ht="18" customHeight="1" s="1223">
+      <c r="A87" s="747" t="n"/>
+      <c r="J87" s="741" t="n"/>
+      <c r="K87" s="739" t="n"/>
+      <c r="M87" s="741" t="n"/>
     </row>
-    <row r="88" ht="18" customHeight="1" s="539">
-      <c r="A88" s="767" t="n"/>
-      <c r="J88" s="761" t="n"/>
-      <c r="K88" s="759" t="n"/>
-      <c r="M88" s="761" t="n"/>
+    <row r="88" ht="18" customHeight="1" s="1223">
+      <c r="A88" s="747" t="n"/>
+      <c r="J88" s="741" t="n"/>
+      <c r="K88" s="739" t="n"/>
+      <c r="M88" s="741" t="n"/>
     </row>
-    <row r="89" ht="18" customHeight="1" s="539">
-      <c r="A89" s="767" t="n"/>
-      <c r="J89" s="761" t="n"/>
-      <c r="K89" s="759" t="n"/>
-      <c r="M89" s="761" t="n"/>
+    <row r="89" ht="18" customHeight="1" s="1223">
+      <c r="A89" s="747" t="n"/>
+      <c r="J89" s="741" t="n"/>
+      <c r="K89" s="739" t="n"/>
+      <c r="M89" s="741" t="n"/>
     </row>
-    <row r="90" ht="18" customHeight="1" s="539">
-      <c r="A90" s="767" t="n"/>
-      <c r="J90" s="761" t="n"/>
-      <c r="K90" s="759" t="n"/>
-      <c r="M90" s="761" t="n"/>
+    <row r="90" ht="18" customHeight="1" s="1223">
+      <c r="A90" s="747" t="n"/>
+      <c r="J90" s="741" t="n"/>
+      <c r="K90" s="739" t="n"/>
+      <c r="M90" s="741" t="n"/>
     </row>
-    <row r="91" ht="18" customHeight="1" s="539">
-      <c r="A91" s="767" t="n"/>
-      <c r="J91" s="761" t="n"/>
-      <c r="K91" s="759" t="n"/>
-      <c r="M91" s="761" t="n"/>
+    <row r="91" ht="18" customHeight="1" s="1223">
+      <c r="A91" s="747" t="n"/>
+      <c r="J91" s="741" t="n"/>
+      <c r="K91" s="739" t="n"/>
+      <c r="M91" s="741" t="n"/>
     </row>
-    <row r="92" ht="18" customHeight="1" s="539">
-      <c r="A92" s="767" t="n"/>
-      <c r="J92" s="761" t="n"/>
-      <c r="K92" s="759" t="n"/>
-      <c r="M92" s="761" t="n"/>
+    <row r="92" ht="18" customHeight="1" s="1223">
+      <c r="A92" s="747" t="n"/>
+      <c r="J92" s="741" t="n"/>
+      <c r="K92" s="739" t="n"/>
+      <c r="M92" s="741" t="n"/>
     </row>
-    <row r="93" ht="18" customHeight="1" s="539">
-      <c r="A93" s="779" t="n"/>
-      <c r="B93" s="763" t="n"/>
-      <c r="C93" s="763" t="n"/>
-      <c r="D93" s="763" t="n"/>
-      <c r="E93" s="763" t="n"/>
-      <c r="F93" s="763" t="n"/>
-      <c r="G93" s="763" t="n"/>
-      <c r="H93" s="763" t="n"/>
-      <c r="I93" s="763" t="n"/>
-      <c r="J93" s="764" t="n"/>
-      <c r="K93" s="762" t="n"/>
-      <c r="L93" s="763" t="n"/>
-      <c r="M93" s="764" t="n"/>
+    <row r="93" ht="18" customHeight="1" s="1223">
+      <c r="A93" s="756" t="n"/>
+      <c r="B93" s="743" t="n"/>
+      <c r="C93" s="743" t="n"/>
+      <c r="D93" s="743" t="n"/>
+      <c r="E93" s="743" t="n"/>
+      <c r="F93" s="743" t="n"/>
+      <c r="G93" s="743" t="n"/>
+      <c r="H93" s="743" t="n"/>
+      <c r="I93" s="743" t="n"/>
+      <c r="J93" s="744" t="n"/>
+      <c r="K93" s="742" t="n"/>
+      <c r="L93" s="743" t="n"/>
+      <c r="M93" s="744" t="n"/>
     </row>
-    <row r="94" ht="19.5" customHeight="1" s="539">
-      <c r="A94" s="795" t="inlineStr">
+    <row r="94" ht="19.5" customHeight="1" s="1223">
+      <c r="A94" s="772" t="inlineStr">
         <is>
           <t>07  |  RESPONSABLES Y TRAZABILIDAD</t>
         </is>
       </c>
-      <c r="M94" s="552" t="n"/>
+      <c r="M94" s="546" t="n"/>
     </row>
-    <row r="95" ht="18" customHeight="1" s="539">
-      <c r="A95" s="838" t="inlineStr">
+    <row r="95" ht="18" customHeight="1" s="1223">
+      <c r="A95" s="809" t="inlineStr">
         <is>
           <t>ELABORÓ</t>
         </is>
       </c>
-      <c r="B95" s="784" t="n"/>
-      <c r="C95" s="784" t="n"/>
-      <c r="D95" s="785" t="n"/>
-      <c r="E95" s="824" t="inlineStr">
+      <c r="B95" s="761" t="n"/>
+      <c r="C95" s="761" t="n"/>
+      <c r="D95" s="762" t="n"/>
+      <c r="E95" s="796" t="inlineStr">
         <is>
           <t>REVISÓ</t>
         </is>
       </c>
-      <c r="F95" s="784" t="n"/>
-      <c r="G95" s="784" t="n"/>
-      <c r="H95" s="784" t="n"/>
-      <c r="I95" s="825" t="inlineStr">
+      <c r="F95" s="761" t="n"/>
+      <c r="G95" s="761" t="n"/>
+      <c r="H95" s="761" t="n"/>
+      <c r="I95" s="797" t="inlineStr">
         <is>
           <t>APROBÓ</t>
         </is>
       </c>
-      <c r="J95" s="817" t="n"/>
-      <c r="K95" s="817" t="n"/>
-      <c r="L95" s="817" t="n"/>
-      <c r="M95" s="826" t="n"/>
+      <c r="J95" s="790" t="n"/>
+      <c r="K95" s="790" t="n"/>
+      <c r="L95" s="790" t="n"/>
+      <c r="M95" s="798" t="n"/>
     </row>
-    <row r="96" ht="18" customHeight="1" s="539">
+    <row r="96" ht="18" customHeight="1" s="1223">
       <c r="A96" s="75" t="n"/>
-      <c r="B96" s="832" t="n"/>
-      <c r="C96" s="757" t="n"/>
-      <c r="D96" s="758" t="n"/>
-      <c r="E96" s="792" t="n"/>
-      <c r="F96" s="757" t="n"/>
-      <c r="G96" s="757" t="n"/>
-      <c r="H96" s="793" t="n"/>
-      <c r="I96" s="799" t="n"/>
-      <c r="J96" s="800" t="n"/>
-      <c r="K96" s="800" t="n"/>
-      <c r="L96" s="800" t="n"/>
-      <c r="M96" s="801" t="n"/>
+      <c r="B96" s="803" t="n"/>
+      <c r="C96" s="737" t="n"/>
+      <c r="D96" s="738" t="n"/>
+      <c r="E96" s="769" t="n"/>
+      <c r="F96" s="737" t="n"/>
+      <c r="G96" s="737" t="n"/>
+      <c r="H96" s="770" t="n"/>
+      <c r="I96" s="776" t="n"/>
+      <c r="J96" s="777" t="n"/>
+      <c r="K96" s="777" t="n"/>
+      <c r="L96" s="777" t="n"/>
+      <c r="M96" s="778" t="n"/>
     </row>
-    <row r="97" ht="18" customHeight="1" s="539">
+    <row r="97" ht="18" customHeight="1" s="1223">
       <c r="A97" s="75" t="n"/>
-      <c r="B97" s="763" t="n"/>
-      <c r="C97" s="763" t="n"/>
-      <c r="D97" s="764" t="n"/>
-      <c r="E97" s="762" t="n"/>
-      <c r="F97" s="763" t="n"/>
-      <c r="G97" s="763" t="n"/>
-      <c r="H97" s="794" t="n"/>
-      <c r="I97" s="802" t="n"/>
-      <c r="J97" s="803" t="n"/>
-      <c r="K97" s="803" t="n"/>
-      <c r="L97" s="803" t="n"/>
-      <c r="M97" s="804" t="n"/>
+      <c r="B97" s="743" t="n"/>
+      <c r="C97" s="743" t="n"/>
+      <c r="D97" s="744" t="n"/>
+      <c r="E97" s="742" t="n"/>
+      <c r="F97" s="743" t="n"/>
+      <c r="G97" s="743" t="n"/>
+      <c r="H97" s="771" t="n"/>
+      <c r="I97" s="779" t="n"/>
+      <c r="J97" s="780" t="n"/>
+      <c r="K97" s="780" t="n"/>
+      <c r="L97" s="780" t="n"/>
+      <c r="M97" s="781" t="n"/>
     </row>
-    <row r="98" ht="18" customHeight="1" s="539">
-      <c r="A98" s="778" t="inlineStr">
+    <row r="98" ht="18" customHeight="1" s="1223">
+      <c r="A98" s="755" t="inlineStr">
         <is>
           <t>Nombre / cargo / firma</t>
         </is>
       </c>
-      <c r="B98" s="757" t="n"/>
-      <c r="C98" s="757" t="n"/>
-      <c r="D98" s="758" t="n"/>
-      <c r="E98" s="798" t="inlineStr">
+      <c r="B98" s="737" t="n"/>
+      <c r="C98" s="737" t="n"/>
+      <c r="D98" s="738" t="n"/>
+      <c r="E98" s="775" t="inlineStr">
         <is>
           <t>Nombre / cargo / firma</t>
         </is>
       </c>
-      <c r="F98" s="757" t="n"/>
-      <c r="G98" s="757" t="n"/>
-      <c r="H98" s="757" t="n"/>
-      <c r="I98" s="807" t="inlineStr">
+      <c r="F98" s="737" t="n"/>
+      <c r="G98" s="737" t="n"/>
+      <c r="H98" s="737" t="n"/>
+      <c r="I98" s="784" t="inlineStr">
         <is>
           <t>Nombre / cargo / firma</t>
         </is>
       </c>
-      <c r="J98" s="800" t="n"/>
-      <c r="K98" s="800" t="n"/>
-      <c r="L98" s="800" t="n"/>
-      <c r="M98" s="801" t="n"/>
+      <c r="J98" s="777" t="n"/>
+      <c r="K98" s="777" t="n"/>
+      <c r="L98" s="777" t="n"/>
+      <c r="M98" s="778" t="n"/>
     </row>
-    <row r="99" ht="18" customHeight="1" s="539">
-      <c r="A99" s="779" t="n"/>
-      <c r="B99" s="763" t="n"/>
-      <c r="C99" s="763" t="n"/>
-      <c r="D99" s="764" t="n"/>
-      <c r="E99" s="762" t="n"/>
-      <c r="F99" s="763" t="n"/>
-      <c r="G99" s="763" t="n"/>
-      <c r="H99" s="763" t="n"/>
-      <c r="I99" s="802" t="n"/>
-      <c r="J99" s="803" t="n"/>
-      <c r="K99" s="803" t="n"/>
-      <c r="L99" s="803" t="n"/>
-      <c r="M99" s="804" t="n"/>
+    <row r="99" ht="18" customHeight="1" s="1223">
+      <c r="A99" s="756" t="n"/>
+      <c r="B99" s="743" t="n"/>
+      <c r="C99" s="743" t="n"/>
+      <c r="D99" s="744" t="n"/>
+      <c r="E99" s="742" t="n"/>
+      <c r="F99" s="743" t="n"/>
+      <c r="G99" s="743" t="n"/>
+      <c r="H99" s="743" t="n"/>
+      <c r="I99" s="779" t="n"/>
+      <c r="J99" s="780" t="n"/>
+      <c r="K99" s="780" t="n"/>
+      <c r="L99" s="780" t="n"/>
+      <c r="M99" s="781" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="214" t="inlineStr">
+      <c r="A100" s="209" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="M100" s="215">
+      <c r="M100" s="210">
         <f>L5</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="83">
+  <mergeCells count="82">
     <mergeCell ref="H59:M74"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="A36:D37"/>
@@ -11718,7 +12018,6 @@
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="D31:G31"/>
-    <mergeCell ref="A1:C8"/>
     <mergeCell ref="D5:J6"/>
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A98:D99"/>

--- a/public/plantilla-memoria.xlsx
+++ b/public/plantilla-memoria.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -23,8 +23,9 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1227,6 +1228,15 @@
     <font>
       <name val="Calibri"/>
       <color rgb="FF8A8F99"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="008A8F99"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -1679,7 +1689,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6564,6 +6574,20 @@
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6573,7 +6597,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9797,6 +9821,22 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10019,7 +10059,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10215,7 +10255,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10306,7 +10346,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10339,7 +10379,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -10614,7 +10654,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFC9A227"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M100"/>

--- a/public/plantilla-memoria.xlsx
+++ b/public/plantilla-memoria.xlsx
@@ -10401,31 +10401,6 @@
     </a:ln>
   </spPr>
 </chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-memoria.xlsx
+++ b/public/plantilla-memoria.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Memoria de Cálculo" sheetId="1" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria de Cálculo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -1689,7 +1690,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="412">
+  <borders count="413">
     <border>
       <left/>
       <right/>
@@ -6587,6 +6588,20 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9A227"/>
       </bottom>
     </border>
   </borders>
@@ -6597,7 +6612,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1313">
+  <cellXfs count="1317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9838,6 +9853,16 @@
     </xf>
     <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="412" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9970,440 +9995,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10625,13 +10217,13 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFC9A227"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" customWidth="1" style="740" min="1" max="1"/>
@@ -11939,91 +11531,86 @@
       <c r="L95" s="790" t="n"/>
       <c r="M95" s="798" t="n"/>
     </row>
-    <row r="96" ht="18" customHeight="1" s="1223">
-      <c r="A96" s="75" t="n"/>
-      <c r="B96" s="803" t="n"/>
-      <c r="C96" s="737" t="n"/>
-      <c r="D96" s="738" t="n"/>
-      <c r="E96" s="769" t="n"/>
-      <c r="F96" s="737" t="n"/>
-      <c r="G96" s="737" t="n"/>
-      <c r="H96" s="770" t="n"/>
-      <c r="I96" s="776" t="n"/>
-      <c r="J96" s="777" t="n"/>
-      <c r="K96" s="777" t="n"/>
-      <c r="L96" s="777" t="n"/>
-      <c r="M96" s="778" t="n"/>
+    <row r="96">
+      <c r="A96" s="1313" t="n"/>
+      <c r="E96" s="1313" t="n"/>
+      <c r="I96" s="1313" t="n"/>
     </row>
-    <row r="97" ht="18" customHeight="1" s="1223">
-      <c r="A97" s="75" t="n"/>
-      <c r="B97" s="743" t="n"/>
-      <c r="C97" s="743" t="n"/>
-      <c r="D97" s="744" t="n"/>
-      <c r="E97" s="742" t="n"/>
-      <c r="F97" s="743" t="n"/>
-      <c r="G97" s="743" t="n"/>
-      <c r="H97" s="771" t="n"/>
-      <c r="I97" s="779" t="n"/>
-      <c r="J97" s="780" t="n"/>
-      <c r="K97" s="780" t="n"/>
-      <c r="L97" s="780" t="n"/>
-      <c r="M97" s="781" t="n"/>
-    </row>
+    <row r="97"/>
     <row r="98" ht="18" customHeight="1" s="1223">
-      <c r="A98" s="755" t="inlineStr">
-        <is>
-          <t>Nombre / cargo / firma</t>
-        </is>
-      </c>
-      <c r="B98" s="737" t="n"/>
+      <c r="A98" s="75" t="n"/>
+      <c r="B98" s="1314" t="n"/>
       <c r="C98" s="737" t="n"/>
       <c r="D98" s="738" t="n"/>
-      <c r="E98" s="775" t="inlineStr">
-        <is>
-          <t>Nombre / cargo / firma</t>
-        </is>
-      </c>
+      <c r="E98" s="1315" t="n"/>
       <c r="F98" s="737" t="n"/>
       <c r="G98" s="737" t="n"/>
-      <c r="H98" s="737" t="n"/>
-      <c r="I98" s="784" t="inlineStr">
-        <is>
-          <t>Nombre / cargo / firma</t>
-        </is>
-      </c>
+      <c r="H98" s="770" t="n"/>
+      <c r="I98" s="1316" t="n"/>
       <c r="J98" s="777" t="n"/>
       <c r="K98" s="777" t="n"/>
       <c r="L98" s="777" t="n"/>
       <c r="M98" s="778" t="n"/>
     </row>
     <row r="99" ht="18" customHeight="1" s="1223">
-      <c r="A99" s="756" t="n"/>
+      <c r="A99" s="75" t="n"/>
       <c r="B99" s="743" t="n"/>
       <c r="C99" s="743" t="n"/>
       <c r="D99" s="744" t="n"/>
       <c r="E99" s="742" t="n"/>
       <c r="F99" s="743" t="n"/>
       <c r="G99" s="743" t="n"/>
-      <c r="H99" s="743" t="n"/>
+      <c r="H99" s="771" t="n"/>
       <c r="I99" s="779" t="n"/>
       <c r="J99" s="780" t="n"/>
       <c r="K99" s="780" t="n"/>
       <c r="L99" s="780" t="n"/>
       <c r="M99" s="781" t="n"/>
     </row>
-    <row r="100">
-      <c r="A100" s="209" t="inlineStr">
+    <row r="100" ht="18" customHeight="1" s="1223">
+      <c r="A100" s="755" t="n"/>
+      <c r="B100" s="737" t="n"/>
+      <c r="C100" s="737" t="n"/>
+      <c r="D100" s="738" t="n"/>
+      <c r="E100" s="775" t="n"/>
+      <c r="F100" s="737" t="n"/>
+      <c r="G100" s="737" t="n"/>
+      <c r="H100" s="737" t="n"/>
+      <c r="I100" s="784" t="n"/>
+      <c r="J100" s="777" t="n"/>
+      <c r="K100" s="777" t="n"/>
+      <c r="L100" s="777" t="n"/>
+      <c r="M100" s="778" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1" s="1223">
+      <c r="A101" s="756" t="n"/>
+      <c r="B101" s="743" t="n"/>
+      <c r="C101" s="743" t="n"/>
+      <c r="D101" s="744" t="n"/>
+      <c r="E101" s="742" t="n"/>
+      <c r="F101" s="743" t="n"/>
+      <c r="G101" s="743" t="n"/>
+      <c r="H101" s="743" t="n"/>
+      <c r="I101" s="779" t="n"/>
+      <c r="J101" s="780" t="n"/>
+      <c r="K101" s="780" t="n"/>
+      <c r="L101" s="780" t="n"/>
+      <c r="M101" s="781" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="209" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="M100" s="210">
+      <c r="M102" s="210">
         <f>L5</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="82">
+  <mergeCells count="85">
+    <mergeCell ref="I100:M101"/>
     <mergeCell ref="H59:M74"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="A36:D37"/>
@@ -12034,7 +11621,6 @@
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="D5:J6"/>
     <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A98:D99"/>
     <mergeCell ref="H41:M56"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="A11:B11"/>
@@ -12047,6 +11633,7 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="H11:I11"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A96:D97"/>
     <mergeCell ref="A75:G75"/>
     <mergeCell ref="J27:M27"/>
     <mergeCell ref="H12:I12"/>
@@ -12061,8 +11648,8 @@
     <mergeCell ref="A77:J93"/>
     <mergeCell ref="J12:M12"/>
     <mergeCell ref="E98:H99"/>
+    <mergeCell ref="J21:M21"/>
     <mergeCell ref="I96:M97"/>
-    <mergeCell ref="J21:M21"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="D29:G29"/>
     <mergeCell ref="A58:G58"/>
@@ -12077,9 +11664,12 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="A94:M94"/>
+    <mergeCell ref="A100:D101"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="J24:M24"/>
+    <mergeCell ref="B98:D99"/>
+    <mergeCell ref="E100:H101"/>
     <mergeCell ref="J26:M26"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="H40:M40"/>
@@ -12096,7 +11686,6 @@
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="D1:M3"/>
     <mergeCell ref="H57:M57"/>
-    <mergeCell ref="B96:D97"/>
     <mergeCell ref="J36:M37"/>
     <mergeCell ref="A59:G74"/>
     <mergeCell ref="H32:I32"/>

--- a/public/plantilla-memoria.xlsx
+++ b/public/plantilla-memoria.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Memoria de Cálculo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Memoria de Cálculo" sheetId="1" r:id="rId15"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -16,17 +15,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
-    <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
-    <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;$ &quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="\$\ #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="171" formatCode="\$\ #,##0"/>
     <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
-  <fonts count="170">
+  <fonts count="166">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -636,13 +635,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF17365D"/>
-      <sz val="14"/>
-    </font>
-    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
@@ -1150,28 +1142,9 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color rgb="FF17365D"/>
-      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1228,16 +1201,17 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="008A8F99"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -1690,7 +1664,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="413">
+  <borders count="422">
     <border>
       <left/>
       <right/>
@@ -2888,17 +2862,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.3499862666707358"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.3499862666707358"/>
@@ -5821,21 +5784,6 @@
         <color theme="0"/>
       </left>
       <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249946592608417"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
         <color theme="0" tint="-0.249946592608417"/>
       </right>
       <top style="thin">
@@ -6185,12 +6133,121 @@
       <left style="thin">
         <color rgb="FF002060"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
         <color rgb="FF002060"/>
-      </top>
-      <bottom style="thin">
+      </right>
+      <top style="thin">
         <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB7C3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFC9A227"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9A227"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9A227"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFC9A227"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
       </bottom>
       <diagonal/>
     </border>
@@ -6204,6 +6261,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249946592608417"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thick">
         <color rgb="FF17365D"/>
       </left>
@@ -6286,21 +6369,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF002060"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF002060"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF002060"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF002060"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -6341,35 +6409,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="4" tint="0.5998718222602009"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="4" tint="0.5999633777886288"/>
-      </right>
-      <top style="thin">
-        <color theme="4" tint="0.5999633777886288"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4" tint="0.5998718222602009"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color theme="4" tint="0.5999633777886288"/>
@@ -6382,6 +6421,17 @@
     </border>
     <border>
       <left/>
+      <right style="medium">
+        <color theme="4" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFB7C3D0"/>
       </right>
@@ -6392,16 +6442,39 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB7C3D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF002060"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF002060"/>
-      </bottom>
+      <left style="thin">
+        <color theme="4" tint="0.5998718222602009"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.5998718222602009"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC9A227"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFC9A227"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -6577,31 +6650,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB8C2CC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB8C2CC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB8C2CC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB8C2CC"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00C9A227"/>
-      </left>
-      <right style="thin">
-        <color rgb="00C9A227"/>
-      </right>
-      <top style="thin">
-        <color rgb="00C9A227"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00C9A227"/>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
       </bottom>
     </border>
   </borders>
@@ -6612,7 +6679,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1317">
+  <cellXfs count="1446">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -6765,28 +6832,28 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="34" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6805,15 +6872,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="40" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="40" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="40" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -6825,9 +6892,6 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6855,13 +6919,10 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
@@ -6871,7 +6932,7 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6916,15 +6977,15 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="27" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6952,9 +7013,6 @@
     <xf numFmtId="0" fontId="81" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="45" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -6964,21 +7022,21 @@
     <xf numFmtId="0" fontId="9" fillId="43" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="43" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="9" fillId="43" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="54" fillId="48" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -6991,10 +7049,10 @@
     <xf numFmtId="0" fontId="21" fillId="47" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="108" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="36" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7003,58 +7061,58 @@
     <xf numFmtId="0" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="109" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="142" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -7063,46 +7121,46 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="109" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="110" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="111" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="111" fillId="42" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="91" fillId="20" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="20" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="47" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="3" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="28" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -7117,25 +7175,25 @@
     <xf numFmtId="0" fontId="66" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="57" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="57" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="57" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="58" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="84" fillId="58" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="58" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7154,117 +7212,114 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="53" borderId="174" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="53" borderId="167" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="53" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="2" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="127" fillId="55" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="2" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="68" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="69" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="69" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="18" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="242" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="241" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="240" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="60" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7282,15 +7337,15 @@
     <xf numFmtId="0" fontId="59" fillId="18" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="150" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="149" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="69" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7300,34 +7355,34 @@
     <xf numFmtId="4" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="48" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="26" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="101" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="26" borderId="236" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="37" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7335,64 +7390,64 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="154" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="153" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="25" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="73" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="135" fillId="25" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="73" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="17" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="16" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="28" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="74" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="17" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="16" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="74" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="28" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="74" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="17" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="16" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="74" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="17" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="16" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="25" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="25" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -7407,22 +7462,21 @@
     <xf numFmtId="0" fontId="55" fillId="25" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="42" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7430,33 +7484,33 @@
     <xf numFmtId="0" fontId="38" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="42" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="10" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="146" fillId="42" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="10" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="309" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7466,80 +7520,80 @@
     <xf numFmtId="0" fontId="38" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="18" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="25" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="25" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="25" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="59" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="25" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="25" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="103" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -7548,19 +7602,19 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="97" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="342" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="39" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7569,27 +7623,19 @@
     <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="39" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="26" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="16" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="156" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="158" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="343" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7598,37 +7644,25 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="5" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="86" fillId="5" borderId="345" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="85" fillId="5" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="351" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7636,44 +7670,183 @@
     <xf numFmtId="0" fontId="64" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="28" borderId="173" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="25" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="97" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="28" borderId="172" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="164" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="59" fillId="19" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="18" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="25" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="163" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="159" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7683,10 +7856,13 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="72" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -7697,10 +7873,10 @@
     <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7713,23 +7889,29 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="41" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="41" borderId="186" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7769,10 +7951,6 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -7783,337 +7961,294 @@
     <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="164" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="28" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="157" fillId="3" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="155" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="87" fillId="49" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="62" fillId="0" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="55" fillId="20" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="88" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="25" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="25" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="50" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="104" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="70" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="60" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="55" fillId="20" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="128" fillId="70" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="135" fillId="25" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="96" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="28" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="155" fillId="3" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="155" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="154" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="86" fillId="49" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="163" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="123" fillId="17" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="123" fillId="17" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="163" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="16" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="154" fillId="26" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="28" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="25" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="28" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="96" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="127" fillId="55" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="44" fillId="18" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="44" fillId="18" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="59" fillId="19" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="34" fillId="18" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="155" fillId="26" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="98" fillId="28" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="25" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="116" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="28" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="97" fillId="16" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="52" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="162" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="49" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="115" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="28" borderId="161" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="28" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="41" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="53" fillId="41" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="26" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="27" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="160" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="163" fillId="28" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="28" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="352" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="301" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="300" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8123,150 +8258,150 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="52" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="93" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="265" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="250" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="265" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="264" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="264" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="42" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="151" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="237" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="234" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="42" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="132" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="61" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="238" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="152" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="235" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="256" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="133" fillId="71" borderId="156" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="257" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="255" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="241" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="133" fillId="64" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="61" borderId="239" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="134" fillId="71" borderId="157" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="258" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="259" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="242" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="260" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="261" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="43" borderId="234" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="43" borderId="233" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="61" borderId="239" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="66" borderId="250" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="60" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="60" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="282" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="61" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="284" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="28" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="28" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="286" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="142" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="63" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="253" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="254" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="136" fillId="35" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="35" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8277,26 +8412,29 @@
     <xf numFmtId="0" fontId="66" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="25" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="25" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="75" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="238" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="237" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="60" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="62" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8305,29 +8443,41 @@
     <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="128" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="128" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="109" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="193" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="49" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="370" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="371" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="55" fillId="35" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="28" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="194" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8336,49 +8486,45 @@
     <xf numFmtId="0" fontId="66" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="27" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="101" fillId="37" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="62" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="150" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="100" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="20" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="95" fillId="34" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="109" fillId="20" borderId="195" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="20" borderId="196" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="42" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="152" fillId="3" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="99" fillId="52" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="20" borderId="288" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="34" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="20" borderId="194" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="20" borderId="195" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="42" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8390,17 +8536,17 @@
     <xf numFmtId="0" fontId="43" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="3" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="3" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="80" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="81" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8412,17 +8558,17 @@
     <xf numFmtId="0" fontId="73" fillId="38" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="73" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="34" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8434,35 +8580,43 @@
     <xf numFmtId="0" fontId="82" fillId="58" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="66" fillId="25" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="28" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="20" borderId="141" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="107" fillId="28" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="20" borderId="140" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="149" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="7" borderId="144" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="51" borderId="138" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="51" borderId="137" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="199" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8477,50 +8631,54 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="206" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="104" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="120" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="123" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="208" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="207" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="375" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="376" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="378" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="379" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="380" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="118" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center"/>
     </xf>
@@ -8528,72 +8686,81 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="11" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="202" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="122" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="121" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="10" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
@@ -8604,12 +8771,13 @@
     <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="10" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="10" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="77" fillId="40" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8620,181 +8788,181 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="119" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="77" fillId="10" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="26" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="170" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="175" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="26" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="171" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="176" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="41" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="121" fillId="56" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="28" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="355" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="17" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="168" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="56" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="161" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="53" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="28" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="28" borderId="360" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="354" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="211" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="121" fillId="28" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="357" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="17" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="54" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="53" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="28" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="28" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="212" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="41" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="214" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="174" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="171" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="170" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="125" fillId="41" borderId="186" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="179" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="211" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="25" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="53" borderId="210" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="356" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="4"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="209" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="34" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8819,7 +8987,7 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8827,13 +8995,16 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="53" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8846,8 +9017,8 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="88" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="230" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="58" fillId="34" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8857,15 +9028,15 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="89" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8878,29 +9049,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="220" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="3" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="94" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="20" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="231" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="232" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="233" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8915,11 +9086,11 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="107" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="223" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="21" borderId="90" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -8932,14 +9103,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="216" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="219" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="25" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -8961,13 +9132,13 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="224" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="227" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="228" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -8984,20 +9155,20 @@
     <xf numFmtId="0" fontId="42" fillId="21" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="199" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="31" borderId="222" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="71" fillId="31" borderId="221" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -9017,7 +9188,7 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -9039,11 +9210,11 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="218" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="217" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="104" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="103" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="11" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -9075,84 +9246,84 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="226" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="227" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="30" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="54" fillId="30" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="24" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="54" fillId="29" borderId="329" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="29" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="243" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="341" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="29" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="246" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9165,20 +9336,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="49" fillId="3" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="318" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -9188,10 +9359,10 @@
     <xf numFmtId="0" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="242" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -9203,16 +9374,16 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="88" fillId="14" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9222,11 +9393,14 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="15" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -9234,150 +9408,153 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="340" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="66" fillId="20" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="57" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="159" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="38" fillId="16" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="16" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="51" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="51" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="30" borderId="246" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="3" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="51" fillId="16" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="51" fillId="16" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="20" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="245" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="3" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="20" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="89" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="88" fillId="14" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="3" borderId="336" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="3" borderId="335" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="24" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="48" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="87" fillId="24" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="3" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="54" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="47" fillId="16" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="330" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="327" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9386,29 +9563,29 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="367" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="30" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="14" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="27" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9428,16 +9605,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9449,30 +9626,30 @@
     <xf numFmtId="0" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="0" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="14" borderId="325" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="14" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="4" borderId="101" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="15" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="111" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9481,10 +9658,10 @@
     <xf numFmtId="0" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="49" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9494,18 +9671,21 @@
     <xf numFmtId="0" fontId="49" fillId="15" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="30" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="244" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="57" fillId="25" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="243" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="57" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9514,23 +9694,23 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="269" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="268" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="117" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="30" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="30" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -9539,330 +9719,564 @@
     <xf numFmtId="0" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="39" fillId="3" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="105" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="322" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="104" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="3" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="58" fillId="3" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="317" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="270" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="22" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="326" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="368" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="15" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="60" fillId="22" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="22" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="40" fillId="3" borderId="114" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="202" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="98" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="349" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="49" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="49" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="99" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="75" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="75" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="383" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="381" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="96" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="28" borderId="162" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="155" fillId="3" borderId="164" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="155" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="154" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="86" fillId="49" borderId="112" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="48" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="55" fillId="35" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="63" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="63" fillId="26" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="66" fillId="20" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="62" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="55" fillId="20" borderId="155" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="49" fillId="34" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="25" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="50" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="25" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="69" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="100" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="55" fillId="20" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="70" fillId="36" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="6" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="70" fillId="36" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="55" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="44" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="20" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="43" fillId="7" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="374" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="126" fillId="55" borderId="187" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="126" fillId="55" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="28" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="177" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="123" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="123" fillId="54" borderId="180" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="41" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="17" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="26" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="53" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="56" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="54" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="105" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="372" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="252" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="10" borderId="92" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="3" borderId="203" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="49" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="70" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="60" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="53" fillId="23" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="332" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="158" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="16" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="70" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="66" fillId="25" borderId="235" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="251" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="132" fillId="60" borderId="283" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="28" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="252" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="66" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="25" borderId="263" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="262" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="266" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="28" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="48" fillId="17" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="262" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="266" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="97" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="28" borderId="163" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="98" fillId="26" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="157" fillId="3" borderId="165" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="97" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="28" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="157" fillId="3" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="155" fillId="16" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="87" fillId="49" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="38" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="66" borderId="251" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="138" fillId="0" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="138" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="49" borderId="384" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="124" fillId="54" borderId="178" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="124" fillId="54" borderId="181" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="412" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="48" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="44" fillId="18" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="363" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="48" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="59" fillId="19" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="49" fillId="3" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="420" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="65" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="51" fillId="16" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="51" fillId="16" borderId="110" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="16" borderId="334" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="53" fillId="23" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="56" fillId="16" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="3" borderId="113" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="18" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="36" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="57" fillId="19" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="58" fillId="3" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="30" borderId="420" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="421" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="22" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="60" fillId="22" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="60" fillId="22" borderId="106" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="39" fillId="3" borderId="267" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="39" fillId="3" borderId="115" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="96" fillId="17" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="136" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="137" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="137" fillId="0" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="23" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="4" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="4" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9995,7 +10409,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10217,7 +10631,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFC9A227"/>
@@ -10226,263 +10640,263 @@
   <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4" customWidth="1" style="740" min="1" max="1"/>
-    <col width="27" customWidth="1" style="740" min="2" max="2"/>
-    <col width="10" customWidth="1" style="740" min="3" max="4"/>
-    <col width="11.5546875" customWidth="1" style="740" min="5" max="5"/>
-    <col width="12" customWidth="1" style="740" min="6" max="6"/>
-    <col width="10" customWidth="1" style="740" min="7" max="7"/>
-    <col width="15" customWidth="1" style="740" min="8" max="8"/>
-    <col width="10" customWidth="1" style="740" min="9" max="9"/>
-    <col width="22" customWidth="1" style="740" min="10" max="10"/>
-    <col width="11" customWidth="1" style="740" min="11" max="13"/>
-    <col width="8.88671875" customWidth="1" style="740" min="14" max="17"/>
-    <col width="8.88671875" customWidth="1" style="740" min="18" max="16384"/>
+    <col width="4" customWidth="1" style="779" min="1" max="1"/>
+    <col width="27" customWidth="1" style="779" min="2" max="2"/>
+    <col width="10" customWidth="1" style="779" min="3" max="4"/>
+    <col width="11.5546875" customWidth="1" style="779" min="5" max="5"/>
+    <col width="12" customWidth="1" style="779" min="6" max="6"/>
+    <col width="10" customWidth="1" style="779" min="7" max="7"/>
+    <col width="15" customWidth="1" style="779" min="8" max="8"/>
+    <col width="10" customWidth="1" style="779" min="9" max="9"/>
+    <col width="22" customWidth="1" style="779" min="10" max="10"/>
+    <col width="11" customWidth="1" style="779" min="11" max="13"/>
+    <col width="8.88671875" customWidth="1" style="779" min="14" max="18"/>
+    <col width="8.88671875" customWidth="1" style="779" min="19" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="1223">
-      <c r="A1" s="1236" t="n"/>
-      <c r="B1" s="1258" t="n"/>
-      <c r="C1" s="1258" t="n"/>
-      <c r="D1" s="1232" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="550">
+      <c r="A1" s="498" t="n"/>
+      <c r="B1" s="618" t="n"/>
+      <c r="C1" s="618" t="n"/>
+      <c r="D1" s="847" t="inlineStr">
         <is>
           <t xml:space="preserve">MEMORIAS DE CÁLCULO
 </t>
         </is>
       </c>
-      <c r="E1" s="550" t="n"/>
-      <c r="F1" s="550" t="n"/>
-      <c r="G1" s="550" t="n"/>
-      <c r="H1" s="550" t="n"/>
-      <c r="I1" s="550" t="n"/>
-      <c r="J1" s="550" t="n"/>
-      <c r="K1" s="550" t="n"/>
-      <c r="L1" s="550" t="n"/>
-      <c r="M1" s="551" t="n"/>
+      <c r="E1" s="583" t="n"/>
+      <c r="F1" s="583" t="n"/>
+      <c r="G1" s="583" t="n"/>
+      <c r="H1" s="583" t="n"/>
+      <c r="I1" s="583" t="n"/>
+      <c r="J1" s="583" t="n"/>
+      <c r="K1" s="583" t="n"/>
+      <c r="L1" s="583" t="n"/>
+      <c r="M1" s="559" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1" s="1223">
-      <c r="A2" s="1258" t="n"/>
-      <c r="B2" s="1236" t="n"/>
-      <c r="C2" s="1258" t="n"/>
-      <c r="M2" s="546" t="n"/>
+    <row r="2" ht="18" customHeight="1" s="550">
+      <c r="A2" s="618" t="n"/>
+      <c r="B2" s="498" t="n"/>
+      <c r="C2" s="618" t="n"/>
+      <c r="M2" s="562" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1" s="1223">
-      <c r="A3" s="1258" t="n"/>
-      <c r="B3" s="1236" t="n"/>
-      <c r="C3" s="1258" t="n"/>
-      <c r="M3" s="546" t="n"/>
+    <row r="3" ht="18" customHeight="1" s="550">
+      <c r="A3" s="618" t="n"/>
+      <c r="B3" s="498" t="n"/>
+      <c r="C3" s="618" t="n"/>
+      <c r="M3" s="562" t="n"/>
     </row>
-    <row r="4" ht="4.95" customHeight="1" s="1223">
-      <c r="A4" s="1258" t="n"/>
-      <c r="B4" s="1236" t="n"/>
-      <c r="C4" s="1258" t="n"/>
-      <c r="D4" s="1233" t="n"/>
-      <c r="E4" s="1233" t="n"/>
-      <c r="F4" s="1233" t="n"/>
-      <c r="G4" s="1233" t="n"/>
-      <c r="H4" s="1233" t="n"/>
-      <c r="I4" s="1233" t="n"/>
-      <c r="J4" s="1233" t="n"/>
-      <c r="K4" s="1233" t="n"/>
-      <c r="L4" s="1233" t="n"/>
-      <c r="M4" s="128" t="n"/>
+    <row r="4" ht="4.95" customHeight="1" s="550">
+      <c r="A4" s="618" t="n"/>
+      <c r="B4" s="498" t="n"/>
+      <c r="C4" s="618" t="n"/>
+      <c r="D4" s="497" t="n"/>
+      <c r="E4" s="497" t="n"/>
+      <c r="F4" s="497" t="n"/>
+      <c r="G4" s="497" t="n"/>
+      <c r="H4" s="497" t="n"/>
+      <c r="I4" s="497" t="n"/>
+      <c r="J4" s="497" t="n"/>
+      <c r="K4" s="497" t="n"/>
+      <c r="L4" s="497" t="n"/>
+      <c r="M4" s="125" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="1223">
-      <c r="A5" s="1258" t="n"/>
-      <c r="B5" s="1236" t="n"/>
-      <c r="C5" s="1258" t="n"/>
-      <c r="D5" s="1234" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="550">
+      <c r="A5" s="618" t="n"/>
+      <c r="B5" s="498" t="n"/>
+      <c r="C5" s="618" t="n"/>
+      <c r="D5" s="791" t="inlineStr">
         <is>
           <t xml:space="preserve">REFORMAS Y REMODELACIONES                                        </t>
         </is>
       </c>
-      <c r="K5" s="745" t="inlineStr">
+      <c r="K5" s="784" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="L5" s="750" t="inlineStr">
+      <c r="L5" s="789" t="inlineStr">
         <is>
           <t>RYR-MC-001</t>
         </is>
       </c>
-      <c r="M5" s="744" t="n"/>
+      <c r="M5" s="783" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="1223">
-      <c r="A6" s="1258" t="n"/>
-      <c r="B6" s="1236" t="n"/>
-      <c r="C6" s="1258" t="n"/>
-      <c r="K6" s="745" t="inlineStr">
+    <row r="6" ht="18" customHeight="1" s="550">
+      <c r="A6" s="618" t="n"/>
+      <c r="B6" s="498" t="n"/>
+      <c r="C6" s="618" t="n"/>
+      <c r="K6" s="784" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="L6" s="750" t="n">
+      <c r="L6" s="789" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="744" t="n"/>
+      <c r="M6" s="783" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="1223">
-      <c r="A7" s="1258" t="n"/>
-      <c r="B7" s="1236" t="n"/>
-      <c r="C7" s="1258" t="n"/>
-      <c r="D7" s="1235" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="550">
+      <c r="A7" s="618" t="n"/>
+      <c r="B7" s="498" t="n"/>
+      <c r="C7" s="618" t="n"/>
+      <c r="D7" s="834" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
         </is>
       </c>
-      <c r="K7" s="745" t="inlineStr">
+      <c r="K7" s="784" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="L7" s="750" t="inlineStr">
+      <c r="L7" s="789" t="inlineStr">
         <is>
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="M7" s="744" t="n"/>
+      <c r="M7" s="783" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="1223">
-      <c r="A8" s="1237" t="n"/>
-      <c r="B8" s="1237" t="n"/>
-      <c r="C8" s="1237" t="n"/>
-      <c r="D8" s="1238" t="n"/>
-      <c r="E8" s="1238" t="n"/>
-      <c r="F8" s="1238" t="n"/>
-      <c r="G8" s="1238" t="n"/>
-      <c r="H8" s="1238" t="n"/>
-      <c r="I8" s="1238" t="n"/>
-      <c r="J8" s="1238" t="n"/>
-      <c r="K8" s="1239" t="inlineStr">
+    <row r="8" ht="18" customHeight="1" s="550">
+      <c r="A8" s="499" t="n"/>
+      <c r="B8" s="499" t="n"/>
+      <c r="C8" s="499" t="n"/>
+      <c r="D8" s="500" t="n"/>
+      <c r="E8" s="500" t="n"/>
+      <c r="F8" s="500" t="n"/>
+      <c r="G8" s="500" t="n"/>
+      <c r="H8" s="500" t="n"/>
+      <c r="I8" s="500" t="n"/>
+      <c r="J8" s="500" t="n"/>
+      <c r="K8" s="501" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="L8" s="1240" t="inlineStr">
+      <c r="L8" s="827" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
-      <c r="M8" s="741" t="n"/>
+      <c r="M8" s="780" t="n"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1" s="1223">
-      <c r="A9" s="1241" t="inlineStr">
+    <row r="9" ht="19.5" customHeight="1" s="550">
+      <c r="A9" s="824" t="inlineStr">
         <is>
           <t>01  |  IDENTIFICACIÓN DEL PROYECTO Y DE LA ACTIVIDAD</t>
         </is>
       </c>
-      <c r="B9" s="1242" t="n"/>
-      <c r="C9" s="1242" t="n"/>
-      <c r="D9" s="1242" t="n"/>
-      <c r="E9" s="1242" t="n"/>
-      <c r="F9" s="1242" t="n"/>
-      <c r="G9" s="1242" t="n"/>
-      <c r="H9" s="1242" t="n"/>
-      <c r="I9" s="1242" t="n"/>
-      <c r="J9" s="1242" t="n"/>
-      <c r="K9" s="1242" t="n"/>
-      <c r="L9" s="1242" t="n"/>
-      <c r="M9" s="1299" t="n"/>
+      <c r="B9" s="713" t="n"/>
+      <c r="C9" s="713" t="n"/>
+      <c r="D9" s="713" t="n"/>
+      <c r="E9" s="713" t="n"/>
+      <c r="F9" s="713" t="n"/>
+      <c r="G9" s="713" t="n"/>
+      <c r="H9" s="713" t="n"/>
+      <c r="I9" s="713" t="n"/>
+      <c r="J9" s="713" t="n"/>
+      <c r="K9" s="713" t="n"/>
+      <c r="L9" s="713" t="n"/>
+      <c r="M9" s="825" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="1223">
-      <c r="A10" s="757" t="inlineStr">
+    <row r="10" ht="18" customHeight="1" s="550">
+      <c r="A10" s="794" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B10" s="743" t="n"/>
-      <c r="C10" s="786" t="n"/>
-      <c r="H10" s="745" t="inlineStr">
+      <c r="B10" s="782" t="n"/>
+      <c r="C10" s="823" t="n"/>
+      <c r="H10" s="784" t="inlineStr">
         <is>
           <t>Área / Frente</t>
         </is>
       </c>
-      <c r="I10" s="743" t="n"/>
+      <c r="I10" s="782" t="n"/>
       <c r="J10" s="31" t="n"/>
-      <c r="K10" s="745" t="inlineStr">
+      <c r="K10" s="784" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="L10" s="743" t="n"/>
+      <c r="L10" s="782" t="n"/>
       <c r="M10" s="69" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="1223">
-      <c r="A11" s="757" t="inlineStr">
+    <row r="11" ht="18" customHeight="1" s="550">
+      <c r="A11" s="794" t="inlineStr">
         <is>
           <t>Contratante</t>
         </is>
       </c>
-      <c r="B11" s="743" t="n"/>
-      <c r="C11" s="789" t="n"/>
-      <c r="D11" s="790" t="n"/>
-      <c r="E11" s="790" t="n"/>
-      <c r="F11" s="790" t="n"/>
-      <c r="G11" s="790" t="n"/>
-      <c r="H11" s="764" t="inlineStr">
+      <c r="B11" s="782" t="n"/>
+      <c r="C11" s="830" t="n"/>
+      <c r="D11" s="831" t="n"/>
+      <c r="E11" s="831" t="n"/>
+      <c r="F11" s="831" t="n"/>
+      <c r="G11" s="831" t="n"/>
+      <c r="H11" s="801" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="I11" s="761" t="n"/>
+      <c r="I11" s="798" t="n"/>
       <c r="J11" s="32" t="n"/>
-      <c r="K11" s="745" t="inlineStr">
+      <c r="K11" s="784" t="inlineStr">
         <is>
           <t>Memoria No.</t>
         </is>
       </c>
-      <c r="L11" s="743" t="n"/>
+      <c r="L11" s="782" t="n"/>
       <c r="M11" s="69" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="1223">
-      <c r="A12" s="757" t="inlineStr">
+    <row r="12" ht="30" customHeight="1" s="550">
+      <c r="A12" s="794" t="inlineStr">
         <is>
           <t>Actividad / Ítem</t>
         </is>
       </c>
-      <c r="B12" s="743" t="n"/>
-      <c r="C12" s="788" t="inlineStr">
+      <c r="B12" s="782" t="n"/>
+      <c r="C12" s="828" t="inlineStr">
         <is>
           <t>1.3.1</t>
         </is>
       </c>
-      <c r="D12" s="743" t="n"/>
-      <c r="E12" s="745" t="inlineStr">
+      <c r="D12" s="782" t="n"/>
+      <c r="E12" s="784" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="F12" s="800" t="inlineStr">
+      <c r="F12" s="844" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
-      <c r="G12" s="801" t="n"/>
-      <c r="H12" s="768" t="inlineStr">
+      <c r="G12" s="845" t="n"/>
+      <c r="H12" s="811" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="I12" s="761" t="n"/>
-      <c r="J12" s="774" t="n"/>
-      <c r="K12" s="761" t="n"/>
-      <c r="L12" s="761" t="n"/>
-      <c r="M12" s="762" t="n"/>
+      <c r="I12" s="798" t="n"/>
+      <c r="J12" s="815" t="n"/>
+      <c r="K12" s="798" t="n"/>
+      <c r="L12" s="798" t="n"/>
+      <c r="M12" s="799" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="1223">
+    <row r="13" ht="18" customHeight="1" s="550">
       <c r="A13" s="70" t="n"/>
       <c r="M13" s="71" t="n"/>
     </row>
-    <row r="14" ht="19.5" customHeight="1" s="1223" thickBot="1">
-      <c r="A14" s="787" t="inlineStr">
+    <row r="14" ht="19.5" customHeight="1" s="550" thickBot="1">
+      <c r="A14" s="826" t="inlineStr">
         <is>
           <t>02  |  MEDICIÓN DE CAMPO / DATOS DE ENTRADA</t>
         </is>
       </c>
-      <c r="M14" s="741" t="n"/>
+      <c r="M14" s="780" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="1223" thickBot="1">
+    <row r="15" ht="18" customHeight="1" s="550" thickBot="1">
       <c r="A15" s="76" t="inlineStr">
         <is>
           <t>N°</t>
@@ -10528,26 +10942,26 @@
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="J15" s="805" t="inlineStr">
+      <c r="J15" s="850" t="inlineStr">
         <is>
           <t>OBSERVACIÓN</t>
         </is>
       </c>
-      <c r="K15" s="754" t="n"/>
-      <c r="L15" s="754" t="n"/>
-      <c r="M15" s="806" t="n"/>
+      <c r="K15" s="793" t="n"/>
+      <c r="L15" s="793" t="n"/>
+      <c r="M15" s="851" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1" s="1223">
+    <row r="16" ht="18" customHeight="1" s="550">
       <c r="A16" s="72" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="10" t="n"/>
-      <c r="C16" s="1300" t="n"/>
-      <c r="D16" s="1300" t="n"/>
-      <c r="E16" s="1300" t="n"/>
-      <c r="F16" s="1300" t="n"/>
-      <c r="G16" s="1300" t="n"/>
-      <c r="H16" s="1301">
+      <c r="C16" s="1441" t="n"/>
+      <c r="D16" s="1441" t="n"/>
+      <c r="E16" s="1441" t="n"/>
+      <c r="F16" s="1441" t="n"/>
+      <c r="G16" s="1441" t="n"/>
+      <c r="H16" s="1442">
         <f>IF(COUNTA(C16:G16)=0,"",ROUND(PRODUCT(C16:G16),3))</f>
         <v/>
       </c>
@@ -10556,22 +10970,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J16" s="793" t="n"/>
-      <c r="K16" s="794" t="n"/>
-      <c r="L16" s="794" t="n"/>
-      <c r="M16" s="795" t="n"/>
+      <c r="J16" s="837" t="n"/>
+      <c r="K16" s="838" t="n"/>
+      <c r="L16" s="838" t="n"/>
+      <c r="M16" s="839" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="1223">
+    <row r="17" ht="18" customHeight="1" s="550">
       <c r="A17" s="72" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="10" t="n"/>
-      <c r="C17" s="1300" t="n"/>
-      <c r="D17" s="1300" t="n"/>
-      <c r="E17" s="1300" t="n"/>
-      <c r="F17" s="1300" t="n"/>
-      <c r="G17" s="1300" t="n"/>
-      <c r="H17" s="1301">
+      <c r="C17" s="1441" t="n"/>
+      <c r="D17" s="1441" t="n"/>
+      <c r="E17" s="1441" t="n"/>
+      <c r="F17" s="1441" t="n"/>
+      <c r="G17" s="1441" t="n"/>
+      <c r="H17" s="1442">
         <f>IF(COUNTA(C17:G17)=0,"",ROUND(PRODUCT(C17:G17),3))</f>
         <v/>
       </c>
@@ -10580,22 +10994,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J17" s="748" t="n"/>
-      <c r="K17" s="530" t="n"/>
-      <c r="L17" s="530" t="n"/>
-      <c r="M17" s="749" t="n"/>
+      <c r="J17" s="787" t="n"/>
+      <c r="K17" s="567" t="n"/>
+      <c r="L17" s="567" t="n"/>
+      <c r="M17" s="788" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="1223">
+    <row r="18" ht="18" customHeight="1" s="550">
       <c r="A18" s="72" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="10" t="n"/>
-      <c r="C18" s="1300" t="n"/>
-      <c r="D18" s="1300" t="n"/>
-      <c r="E18" s="1300" t="n"/>
-      <c r="F18" s="1300" t="n"/>
-      <c r="G18" s="1300" t="n"/>
-      <c r="H18" s="1301">
+      <c r="C18" s="1441" t="n"/>
+      <c r="D18" s="1441" t="n"/>
+      <c r="E18" s="1441" t="n"/>
+      <c r="F18" s="1441" t="n"/>
+      <c r="G18" s="1441" t="n"/>
+      <c r="H18" s="1442">
         <f>IF(COUNTA(C18:G18)=0,"",ROUND(PRODUCT(C18:G18),3))</f>
         <v/>
       </c>
@@ -10604,22 +11018,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J18" s="748" t="n"/>
-      <c r="K18" s="530" t="n"/>
-      <c r="L18" s="530" t="n"/>
-      <c r="M18" s="749" t="n"/>
+      <c r="J18" s="787" t="n"/>
+      <c r="K18" s="567" t="n"/>
+      <c r="L18" s="567" t="n"/>
+      <c r="M18" s="788" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="1223">
+    <row r="19" ht="18" customHeight="1" s="550">
       <c r="A19" s="72" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="10" t="n"/>
-      <c r="C19" s="1300" t="n"/>
-      <c r="D19" s="1300" t="n"/>
-      <c r="E19" s="1300" t="n"/>
-      <c r="F19" s="1300" t="n"/>
-      <c r="G19" s="1300" t="n"/>
-      <c r="H19" s="1301">
+      <c r="C19" s="1441" t="n"/>
+      <c r="D19" s="1441" t="n"/>
+      <c r="E19" s="1441" t="n"/>
+      <c r="F19" s="1441" t="n"/>
+      <c r="G19" s="1441" t="n"/>
+      <c r="H19" s="1442">
         <f>IF(COUNTA(C19:G19)=0,"",ROUND(PRODUCT(C19:G19),3))</f>
         <v/>
       </c>
@@ -10628,22 +11042,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J19" s="748" t="n"/>
-      <c r="K19" s="530" t="n"/>
-      <c r="L19" s="530" t="n"/>
-      <c r="M19" s="749" t="n"/>
+      <c r="J19" s="787" t="n"/>
+      <c r="K19" s="567" t="n"/>
+      <c r="L19" s="567" t="n"/>
+      <c r="M19" s="788" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="1223">
+    <row r="20" ht="18" customHeight="1" s="550">
       <c r="A20" s="72" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="10" t="n"/>
-      <c r="C20" s="1300" t="n"/>
-      <c r="D20" s="1300" t="n"/>
-      <c r="E20" s="1300" t="n"/>
-      <c r="F20" s="1300" t="n"/>
-      <c r="G20" s="1300" t="n"/>
-      <c r="H20" s="1301">
+      <c r="C20" s="1441" t="n"/>
+      <c r="D20" s="1441" t="n"/>
+      <c r="E20" s="1441" t="n"/>
+      <c r="F20" s="1441" t="n"/>
+      <c r="G20" s="1441" t="n"/>
+      <c r="H20" s="1442">
         <f>IF(COUNTA(C20:G20)=0,"",ROUND(PRODUCT(C20:G20),3))</f>
         <v/>
       </c>
@@ -10652,22 +11066,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J20" s="748" t="n"/>
-      <c r="K20" s="530" t="n"/>
-      <c r="L20" s="530" t="n"/>
-      <c r="M20" s="749" t="n"/>
+      <c r="J20" s="787" t="n"/>
+      <c r="K20" s="567" t="n"/>
+      <c r="L20" s="567" t="n"/>
+      <c r="M20" s="788" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="1223">
+    <row r="21" ht="18" customHeight="1" s="550">
       <c r="A21" s="72" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="10" t="n"/>
-      <c r="C21" s="1300" t="n"/>
-      <c r="D21" s="1300" t="n"/>
-      <c r="E21" s="1300" t="n"/>
-      <c r="F21" s="1300" t="n"/>
-      <c r="G21" s="1300" t="n"/>
-      <c r="H21" s="1301">
+      <c r="C21" s="1441" t="n"/>
+      <c r="D21" s="1441" t="n"/>
+      <c r="E21" s="1441" t="n"/>
+      <c r="F21" s="1441" t="n"/>
+      <c r="G21" s="1441" t="n"/>
+      <c r="H21" s="1442">
         <f>IF(COUNTA(C21:G21)=0,"",ROUND(PRODUCT(C21:G21),3))</f>
         <v/>
       </c>
@@ -10676,22 +11090,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J21" s="748" t="n"/>
-      <c r="K21" s="530" t="n"/>
-      <c r="L21" s="530" t="n"/>
-      <c r="M21" s="749" t="n"/>
+      <c r="J21" s="787" t="n"/>
+      <c r="K21" s="567" t="n"/>
+      <c r="L21" s="567" t="n"/>
+      <c r="M21" s="788" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="1223">
+    <row r="22" ht="18" customHeight="1" s="550">
       <c r="A22" s="72" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="10" t="n"/>
-      <c r="C22" s="1300" t="n"/>
-      <c r="D22" s="1300" t="n"/>
-      <c r="E22" s="1300" t="n"/>
-      <c r="F22" s="1300" t="n"/>
-      <c r="G22" s="1300" t="n"/>
-      <c r="H22" s="1301">
+      <c r="C22" s="1441" t="n"/>
+      <c r="D22" s="1441" t="n"/>
+      <c r="E22" s="1441" t="n"/>
+      <c r="F22" s="1441" t="n"/>
+      <c r="G22" s="1441" t="n"/>
+      <c r="H22" s="1442">
         <f>IF(COUNTA(C22:G22)=0,"",ROUND(PRODUCT(C22:G22),3))</f>
         <v/>
       </c>
@@ -10700,22 +11114,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J22" s="748" t="n"/>
-      <c r="K22" s="530" t="n"/>
-      <c r="L22" s="530" t="n"/>
-      <c r="M22" s="749" t="n"/>
+      <c r="J22" s="787" t="n"/>
+      <c r="K22" s="567" t="n"/>
+      <c r="L22" s="567" t="n"/>
+      <c r="M22" s="788" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="1223">
+    <row r="23" ht="18" customHeight="1" s="550">
       <c r="A23" s="72" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="10" t="n"/>
-      <c r="C23" s="1300" t="n"/>
-      <c r="D23" s="1300" t="n"/>
-      <c r="E23" s="1300" t="n"/>
-      <c r="F23" s="1300" t="n"/>
-      <c r="G23" s="1300" t="n"/>
-      <c r="H23" s="1301">
+      <c r="C23" s="1441" t="n"/>
+      <c r="D23" s="1441" t="n"/>
+      <c r="E23" s="1441" t="n"/>
+      <c r="F23" s="1441" t="n"/>
+      <c r="G23" s="1441" t="n"/>
+      <c r="H23" s="1442">
         <f>IF(COUNTA(C23:G23)=0,"",ROUND(PRODUCT(C23:G23),3))</f>
         <v/>
       </c>
@@ -10724,22 +11138,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J23" s="748" t="n"/>
-      <c r="K23" s="530" t="n"/>
-      <c r="L23" s="530" t="n"/>
-      <c r="M23" s="749" t="n"/>
+      <c r="J23" s="787" t="n"/>
+      <c r="K23" s="567" t="n"/>
+      <c r="L23" s="567" t="n"/>
+      <c r="M23" s="788" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="1223">
+    <row r="24" ht="18" customHeight="1" s="550">
       <c r="A24" s="72" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="10" t="n"/>
-      <c r="C24" s="1300" t="n"/>
-      <c r="D24" s="1300" t="n"/>
-      <c r="E24" s="1300" t="n"/>
-      <c r="F24" s="1300" t="n"/>
-      <c r="G24" s="1300" t="n"/>
-      <c r="H24" s="1301">
+      <c r="C24" s="1441" t="n"/>
+      <c r="D24" s="1441" t="n"/>
+      <c r="E24" s="1441" t="n"/>
+      <c r="F24" s="1441" t="n"/>
+      <c r="G24" s="1441" t="n"/>
+      <c r="H24" s="1442">
         <f>IF(COUNTA(C24:G24)=0,"",ROUND(PRODUCT(C24:G24),3))</f>
         <v/>
       </c>
@@ -10748,22 +11162,22 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J24" s="748" t="n"/>
-      <c r="K24" s="530" t="n"/>
-      <c r="L24" s="530" t="n"/>
-      <c r="M24" s="749" t="n"/>
+      <c r="J24" s="787" t="n"/>
+      <c r="K24" s="567" t="n"/>
+      <c r="L24" s="567" t="n"/>
+      <c r="M24" s="788" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="1223" thickBot="1">
+    <row r="25" ht="18" customHeight="1" s="550" thickBot="1">
       <c r="A25" s="72" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="10" t="n"/>
-      <c r="C25" s="1300" t="n"/>
-      <c r="D25" s="1300" t="n"/>
-      <c r="E25" s="1300" t="n"/>
-      <c r="F25" s="1300" t="n"/>
-      <c r="G25" s="1300" t="n"/>
-      <c r="H25" s="1301">
+      <c r="C25" s="1441" t="n"/>
+      <c r="D25" s="1441" t="n"/>
+      <c r="E25" s="1441" t="n"/>
+      <c r="F25" s="1441" t="n"/>
+      <c r="G25" s="1441" t="n"/>
+      <c r="H25" s="1442">
         <f>IF(COUNTA(C25:G25)=0,"",ROUND(PRODUCT(C25:G25),3))</f>
         <v/>
       </c>
@@ -10772,23 +11186,23 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J25" s="748" t="n"/>
-      <c r="K25" s="530" t="n"/>
-      <c r="L25" s="530" t="n"/>
-      <c r="M25" s="749" t="n"/>
+      <c r="J25" s="787" t="n"/>
+      <c r="K25" s="567" t="n"/>
+      <c r="L25" s="567" t="n"/>
+      <c r="M25" s="788" t="n"/>
     </row>
     <row r="26" ht="18" customFormat="1" customHeight="1" s="12" thickBot="1">
-      <c r="A26" s="753" t="inlineStr">
+      <c r="A26" s="792" t="inlineStr">
         <is>
           <t>TOTAL CANTIDAD CALCULADA</t>
         </is>
       </c>
-      <c r="B26" s="754" t="n"/>
-      <c r="C26" s="754" t="n"/>
-      <c r="D26" s="754" t="n"/>
-      <c r="E26" s="754" t="n"/>
-      <c r="F26" s="754" t="n"/>
-      <c r="G26" s="754" t="n"/>
+      <c r="B26" s="793" t="n"/>
+      <c r="C26" s="793" t="n"/>
+      <c r="D26" s="793" t="n"/>
+      <c r="E26" s="793" t="n"/>
+      <c r="F26" s="793" t="n"/>
+      <c r="G26" s="793" t="n"/>
       <c r="H26" s="11">
         <f>IF(COUNT(H16:H25)=0,"",ROUND(SUM(H16:H25),3))</f>
         <v/>
@@ -10798,144 +11212,144 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="J26" s="748" t="n"/>
-      <c r="K26" s="530" t="n"/>
-      <c r="L26" s="530" t="n"/>
-      <c r="M26" s="749" t="n"/>
+      <c r="J26" s="787" t="n"/>
+      <c r="K26" s="567" t="n"/>
+      <c r="L26" s="567" t="n"/>
+      <c r="M26" s="788" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="1223">
+    <row r="27" ht="18" customHeight="1" s="550">
       <c r="A27" s="70" t="n"/>
-      <c r="J27" s="766" t="n"/>
-      <c r="K27" s="743" t="n"/>
-      <c r="L27" s="743" t="n"/>
-      <c r="M27" s="767" t="n"/>
+      <c r="J27" s="809" t="n"/>
+      <c r="K27" s="782" t="n"/>
+      <c r="L27" s="782" t="n"/>
+      <c r="M27" s="810" t="n"/>
     </row>
-    <row r="28" ht="19.5" customHeight="1" s="1223">
-      <c r="A28" s="760" t="inlineStr">
+    <row r="28" ht="19.5" customHeight="1" s="550">
+      <c r="A28" s="797" t="inlineStr">
         <is>
           <t>03  |  RESUMEN Y CONTROL DE CANTIDADES</t>
         </is>
       </c>
-      <c r="B28" s="761" t="n"/>
-      <c r="C28" s="761" t="n"/>
-      <c r="D28" s="761" t="n"/>
-      <c r="E28" s="761" t="n"/>
-      <c r="F28" s="761" t="n"/>
-      <c r="G28" s="761" t="n"/>
-      <c r="H28" s="761" t="n"/>
-      <c r="I28" s="761" t="n"/>
-      <c r="J28" s="761" t="n"/>
-      <c r="K28" s="761" t="n"/>
-      <c r="L28" s="761" t="n"/>
-      <c r="M28" s="762" t="n"/>
+      <c r="B28" s="798" t="n"/>
+      <c r="C28" s="798" t="n"/>
+      <c r="D28" s="798" t="n"/>
+      <c r="E28" s="798" t="n"/>
+      <c r="F28" s="798" t="n"/>
+      <c r="G28" s="798" t="n"/>
+      <c r="H28" s="798" t="n"/>
+      <c r="I28" s="798" t="n"/>
+      <c r="J28" s="798" t="n"/>
+      <c r="K28" s="798" t="n"/>
+      <c r="L28" s="798" t="n"/>
+      <c r="M28" s="799" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="1223">
-      <c r="A29" s="757" t="inlineStr">
+    <row r="29" ht="18" customHeight="1" s="550">
+      <c r="A29" s="794" t="inlineStr">
         <is>
           <t>Cantidad calculada</t>
         </is>
       </c>
-      <c r="B29" s="743" t="n"/>
-      <c r="C29" s="743" t="n"/>
-      <c r="D29" s="751">
+      <c r="B29" s="782" t="n"/>
+      <c r="C29" s="782" t="n"/>
+      <c r="D29" s="790">
         <f>H26</f>
         <v/>
       </c>
-      <c r="E29" s="743" t="n"/>
-      <c r="F29" s="743" t="n"/>
-      <c r="G29" s="743" t="n"/>
-      <c r="H29" s="782" t="inlineStr">
+      <c r="E29" s="782" t="n"/>
+      <c r="F29" s="782" t="n"/>
+      <c r="G29" s="782" t="n"/>
+      <c r="H29" s="819" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="I29" s="743" t="n"/>
+      <c r="I29" s="782" t="n"/>
       <c r="M29" s="71" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="1223">
-      <c r="A30" s="757" t="inlineStr">
+    <row r="30" ht="18" customHeight="1" s="550">
+      <c r="A30" s="794" t="inlineStr">
         <is>
           <t>Cantidad contractual</t>
         </is>
       </c>
-      <c r="B30" s="743" t="n"/>
-      <c r="C30" s="743" t="n"/>
-      <c r="D30" s="799" t="n"/>
-      <c r="E30" s="743" t="n"/>
-      <c r="F30" s="743" t="n"/>
-      <c r="G30" s="743" t="n"/>
-      <c r="H30" s="782" t="inlineStr">
+      <c r="B30" s="782" t="n"/>
+      <c r="C30" s="782" t="n"/>
+      <c r="D30" s="843" t="n"/>
+      <c r="E30" s="782" t="n"/>
+      <c r="F30" s="782" t="n"/>
+      <c r="G30" s="782" t="n"/>
+      <c r="H30" s="819" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="I30" s="743" t="n"/>
+      <c r="I30" s="782" t="n"/>
       <c r="M30" s="71" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="1223">
-      <c r="A31" s="757" t="inlineStr">
+    <row r="31" ht="18" customHeight="1" s="550">
+      <c r="A31" s="794" t="inlineStr">
         <is>
           <t>Saldo contractual</t>
         </is>
       </c>
-      <c r="B31" s="743" t="n"/>
-      <c r="C31" s="743" t="n"/>
-      <c r="D31" s="751">
+      <c r="B31" s="782" t="n"/>
+      <c r="C31" s="782" t="n"/>
+      <c r="D31" s="790">
         <f>IF(OR(D29="",D30=""),"",D30-D29)</f>
         <v/>
       </c>
-      <c r="E31" s="743" t="n"/>
-      <c r="F31" s="743" t="n"/>
-      <c r="G31" s="743" t="n"/>
-      <c r="H31" s="782" t="inlineStr">
+      <c r="E31" s="782" t="n"/>
+      <c r="F31" s="782" t="n"/>
+      <c r="G31" s="782" t="n"/>
+      <c r="H31" s="819" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="I31" s="743" t="n"/>
+      <c r="I31" s="782" t="n"/>
       <c r="M31" s="71" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="1223">
-      <c r="A32" s="757" t="inlineStr">
+    <row r="32" ht="18" customHeight="1" s="550">
+      <c r="A32" s="794" t="inlineStr">
         <is>
           <t>% ejecutado</t>
         </is>
       </c>
-      <c r="B32" s="743" t="n"/>
-      <c r="C32" s="743" t="n"/>
-      <c r="D32" s="807">
+      <c r="B32" s="782" t="n"/>
+      <c r="C32" s="782" t="n"/>
+      <c r="D32" s="852">
         <f>IFERROR(D29/D30,0)</f>
         <v/>
       </c>
-      <c r="E32" s="743" t="n"/>
-      <c r="F32" s="743" t="n"/>
-      <c r="G32" s="743" t="n"/>
-      <c r="H32" s="782" t="inlineStr">
+      <c r="E32" s="782" t="n"/>
+      <c r="F32" s="782" t="n"/>
+      <c r="G32" s="782" t="n"/>
+      <c r="H32" s="819" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="I32" s="743" t="n"/>
+      <c r="I32" s="782" t="n"/>
       <c r="M32" s="71" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="1223">
-      <c r="A33" s="802" t="inlineStr">
+    <row r="33" ht="18" customHeight="1" s="550">
+      <c r="A33" s="846" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D33" s="759">
+      <c r="D33" s="796">
         <f>IF(D30="","PENDIENTE DE DATO",IF(D29&lt;=D30,"DENTRO DE CANTIDAD","REVISAR SOBREEJECUCIÓN"))</f>
         <v/>
       </c>
-      <c r="H33" s="808" t="inlineStr">
+      <c r="H33" s="853" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
       <c r="M33" s="71" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="1223">
+    <row r="34" ht="18" customHeight="1" s="550">
       <c r="A34" s="73" t="n"/>
       <c r="B34" s="8" t="n"/>
       <c r="C34" s="8" t="n"/>
@@ -10950,435 +11364,435 @@
       <c r="L34" s="8" t="n"/>
       <c r="M34" s="74" t="n"/>
     </row>
-    <row r="35" ht="19.5" customHeight="1" s="1223">
-      <c r="A35" s="758" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1" s="550">
+      <c r="A35" s="795" t="inlineStr">
         <is>
           <t>04  |  DESARROLLO MATEMÁTICO Y CRITERIO DE MEDICIÓN</t>
         </is>
       </c>
-      <c r="B35" s="743" t="n"/>
-      <c r="C35" s="743" t="n"/>
-      <c r="D35" s="743" t="n"/>
-      <c r="E35" s="743" t="n"/>
-      <c r="F35" s="743" t="n"/>
-      <c r="G35" s="743" t="n"/>
-      <c r="H35" s="743" t="n"/>
-      <c r="I35" s="743" t="n"/>
-      <c r="J35" s="743" t="n"/>
-      <c r="K35" s="743" t="n"/>
-      <c r="L35" s="743" t="n"/>
-      <c r="M35" s="744" t="n"/>
+      <c r="B35" s="782" t="n"/>
+      <c r="C35" s="782" t="n"/>
+      <c r="D35" s="782" t="n"/>
+      <c r="E35" s="782" t="n"/>
+      <c r="F35" s="782" t="n"/>
+      <c r="G35" s="782" t="n"/>
+      <c r="H35" s="782" t="n"/>
+      <c r="I35" s="782" t="n"/>
+      <c r="J35" s="782" t="n"/>
+      <c r="K35" s="782" t="n"/>
+      <c r="L35" s="782" t="n"/>
+      <c r="M35" s="783" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="1223">
-      <c r="A36" s="746" t="inlineStr">
+    <row r="36" ht="18" customHeight="1" s="550">
+      <c r="A36" s="785" t="inlineStr">
         <is>
           <t>CRITERIO
 Producto de las dimensiones, cantidades y factores registrados. Ajustar el factor cuando aplique.</t>
         </is>
       </c>
-      <c r="B36" s="737" t="n"/>
-      <c r="C36" s="737" t="n"/>
-      <c r="D36" s="738" t="n"/>
-      <c r="E36" s="763" t="inlineStr">
+      <c r="B36" s="776" t="n"/>
+      <c r="C36" s="776" t="n"/>
+      <c r="D36" s="777" t="n"/>
+      <c r="E36" s="800" t="inlineStr">
         <is>
           <t>OPERACIÓN AUTOMÁTICA
 Resultado por registro = PRODUCTO(CANT., LARGO, ANCHO, ALTO/PESO, FACTOR)</t>
         </is>
       </c>
-      <c r="F36" s="737" t="n"/>
-      <c r="G36" s="737" t="n"/>
-      <c r="H36" s="737" t="n"/>
-      <c r="I36" s="738" t="n"/>
-      <c r="J36" s="804" t="inlineStr">
+      <c r="F36" s="776" t="n"/>
+      <c r="G36" s="776" t="n"/>
+      <c r="H36" s="776" t="n"/>
+      <c r="I36" s="777" t="n"/>
+      <c r="J36" s="848" t="inlineStr">
         <is>
           <t>RESULTADO
 =H23</t>
         </is>
       </c>
-      <c r="K36" s="737" t="n"/>
-      <c r="L36" s="737" t="n"/>
-      <c r="M36" s="752" t="n"/>
+      <c r="K36" s="776" t="n"/>
+      <c r="L36" s="776" t="n"/>
+      <c r="M36" s="849" t="n"/>
     </row>
-    <row r="37" ht="60" customHeight="1" s="1223">
-      <c r="A37" s="747" t="n"/>
-      <c r="D37" s="741" t="n"/>
-      <c r="E37" s="739" t="n"/>
-      <c r="I37" s="741" t="n"/>
-      <c r="M37" s="546" t="n"/>
+    <row r="37" ht="60" customHeight="1" s="550">
+      <c r="A37" s="786" t="n"/>
+      <c r="D37" s="780" t="n"/>
+      <c r="E37" s="778" t="n"/>
+      <c r="I37" s="780" t="n"/>
+      <c r="M37" s="562" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="1223">
+    <row r="38" ht="18" customHeight="1" s="550">
       <c r="A38" s="70" t="n"/>
       <c r="M38" s="71" t="n"/>
     </row>
-    <row r="39" ht="19.5" customHeight="1" s="1223">
-      <c r="A39" s="787" t="inlineStr">
+    <row r="39" ht="19.5" customHeight="1" s="550">
+      <c r="A39" s="826" t="inlineStr">
         <is>
           <t>05  |  SOPORTE GRÁFICO</t>
         </is>
       </c>
-      <c r="M39" s="741" t="n"/>
+      <c r="M39" s="780" t="n"/>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="12">
-      <c r="A40" s="783" t="inlineStr">
+      <c r="A40" s="820" t="inlineStr">
         <is>
           <t>FOTOGRAFÍA 01</t>
         </is>
       </c>
-      <c r="B40" s="761" t="n"/>
-      <c r="C40" s="761" t="n"/>
-      <c r="D40" s="761" t="n"/>
-      <c r="E40" s="761" t="n"/>
-      <c r="F40" s="761" t="n"/>
-      <c r="G40" s="762" t="n"/>
-      <c r="H40" s="791" t="inlineStr">
+      <c r="B40" s="798" t="n"/>
+      <c r="C40" s="798" t="n"/>
+      <c r="D40" s="798" t="n"/>
+      <c r="E40" s="798" t="n"/>
+      <c r="F40" s="798" t="n"/>
+      <c r="G40" s="799" t="n"/>
+      <c r="H40" s="835" t="inlineStr">
         <is>
           <t>FOTOGRAFÍA 02</t>
         </is>
       </c>
-      <c r="I40" s="761" t="n"/>
-      <c r="J40" s="761" t="n"/>
-      <c r="K40" s="761" t="n"/>
-      <c r="L40" s="761" t="n"/>
-      <c r="M40" s="762" t="n"/>
+      <c r="I40" s="798" t="n"/>
+      <c r="J40" s="798" t="n"/>
+      <c r="K40" s="798" t="n"/>
+      <c r="L40" s="798" t="n"/>
+      <c r="M40" s="799" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="1223">
-      <c r="A41" s="792" t="inlineStr">
+    <row r="41" ht="18" customHeight="1" s="550">
+      <c r="A41" s="836" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="B41" s="737" t="n"/>
-      <c r="C41" s="737" t="n"/>
-      <c r="D41" s="737" t="n"/>
-      <c r="E41" s="737" t="n"/>
-      <c r="F41" s="737" t="n"/>
-      <c r="G41" s="738" t="n"/>
-      <c r="H41" s="736" t="inlineStr">
+      <c r="B41" s="776" t="n"/>
+      <c r="C41" s="776" t="n"/>
+      <c r="D41" s="776" t="n"/>
+      <c r="E41" s="776" t="n"/>
+      <c r="F41" s="776" t="n"/>
+      <c r="G41" s="777" t="n"/>
+      <c r="H41" s="775" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="I41" s="737" t="n"/>
-      <c r="J41" s="737" t="n"/>
-      <c r="K41" s="737" t="n"/>
-      <c r="L41" s="737" t="n"/>
-      <c r="M41" s="738" t="n"/>
+      <c r="I41" s="776" t="n"/>
+      <c r="J41" s="776" t="n"/>
+      <c r="K41" s="776" t="n"/>
+      <c r="L41" s="776" t="n"/>
+      <c r="M41" s="777" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="1223">
-      <c r="A42" s="747" t="n"/>
-      <c r="G42" s="741" t="n"/>
-      <c r="H42" s="739" t="n"/>
-      <c r="M42" s="741" t="n"/>
+    <row r="42" ht="18" customHeight="1" s="550">
+      <c r="A42" s="786" t="n"/>
+      <c r="G42" s="780" t="n"/>
+      <c r="H42" s="778" t="n"/>
+      <c r="M42" s="780" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="1223">
-      <c r="A43" s="747" t="n"/>
-      <c r="G43" s="741" t="n"/>
-      <c r="H43" s="739" t="n"/>
-      <c r="M43" s="741" t="n"/>
+    <row r="43" ht="18" customHeight="1" s="550">
+      <c r="A43" s="786" t="n"/>
+      <c r="G43" s="780" t="n"/>
+      <c r="H43" s="778" t="n"/>
+      <c r="M43" s="780" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="1223">
-      <c r="A44" s="747" t="n"/>
-      <c r="G44" s="741" t="n"/>
-      <c r="H44" s="739" t="n"/>
-      <c r="M44" s="741" t="n"/>
+    <row r="44" ht="18" customHeight="1" s="550">
+      <c r="A44" s="786" t="n"/>
+      <c r="G44" s="780" t="n"/>
+      <c r="H44" s="778" t="n"/>
+      <c r="M44" s="780" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="1223">
-      <c r="A45" s="747" t="n"/>
-      <c r="G45" s="741" t="n"/>
-      <c r="H45" s="739" t="n"/>
-      <c r="M45" s="741" t="n"/>
+    <row r="45" ht="18" customHeight="1" s="550">
+      <c r="A45" s="786" t="n"/>
+      <c r="G45" s="780" t="n"/>
+      <c r="H45" s="778" t="n"/>
+      <c r="M45" s="780" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1" s="1223">
-      <c r="A46" s="747" t="n"/>
-      <c r="G46" s="741" t="n"/>
-      <c r="H46" s="739" t="n"/>
-      <c r="M46" s="741" t="n"/>
+    <row r="46" ht="18" customHeight="1" s="550">
+      <c r="A46" s="786" t="n"/>
+      <c r="G46" s="780" t="n"/>
+      <c r="H46" s="778" t="n"/>
+      <c r="M46" s="780" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1" s="1223">
-      <c r="A47" s="747" t="n"/>
-      <c r="G47" s="741" t="n"/>
-      <c r="H47" s="739" t="n"/>
-      <c r="M47" s="741" t="n"/>
+    <row r="47" ht="18" customHeight="1" s="550">
+      <c r="A47" s="786" t="n"/>
+      <c r="G47" s="780" t="n"/>
+      <c r="H47" s="778" t="n"/>
+      <c r="M47" s="780" t="n"/>
     </row>
-    <row r="48" ht="18" customHeight="1" s="1223">
-      <c r="A48" s="747" t="n"/>
-      <c r="G48" s="741" t="n"/>
-      <c r="H48" s="739" t="n"/>
-      <c r="M48" s="741" t="n"/>
+    <row r="48" ht="18" customHeight="1" s="550">
+      <c r="A48" s="786" t="n"/>
+      <c r="G48" s="780" t="n"/>
+      <c r="H48" s="778" t="n"/>
+      <c r="M48" s="780" t="n"/>
     </row>
-    <row r="49" ht="18" customHeight="1" s="1223">
-      <c r="A49" s="747" t="n"/>
-      <c r="G49" s="741" t="n"/>
-      <c r="H49" s="739" t="n"/>
-      <c r="M49" s="741" t="n"/>
+    <row r="49" ht="18" customHeight="1" s="550">
+      <c r="A49" s="786" t="n"/>
+      <c r="G49" s="780" t="n"/>
+      <c r="H49" s="778" t="n"/>
+      <c r="M49" s="780" t="n"/>
     </row>
-    <row r="50" ht="18" customHeight="1" s="1223">
-      <c r="A50" s="747" t="n"/>
-      <c r="G50" s="741" t="n"/>
-      <c r="H50" s="739" t="n"/>
-      <c r="M50" s="741" t="n"/>
+    <row r="50" ht="18" customHeight="1" s="550">
+      <c r="A50" s="786" t="n"/>
+      <c r="G50" s="780" t="n"/>
+      <c r="H50" s="778" t="n"/>
+      <c r="M50" s="780" t="n"/>
     </row>
-    <row r="51" ht="18" customHeight="1" s="1223">
-      <c r="A51" s="747" t="n"/>
-      <c r="G51" s="741" t="n"/>
-      <c r="H51" s="739" t="n"/>
-      <c r="M51" s="741" t="n"/>
+    <row r="51" ht="18" customHeight="1" s="550">
+      <c r="A51" s="786" t="n"/>
+      <c r="G51" s="780" t="n"/>
+      <c r="H51" s="778" t="n"/>
+      <c r="M51" s="780" t="n"/>
     </row>
-    <row r="52" ht="18" customHeight="1" s="1223">
-      <c r="A52" s="747" t="n"/>
-      <c r="G52" s="741" t="n"/>
-      <c r="H52" s="739" t="n"/>
-      <c r="M52" s="741" t="n"/>
+    <row r="52" ht="18" customHeight="1" s="550">
+      <c r="A52" s="786" t="n"/>
+      <c r="G52" s="780" t="n"/>
+      <c r="H52" s="778" t="n"/>
+      <c r="M52" s="780" t="n"/>
     </row>
-    <row r="53" ht="18" customHeight="1" s="1223">
-      <c r="A53" s="747" t="n"/>
-      <c r="G53" s="741" t="n"/>
-      <c r="H53" s="739" t="n"/>
-      <c r="M53" s="741" t="n"/>
+    <row r="53" ht="18" customHeight="1" s="550">
+      <c r="A53" s="786" t="n"/>
+      <c r="G53" s="780" t="n"/>
+      <c r="H53" s="778" t="n"/>
+      <c r="M53" s="780" t="n"/>
     </row>
-    <row r="54" ht="18" customHeight="1" s="1223">
-      <c r="A54" s="747" t="n"/>
-      <c r="G54" s="741" t="n"/>
-      <c r="H54" s="739" t="n"/>
-      <c r="M54" s="741" t="n"/>
+    <row r="54" ht="18" customHeight="1" s="550">
+      <c r="A54" s="786" t="n"/>
+      <c r="G54" s="780" t="n"/>
+      <c r="H54" s="778" t="n"/>
+      <c r="M54" s="780" t="n"/>
     </row>
-    <row r="55" ht="18" customHeight="1" s="1223">
-      <c r="A55" s="747" t="n"/>
-      <c r="G55" s="741" t="n"/>
-      <c r="H55" s="739" t="n"/>
-      <c r="M55" s="741" t="n"/>
+    <row r="55" ht="18" customHeight="1" s="550">
+      <c r="A55" s="786" t="n"/>
+      <c r="G55" s="780" t="n"/>
+      <c r="H55" s="778" t="n"/>
+      <c r="M55" s="780" t="n"/>
     </row>
-    <row r="56" ht="18" customHeight="1" s="1223">
-      <c r="A56" s="756" t="n"/>
-      <c r="B56" s="743" t="n"/>
-      <c r="C56" s="743" t="n"/>
-      <c r="D56" s="743" t="n"/>
-      <c r="E56" s="743" t="n"/>
-      <c r="F56" s="743" t="n"/>
-      <c r="G56" s="744" t="n"/>
-      <c r="H56" s="742" t="n"/>
-      <c r="I56" s="743" t="n"/>
-      <c r="J56" s="743" t="n"/>
-      <c r="K56" s="743" t="n"/>
-      <c r="L56" s="743" t="n"/>
-      <c r="M56" s="744" t="n"/>
+    <row r="56" ht="18" customHeight="1" s="550">
+      <c r="A56" s="814" t="n"/>
+      <c r="B56" s="782" t="n"/>
+      <c r="C56" s="782" t="n"/>
+      <c r="D56" s="782" t="n"/>
+      <c r="E56" s="782" t="n"/>
+      <c r="F56" s="782" t="n"/>
+      <c r="G56" s="783" t="n"/>
+      <c r="H56" s="781" t="n"/>
+      <c r="I56" s="782" t="n"/>
+      <c r="J56" s="782" t="n"/>
+      <c r="K56" s="782" t="n"/>
+      <c r="L56" s="782" t="n"/>
+      <c r="M56" s="783" t="n"/>
     </row>
-    <row r="57" ht="18" customHeight="1" s="1223">
-      <c r="A57" s="765" t="inlineStr">
+    <row r="57" ht="18" customHeight="1" s="550">
+      <c r="A57" s="808" t="inlineStr">
         <is>
           <t>Pie de foto / fecha / ubicación: ____________________</t>
         </is>
       </c>
-      <c r="B57" s="761" t="n"/>
-      <c r="C57" s="761" t="n"/>
-      <c r="D57" s="761" t="n"/>
-      <c r="E57" s="761" t="n"/>
-      <c r="F57" s="761" t="n"/>
-      <c r="G57" s="762" t="n"/>
-      <c r="H57" s="785" t="inlineStr">
+      <c r="B57" s="798" t="n"/>
+      <c r="C57" s="798" t="n"/>
+      <c r="D57" s="798" t="n"/>
+      <c r="E57" s="798" t="n"/>
+      <c r="F57" s="798" t="n"/>
+      <c r="G57" s="799" t="n"/>
+      <c r="H57" s="822" t="inlineStr">
         <is>
           <t>Pie de foto / fecha / ubicación: ____________________</t>
         </is>
       </c>
-      <c r="I57" s="761" t="n"/>
-      <c r="J57" s="761" t="n"/>
-      <c r="K57" s="761" t="n"/>
-      <c r="L57" s="761" t="n"/>
-      <c r="M57" s="762" t="n"/>
+      <c r="I57" s="798" t="n"/>
+      <c r="J57" s="798" t="n"/>
+      <c r="K57" s="798" t="n"/>
+      <c r="L57" s="798" t="n"/>
+      <c r="M57" s="799" t="n"/>
     </row>
     <row r="58" ht="18" customFormat="1" customHeight="1" s="12">
-      <c r="A58" s="783" t="inlineStr">
+      <c r="A58" s="820" t="inlineStr">
         <is>
           <t>FOTOGRAFÍA 03</t>
         </is>
       </c>
-      <c r="B58" s="761" t="n"/>
-      <c r="C58" s="761" t="n"/>
-      <c r="D58" s="761" t="n"/>
-      <c r="E58" s="761" t="n"/>
-      <c r="F58" s="761" t="n"/>
-      <c r="G58" s="762" t="n"/>
-      <c r="H58" s="791" t="inlineStr">
+      <c r="B58" s="798" t="n"/>
+      <c r="C58" s="798" t="n"/>
+      <c r="D58" s="798" t="n"/>
+      <c r="E58" s="798" t="n"/>
+      <c r="F58" s="798" t="n"/>
+      <c r="G58" s="799" t="n"/>
+      <c r="H58" s="835" t="inlineStr">
         <is>
           <t>FOTOGRAFÍA 04</t>
         </is>
       </c>
-      <c r="I58" s="761" t="n"/>
-      <c r="J58" s="761" t="n"/>
-      <c r="K58" s="761" t="n"/>
-      <c r="L58" s="761" t="n"/>
-      <c r="M58" s="762" t="n"/>
+      <c r="I58" s="798" t="n"/>
+      <c r="J58" s="798" t="n"/>
+      <c r="K58" s="798" t="n"/>
+      <c r="L58" s="798" t="n"/>
+      <c r="M58" s="799" t="n"/>
     </row>
-    <row r="59" ht="18" customHeight="1" s="1223">
-      <c r="A59" s="792" t="inlineStr">
+    <row r="59" ht="18" customHeight="1" s="550">
+      <c r="A59" s="836" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="B59" s="737" t="n"/>
-      <c r="C59" s="737" t="n"/>
-      <c r="D59" s="737" t="n"/>
-      <c r="E59" s="737" t="n"/>
-      <c r="F59" s="737" t="n"/>
-      <c r="G59" s="738" t="n"/>
-      <c r="H59" s="736" t="inlineStr">
+      <c r="B59" s="776" t="n"/>
+      <c r="C59" s="776" t="n"/>
+      <c r="D59" s="776" t="n"/>
+      <c r="E59" s="776" t="n"/>
+      <c r="F59" s="776" t="n"/>
+      <c r="G59" s="777" t="n"/>
+      <c r="H59" s="775" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="I59" s="737" t="n"/>
-      <c r="J59" s="737" t="n"/>
-      <c r="K59" s="737" t="n"/>
-      <c r="L59" s="737" t="n"/>
-      <c r="M59" s="738" t="n"/>
+      <c r="I59" s="776" t="n"/>
+      <c r="J59" s="776" t="n"/>
+      <c r="K59" s="776" t="n"/>
+      <c r="L59" s="776" t="n"/>
+      <c r="M59" s="777" t="n"/>
     </row>
-    <row r="60" ht="18" customHeight="1" s="1223">
-      <c r="A60" s="747" t="n"/>
-      <c r="G60" s="741" t="n"/>
-      <c r="H60" s="739" t="n"/>
-      <c r="M60" s="741" t="n"/>
+    <row r="60" ht="18" customHeight="1" s="550">
+      <c r="A60" s="786" t="n"/>
+      <c r="G60" s="780" t="n"/>
+      <c r="H60" s="778" t="n"/>
+      <c r="M60" s="780" t="n"/>
     </row>
-    <row r="61" ht="18" customHeight="1" s="1223">
-      <c r="A61" s="747" t="n"/>
-      <c r="G61" s="741" t="n"/>
-      <c r="H61" s="739" t="n"/>
-      <c r="M61" s="741" t="n"/>
+    <row r="61" ht="18" customHeight="1" s="550">
+      <c r="A61" s="786" t="n"/>
+      <c r="G61" s="780" t="n"/>
+      <c r="H61" s="778" t="n"/>
+      <c r="M61" s="780" t="n"/>
     </row>
-    <row r="62" ht="18" customHeight="1" s="1223">
-      <c r="A62" s="747" t="n"/>
-      <c r="G62" s="741" t="n"/>
-      <c r="H62" s="739" t="n"/>
-      <c r="M62" s="741" t="n"/>
+    <row r="62" ht="18" customHeight="1" s="550">
+      <c r="A62" s="786" t="n"/>
+      <c r="G62" s="780" t="n"/>
+      <c r="H62" s="778" t="n"/>
+      <c r="M62" s="780" t="n"/>
     </row>
-    <row r="63" ht="18" customHeight="1" s="1223">
-      <c r="A63" s="747" t="n"/>
-      <c r="G63" s="741" t="n"/>
-      <c r="H63" s="739" t="n"/>
-      <c r="M63" s="741" t="n"/>
+    <row r="63" ht="18" customHeight="1" s="550">
+      <c r="A63" s="786" t="n"/>
+      <c r="G63" s="780" t="n"/>
+      <c r="H63" s="778" t="n"/>
+      <c r="M63" s="780" t="n"/>
     </row>
-    <row r="64" ht="18" customHeight="1" s="1223">
-      <c r="A64" s="747" t="n"/>
-      <c r="G64" s="741" t="n"/>
-      <c r="H64" s="739" t="n"/>
-      <c r="M64" s="741" t="n"/>
+    <row r="64" ht="18" customHeight="1" s="550">
+      <c r="A64" s="786" t="n"/>
+      <c r="G64" s="780" t="n"/>
+      <c r="H64" s="778" t="n"/>
+      <c r="M64" s="780" t="n"/>
     </row>
-    <row r="65" ht="18" customHeight="1" s="1223">
-      <c r="A65" s="747" t="n"/>
-      <c r="G65" s="741" t="n"/>
-      <c r="H65" s="739" t="n"/>
-      <c r="M65" s="741" t="n"/>
+    <row r="65" ht="18" customHeight="1" s="550">
+      <c r="A65" s="786" t="n"/>
+      <c r="G65" s="780" t="n"/>
+      <c r="H65" s="778" t="n"/>
+      <c r="M65" s="780" t="n"/>
     </row>
-    <row r="66" ht="18" customHeight="1" s="1223">
-      <c r="A66" s="747" t="n"/>
-      <c r="G66" s="741" t="n"/>
-      <c r="H66" s="739" t="n"/>
-      <c r="M66" s="741" t="n"/>
+    <row r="66" ht="18" customHeight="1" s="550">
+      <c r="A66" s="786" t="n"/>
+      <c r="G66" s="780" t="n"/>
+      <c r="H66" s="778" t="n"/>
+      <c r="M66" s="780" t="n"/>
     </row>
-    <row r="67" ht="18" customHeight="1" s="1223">
-      <c r="A67" s="747" t="n"/>
-      <c r="G67" s="741" t="n"/>
-      <c r="H67" s="739" t="n"/>
-      <c r="M67" s="741" t="n"/>
+    <row r="67" ht="18" customHeight="1" s="550">
+      <c r="A67" s="786" t="n"/>
+      <c r="G67" s="780" t="n"/>
+      <c r="H67" s="778" t="n"/>
+      <c r="M67" s="780" t="n"/>
     </row>
-    <row r="68" ht="18" customHeight="1" s="1223">
-      <c r="A68" s="747" t="n"/>
-      <c r="G68" s="741" t="n"/>
-      <c r="H68" s="739" t="n"/>
-      <c r="M68" s="741" t="n"/>
+    <row r="68" ht="18" customHeight="1" s="550">
+      <c r="A68" s="786" t="n"/>
+      <c r="G68" s="780" t="n"/>
+      <c r="H68" s="778" t="n"/>
+      <c r="M68" s="780" t="n"/>
     </row>
-    <row r="69" ht="18" customHeight="1" s="1223">
-      <c r="A69" s="747" t="n"/>
-      <c r="G69" s="741" t="n"/>
-      <c r="H69" s="739" t="n"/>
-      <c r="M69" s="741" t="n"/>
+    <row r="69" ht="18" customHeight="1" s="550">
+      <c r="A69" s="786" t="n"/>
+      <c r="G69" s="780" t="n"/>
+      <c r="H69" s="778" t="n"/>
+      <c r="M69" s="780" t="n"/>
     </row>
-    <row r="70" ht="18" customHeight="1" s="1223">
-      <c r="A70" s="747" t="n"/>
-      <c r="G70" s="741" t="n"/>
-      <c r="H70" s="739" t="n"/>
-      <c r="M70" s="741" t="n"/>
+    <row r="70" ht="18" customHeight="1" s="550">
+      <c r="A70" s="786" t="n"/>
+      <c r="G70" s="780" t="n"/>
+      <c r="H70" s="778" t="n"/>
+      <c r="M70" s="780" t="n"/>
     </row>
-    <row r="71" ht="18" customHeight="1" s="1223">
-      <c r="A71" s="747" t="n"/>
-      <c r="G71" s="741" t="n"/>
-      <c r="H71" s="739" t="n"/>
-      <c r="M71" s="741" t="n"/>
+    <row r="71" ht="18" customHeight="1" s="550">
+      <c r="A71" s="786" t="n"/>
+      <c r="G71" s="780" t="n"/>
+      <c r="H71" s="778" t="n"/>
+      <c r="M71" s="780" t="n"/>
     </row>
-    <row r="72" ht="18" customHeight="1" s="1223">
-      <c r="A72" s="747" t="n"/>
-      <c r="G72" s="741" t="n"/>
-      <c r="H72" s="739" t="n"/>
-      <c r="M72" s="741" t="n"/>
+    <row r="72" ht="18" customHeight="1" s="550">
+      <c r="A72" s="786" t="n"/>
+      <c r="G72" s="780" t="n"/>
+      <c r="H72" s="778" t="n"/>
+      <c r="M72" s="780" t="n"/>
     </row>
-    <row r="73" ht="18" customHeight="1" s="1223">
-      <c r="A73" s="747" t="n"/>
-      <c r="G73" s="741" t="n"/>
-      <c r="H73" s="739" t="n"/>
-      <c r="M73" s="741" t="n"/>
+    <row r="73" ht="18" customHeight="1" s="550">
+      <c r="A73" s="786" t="n"/>
+      <c r="G73" s="780" t="n"/>
+      <c r="H73" s="778" t="n"/>
+      <c r="M73" s="780" t="n"/>
     </row>
-    <row r="74" ht="18" customHeight="1" s="1223">
-      <c r="A74" s="756" t="n"/>
-      <c r="B74" s="743" t="n"/>
-      <c r="C74" s="743" t="n"/>
-      <c r="D74" s="743" t="n"/>
-      <c r="E74" s="743" t="n"/>
-      <c r="F74" s="743" t="n"/>
-      <c r="G74" s="744" t="n"/>
-      <c r="H74" s="742" t="n"/>
-      <c r="I74" s="743" t="n"/>
-      <c r="J74" s="743" t="n"/>
-      <c r="K74" s="743" t="n"/>
-      <c r="L74" s="743" t="n"/>
-      <c r="M74" s="744" t="n"/>
+    <row r="74" ht="18" customHeight="1" s="550">
+      <c r="A74" s="814" t="n"/>
+      <c r="B74" s="782" t="n"/>
+      <c r="C74" s="782" t="n"/>
+      <c r="D74" s="782" t="n"/>
+      <c r="E74" s="782" t="n"/>
+      <c r="F74" s="782" t="n"/>
+      <c r="G74" s="783" t="n"/>
+      <c r="H74" s="781" t="n"/>
+      <c r="I74" s="782" t="n"/>
+      <c r="J74" s="782" t="n"/>
+      <c r="K74" s="782" t="n"/>
+      <c r="L74" s="782" t="n"/>
+      <c r="M74" s="783" t="n"/>
     </row>
-    <row r="75" ht="18" customHeight="1" s="1223">
-      <c r="A75" s="765" t="inlineStr">
+    <row r="75" ht="18" customHeight="1" s="550">
+      <c r="A75" s="808" t="inlineStr">
         <is>
           <t>Pie de foto / fecha / ubicación: ____________________</t>
         </is>
       </c>
-      <c r="B75" s="761" t="n"/>
-      <c r="C75" s="761" t="n"/>
-      <c r="D75" s="761" t="n"/>
-      <c r="E75" s="761" t="n"/>
-      <c r="F75" s="761" t="n"/>
-      <c r="G75" s="762" t="n"/>
-      <c r="H75" s="785" t="inlineStr">
+      <c r="B75" s="798" t="n"/>
+      <c r="C75" s="798" t="n"/>
+      <c r="D75" s="798" t="n"/>
+      <c r="E75" s="798" t="n"/>
+      <c r="F75" s="798" t="n"/>
+      <c r="G75" s="799" t="n"/>
+      <c r="H75" s="822" t="inlineStr">
         <is>
           <t>Pie de foto / fecha / ubicación: ____________________</t>
         </is>
       </c>
-      <c r="I75" s="761" t="n"/>
-      <c r="J75" s="761" t="n"/>
-      <c r="K75" s="761" t="n"/>
-      <c r="L75" s="761" t="n"/>
-      <c r="M75" s="762" t="n"/>
+      <c r="I75" s="798" t="n"/>
+      <c r="J75" s="798" t="n"/>
+      <c r="K75" s="798" t="n"/>
+      <c r="L75" s="798" t="n"/>
+      <c r="M75" s="799" t="n"/>
     </row>
-    <row r="76" ht="19.5" customHeight="1" s="1223">
-      <c r="A76" s="772" t="inlineStr">
+    <row r="76" ht="19.5" customHeight="1" s="550">
+      <c r="A76" s="812" t="inlineStr">
         <is>
           <t>06  |  ESQUEMA DE LA ESTRUCTURA / ELEMENTO INTERVENIDO</t>
         </is>
       </c>
-      <c r="M76" s="546" t="n"/>
+      <c r="M76" s="562" t="n"/>
     </row>
-    <row r="77" ht="19.5" customHeight="1" s="1223">
-      <c r="A77" s="773" t="inlineStr">
+    <row r="77" ht="19.5" customHeight="1" s="550">
+      <c r="A77" s="813" t="inlineStr">
         <is>
           <t>INSERTAR AQUÍ ESQUEMA, CROQUIS, DETALLE CONSTRUCTIVO O PLANO
 Indicar ejes, cotas, niveles, espesores, diámetros, longitudes y referencias necesarias para verificar la medición.</t>
         </is>
       </c>
-      <c r="B77" s="737" t="n"/>
-      <c r="C77" s="737" t="n"/>
-      <c r="D77" s="737" t="n"/>
-      <c r="E77" s="737" t="n"/>
-      <c r="F77" s="737" t="n"/>
-      <c r="G77" s="737" t="n"/>
-      <c r="H77" s="737" t="n"/>
-      <c r="I77" s="737" t="n"/>
-      <c r="J77" s="738" t="n"/>
-      <c r="K77" s="810" t="inlineStr">
+      <c r="B77" s="776" t="n"/>
+      <c r="C77" s="776" t="n"/>
+      <c r="D77" s="776" t="n"/>
+      <c r="E77" s="776" t="n"/>
+      <c r="F77" s="776" t="n"/>
+      <c r="G77" s="776" t="n"/>
+      <c r="H77" s="776" t="n"/>
+      <c r="I77" s="776" t="n"/>
+      <c r="J77" s="777" t="n"/>
+      <c r="K77" s="855" t="inlineStr">
         <is>
           <t>REFERENCIAS
 Plano: __________________
@@ -11388,222 +11802,246 @@
 Observación: _____________</t>
         </is>
       </c>
-      <c r="L77" s="737" t="n"/>
-      <c r="M77" s="738" t="n"/>
+      <c r="L77" s="776" t="n"/>
+      <c r="M77" s="777" t="n"/>
     </row>
-    <row r="78" ht="19.5" customHeight="1" s="1223">
-      <c r="A78" s="747" t="n"/>
-      <c r="J78" s="741" t="n"/>
-      <c r="K78" s="739" t="n"/>
-      <c r="M78" s="741" t="n"/>
+    <row r="78" ht="19.5" customHeight="1" s="550">
+      <c r="A78" s="786" t="n"/>
+      <c r="J78" s="780" t="n"/>
+      <c r="K78" s="778" t="n"/>
+      <c r="M78" s="780" t="n"/>
     </row>
-    <row r="79" ht="19.5" customHeight="1" s="1223">
-      <c r="A79" s="747" t="n"/>
-      <c r="J79" s="741" t="n"/>
-      <c r="K79" s="739" t="n"/>
-      <c r="M79" s="741" t="n"/>
+    <row r="79" ht="19.5" customHeight="1" s="550">
+      <c r="A79" s="786" t="n"/>
+      <c r="J79" s="780" t="n"/>
+      <c r="K79" s="778" t="n"/>
+      <c r="M79" s="780" t="n"/>
     </row>
-    <row r="80" ht="19.5" customHeight="1" s="1223">
-      <c r="A80" s="747" t="n"/>
-      <c r="J80" s="741" t="n"/>
-      <c r="K80" s="739" t="n"/>
-      <c r="M80" s="741" t="n"/>
+    <row r="80" ht="19.5" customHeight="1" s="550">
+      <c r="A80" s="786" t="n"/>
+      <c r="J80" s="780" t="n"/>
+      <c r="K80" s="778" t="n"/>
+      <c r="M80" s="780" t="n"/>
     </row>
-    <row r="81" ht="19.5" customHeight="1" s="1223">
-      <c r="A81" s="747" t="n"/>
-      <c r="J81" s="741" t="n"/>
-      <c r="K81" s="739" t="n"/>
-      <c r="M81" s="741" t="n"/>
+    <row r="81" ht="19.5" customHeight="1" s="550">
+      <c r="A81" s="786" t="n"/>
+      <c r="J81" s="780" t="n"/>
+      <c r="K81" s="778" t="n"/>
+      <c r="M81" s="780" t="n"/>
     </row>
-    <row r="82" ht="19.5" customHeight="1" s="1223">
-      <c r="A82" s="747" t="n"/>
-      <c r="J82" s="741" t="n"/>
-      <c r="K82" s="739" t="n"/>
-      <c r="M82" s="741" t="n"/>
+    <row r="82" ht="19.5" customHeight="1" s="550">
+      <c r="A82" s="786" t="n"/>
+      <c r="J82" s="780" t="n"/>
+      <c r="K82" s="778" t="n"/>
+      <c r="M82" s="780" t="n"/>
     </row>
-    <row r="83" ht="18" customHeight="1" s="1223">
-      <c r="A83" s="747" t="n"/>
-      <c r="J83" s="741" t="n"/>
-      <c r="K83" s="739" t="n"/>
-      <c r="M83" s="741" t="n"/>
+    <row r="83" ht="18" customHeight="1" s="550">
+      <c r="A83" s="786" t="n"/>
+      <c r="J83" s="780" t="n"/>
+      <c r="K83" s="778" t="n"/>
+      <c r="M83" s="780" t="n"/>
     </row>
-    <row r="84" ht="18" customHeight="1" s="1223">
-      <c r="A84" s="747" t="n"/>
-      <c r="J84" s="741" t="n"/>
-      <c r="K84" s="739" t="n"/>
-      <c r="M84" s="741" t="n"/>
+    <row r="84" ht="18" customHeight="1" s="550">
+      <c r="A84" s="786" t="n"/>
+      <c r="J84" s="780" t="n"/>
+      <c r="K84" s="778" t="n"/>
+      <c r="M84" s="780" t="n"/>
     </row>
-    <row r="85" ht="18" customHeight="1" s="1223">
-      <c r="A85" s="747" t="n"/>
-      <c r="J85" s="741" t="n"/>
-      <c r="K85" s="739" t="n"/>
-      <c r="M85" s="741" t="n"/>
+    <row r="85" ht="18" customHeight="1" s="550">
+      <c r="A85" s="786" t="n"/>
+      <c r="J85" s="780" t="n"/>
+      <c r="K85" s="778" t="n"/>
+      <c r="M85" s="780" t="n"/>
     </row>
-    <row r="86" ht="18" customHeight="1" s="1223">
-      <c r="A86" s="747" t="n"/>
-      <c r="J86" s="741" t="n"/>
-      <c r="K86" s="739" t="n"/>
-      <c r="M86" s="741" t="n"/>
+    <row r="86" ht="18" customHeight="1" s="550">
+      <c r="A86" s="786" t="n"/>
+      <c r="J86" s="780" t="n"/>
+      <c r="K86" s="778" t="n"/>
+      <c r="M86" s="780" t="n"/>
     </row>
-    <row r="87" ht="18" customHeight="1" s="1223">
-      <c r="A87" s="747" t="n"/>
-      <c r="J87" s="741" t="n"/>
-      <c r="K87" s="739" t="n"/>
-      <c r="M87" s="741" t="n"/>
+    <row r="87" ht="18" customHeight="1" s="550">
+      <c r="A87" s="786" t="n"/>
+      <c r="J87" s="780" t="n"/>
+      <c r="K87" s="778" t="n"/>
+      <c r="M87" s="780" t="n"/>
     </row>
-    <row r="88" ht="18" customHeight="1" s="1223">
-      <c r="A88" s="747" t="n"/>
-      <c r="J88" s="741" t="n"/>
-      <c r="K88" s="739" t="n"/>
-      <c r="M88" s="741" t="n"/>
+    <row r="88" ht="18" customHeight="1" s="550">
+      <c r="A88" s="786" t="n"/>
+      <c r="J88" s="780" t="n"/>
+      <c r="K88" s="778" t="n"/>
+      <c r="M88" s="780" t="n"/>
     </row>
-    <row r="89" ht="18" customHeight="1" s="1223">
-      <c r="A89" s="747" t="n"/>
-      <c r="J89" s="741" t="n"/>
-      <c r="K89" s="739" t="n"/>
-      <c r="M89" s="741" t="n"/>
+    <row r="89" ht="18" customHeight="1" s="550">
+      <c r="A89" s="786" t="n"/>
+      <c r="J89" s="780" t="n"/>
+      <c r="K89" s="778" t="n"/>
+      <c r="M89" s="780" t="n"/>
     </row>
-    <row r="90" ht="18" customHeight="1" s="1223">
-      <c r="A90" s="747" t="n"/>
-      <c r="J90" s="741" t="n"/>
-      <c r="K90" s="739" t="n"/>
-      <c r="M90" s="741" t="n"/>
+    <row r="90" ht="18" customHeight="1" s="550">
+      <c r="A90" s="786" t="n"/>
+      <c r="J90" s="780" t="n"/>
+      <c r="K90" s="778" t="n"/>
+      <c r="M90" s="780" t="n"/>
     </row>
-    <row r="91" ht="18" customHeight="1" s="1223">
-      <c r="A91" s="747" t="n"/>
-      <c r="J91" s="741" t="n"/>
-      <c r="K91" s="739" t="n"/>
-      <c r="M91" s="741" t="n"/>
+    <row r="91" ht="18" customHeight="1" s="550">
+      <c r="A91" s="786" t="n"/>
+      <c r="J91" s="780" t="n"/>
+      <c r="K91" s="778" t="n"/>
+      <c r="M91" s="780" t="n"/>
     </row>
-    <row r="92" ht="18" customHeight="1" s="1223">
-      <c r="A92" s="747" t="n"/>
-      <c r="J92" s="741" t="n"/>
-      <c r="K92" s="739" t="n"/>
-      <c r="M92" s="741" t="n"/>
+    <row r="92" ht="18" customHeight="1" s="550">
+      <c r="A92" s="786" t="n"/>
+      <c r="J92" s="780" t="n"/>
+      <c r="K92" s="778" t="n"/>
+      <c r="M92" s="780" t="n"/>
     </row>
-    <row r="93" ht="18" customHeight="1" s="1223">
-      <c r="A93" s="756" t="n"/>
-      <c r="B93" s="743" t="n"/>
-      <c r="C93" s="743" t="n"/>
-      <c r="D93" s="743" t="n"/>
-      <c r="E93" s="743" t="n"/>
-      <c r="F93" s="743" t="n"/>
-      <c r="G93" s="743" t="n"/>
-      <c r="H93" s="743" t="n"/>
-      <c r="I93" s="743" t="n"/>
-      <c r="J93" s="744" t="n"/>
-      <c r="K93" s="742" t="n"/>
-      <c r="L93" s="743" t="n"/>
-      <c r="M93" s="744" t="n"/>
+    <row r="93" ht="18" customHeight="1" s="550">
+      <c r="A93" s="814" t="n"/>
+      <c r="B93" s="782" t="n"/>
+      <c r="C93" s="782" t="n"/>
+      <c r="D93" s="782" t="n"/>
+      <c r="E93" s="782" t="n"/>
+      <c r="F93" s="782" t="n"/>
+      <c r="G93" s="782" t="n"/>
+      <c r="H93" s="782" t="n"/>
+      <c r="I93" s="782" t="n"/>
+      <c r="J93" s="783" t="n"/>
+      <c r="K93" s="781" t="n"/>
+      <c r="L93" s="782" t="n"/>
+      <c r="M93" s="783" t="n"/>
     </row>
-    <row r="94" ht="19.5" customHeight="1" s="1223">
-      <c r="A94" s="772" t="inlineStr">
+    <row r="94" ht="19.5" customHeight="1" s="550">
+      <c r="A94" s="812" t="inlineStr">
         <is>
           <t>07  |  RESPONSABLES Y TRAZABILIDAD</t>
         </is>
       </c>
-      <c r="M94" s="546" t="n"/>
+      <c r="M94" s="562" t="n"/>
     </row>
-    <row r="95" ht="18" customHeight="1" s="1223">
-      <c r="A95" s="809" t="inlineStr">
+    <row r="95" ht="18" customHeight="1" s="550">
+      <c r="A95" s="854" t="inlineStr">
         <is>
           <t>ELABORÓ</t>
         </is>
       </c>
-      <c r="B95" s="761" t="n"/>
-      <c r="C95" s="761" t="n"/>
-      <c r="D95" s="762" t="n"/>
-      <c r="E95" s="796" t="inlineStr">
+      <c r="B95" s="798" t="n"/>
+      <c r="C95" s="798" t="n"/>
+      <c r="D95" s="799" t="n"/>
+      <c r="E95" s="840" t="inlineStr">
         <is>
           <t>REVISÓ</t>
         </is>
       </c>
-      <c r="F95" s="761" t="n"/>
-      <c r="G95" s="761" t="n"/>
-      <c r="H95" s="761" t="n"/>
-      <c r="I95" s="797" t="inlineStr">
+      <c r="F95" s="798" t="n"/>
+      <c r="G95" s="798" t="n"/>
+      <c r="H95" s="798" t="n"/>
+      <c r="I95" s="841" t="inlineStr">
         <is>
           <t>APROBÓ</t>
         </is>
       </c>
-      <c r="J95" s="790" t="n"/>
-      <c r="K95" s="790" t="n"/>
-      <c r="L95" s="790" t="n"/>
-      <c r="M95" s="798" t="n"/>
+      <c r="J95" s="831" t="n"/>
+      <c r="K95" s="831" t="n"/>
+      <c r="L95" s="831" t="n"/>
+      <c r="M95" s="842" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="1313" t="n"/>
-      <c r="E96" s="1313" t="n"/>
-      <c r="I96" s="1313" t="n"/>
+      <c r="A96" s="802" t="n"/>
+      <c r="B96" s="803" t="n"/>
+      <c r="C96" s="803" t="n"/>
+      <c r="D96" s="804" t="n"/>
+      <c r="E96" s="802" t="n"/>
+      <c r="F96" s="803" t="n"/>
+      <c r="G96" s="803" t="n"/>
+      <c r="H96" s="804" t="n"/>
+      <c r="I96" s="802" t="n"/>
+      <c r="J96" s="803" t="n"/>
+      <c r="K96" s="803" t="n"/>
+      <c r="L96" s="803" t="n"/>
+      <c r="M96" s="804" t="n"/>
     </row>
-    <row r="97"/>
-    <row r="98" ht="18" customHeight="1" s="1223">
+    <row r="97">
+      <c r="A97" s="805" t="n"/>
+      <c r="B97" s="806" t="n"/>
+      <c r="C97" s="806" t="n"/>
+      <c r="D97" s="807" t="n"/>
+      <c r="E97" s="805" t="n"/>
+      <c r="F97" s="806" t="n"/>
+      <c r="G97" s="806" t="n"/>
+      <c r="H97" s="807" t="n"/>
+      <c r="I97" s="805" t="n"/>
+      <c r="J97" s="806" t="n"/>
+      <c r="K97" s="806" t="n"/>
+      <c r="L97" s="806" t="n"/>
+      <c r="M97" s="807" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1" s="550">
       <c r="A98" s="75" t="n"/>
-      <c r="B98" s="1314" t="n"/>
-      <c r="C98" s="737" t="n"/>
-      <c r="D98" s="738" t="n"/>
-      <c r="E98" s="1315" t="n"/>
-      <c r="F98" s="737" t="n"/>
-      <c r="G98" s="737" t="n"/>
-      <c r="H98" s="770" t="n"/>
-      <c r="I98" s="1316" t="n"/>
-      <c r="J98" s="777" t="n"/>
-      <c r="K98" s="777" t="n"/>
-      <c r="L98" s="777" t="n"/>
-      <c r="M98" s="778" t="n"/>
+      <c r="B98" s="832" t="n"/>
+      <c r="C98" s="776" t="n"/>
+      <c r="D98" s="777" t="n"/>
+      <c r="E98" s="816" t="n"/>
+      <c r="F98" s="776" t="n"/>
+      <c r="G98" s="776" t="n"/>
+      <c r="H98" s="817" t="n"/>
+      <c r="I98" s="821" t="n"/>
+      <c r="J98" s="770" t="n"/>
+      <c r="K98" s="770" t="n"/>
+      <c r="L98" s="770" t="n"/>
+      <c r="M98" s="771" t="n"/>
     </row>
-    <row r="99" ht="18" customHeight="1" s="1223">
+    <row r="99" ht="18" customHeight="1" s="550">
       <c r="A99" s="75" t="n"/>
-      <c r="B99" s="743" t="n"/>
-      <c r="C99" s="743" t="n"/>
-      <c r="D99" s="744" t="n"/>
-      <c r="E99" s="742" t="n"/>
-      <c r="F99" s="743" t="n"/>
-      <c r="G99" s="743" t="n"/>
-      <c r="H99" s="771" t="n"/>
-      <c r="I99" s="779" t="n"/>
-      <c r="J99" s="780" t="n"/>
-      <c r="K99" s="780" t="n"/>
-      <c r="L99" s="780" t="n"/>
-      <c r="M99" s="781" t="n"/>
+      <c r="B99" s="782" t="n"/>
+      <c r="C99" s="782" t="n"/>
+      <c r="D99" s="783" t="n"/>
+      <c r="E99" s="781" t="n"/>
+      <c r="F99" s="782" t="n"/>
+      <c r="G99" s="782" t="n"/>
+      <c r="H99" s="818" t="n"/>
+      <c r="I99" s="772" t="n"/>
+      <c r="J99" s="773" t="n"/>
+      <c r="K99" s="773" t="n"/>
+      <c r="L99" s="773" t="n"/>
+      <c r="M99" s="774" t="n"/>
     </row>
-    <row r="100" ht="18" customHeight="1" s="1223">
-      <c r="A100" s="755" t="n"/>
-      <c r="B100" s="737" t="n"/>
-      <c r="C100" s="737" t="n"/>
-      <c r="D100" s="738" t="n"/>
-      <c r="E100" s="775" t="n"/>
-      <c r="F100" s="737" t="n"/>
-      <c r="G100" s="737" t="n"/>
-      <c r="H100" s="737" t="n"/>
-      <c r="I100" s="784" t="n"/>
-      <c r="J100" s="777" t="n"/>
-      <c r="K100" s="777" t="n"/>
-      <c r="L100" s="777" t="n"/>
-      <c r="M100" s="778" t="n"/>
+    <row r="100" ht="18" customHeight="1" s="550">
+      <c r="A100" s="829" t="n"/>
+      <c r="B100" s="776" t="n"/>
+      <c r="C100" s="776" t="n"/>
+      <c r="D100" s="777" t="n"/>
+      <c r="E100" s="833" t="n"/>
+      <c r="F100" s="776" t="n"/>
+      <c r="G100" s="776" t="n"/>
+      <c r="H100" s="776" t="n"/>
+      <c r="I100" s="769" t="n"/>
+      <c r="J100" s="770" t="n"/>
+      <c r="K100" s="770" t="n"/>
+      <c r="L100" s="770" t="n"/>
+      <c r="M100" s="771" t="n"/>
     </row>
-    <row r="101" ht="18" customHeight="1" s="1223">
-      <c r="A101" s="756" t="n"/>
-      <c r="B101" s="743" t="n"/>
-      <c r="C101" s="743" t="n"/>
-      <c r="D101" s="744" t="n"/>
-      <c r="E101" s="742" t="n"/>
-      <c r="F101" s="743" t="n"/>
-      <c r="G101" s="743" t="n"/>
-      <c r="H101" s="743" t="n"/>
-      <c r="I101" s="779" t="n"/>
-      <c r="J101" s="780" t="n"/>
-      <c r="K101" s="780" t="n"/>
-      <c r="L101" s="780" t="n"/>
-      <c r="M101" s="781" t="n"/>
+    <row r="101" ht="18" customHeight="1" s="550">
+      <c r="A101" s="814" t="n"/>
+      <c r="B101" s="782" t="n"/>
+      <c r="C101" s="782" t="n"/>
+      <c r="D101" s="783" t="n"/>
+      <c r="E101" s="781" t="n"/>
+      <c r="F101" s="782" t="n"/>
+      <c r="G101" s="782" t="n"/>
+      <c r="H101" s="782" t="n"/>
+      <c r="I101" s="772" t="n"/>
+      <c r="J101" s="773" t="n"/>
+      <c r="K101" s="773" t="n"/>
+      <c r="L101" s="773" t="n"/>
+      <c r="M101" s="774" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="209" t="inlineStr">
+      <c r="A102" s="206" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="M102" s="210">
+      <c r="M102" s="207">
         <f>L5</f>
         <v/>
       </c>
@@ -11652,8 +12090,8 @@
     <mergeCell ref="I96:M97"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="D29:G29"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="A58:G58"/>
-    <mergeCell ref="K11:L11"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="I98:M99"/>
     <mergeCell ref="H75:M75"/>
